--- a/docs/data/jp/xlsx/5832.xlsx
+++ b/docs/data/jp/xlsx/5832.xlsx
@@ -195,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -311,6 +311,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -705,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC229"/>
+  <dimension ref="A1:AC242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5161,10 +5164,12 @@
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B59" s="27" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="n">
+        <v>3284</v>
+      </c>
       <c r="C59" s="28" t="n"/>
       <c r="D59" s="29" t="n"/>
       <c r="E59" s="29" t="n"/>
@@ -5199,7 +5204,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B60" s="27" t="n"/>
+      <c r="B60" s="27" t="n">
+        <v>184771461</v>
+      </c>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="29" t="n"/>
       <c r="E60" s="29" t="n"/>
@@ -6398,7 +6405,7 @@
     <row r="86">
       <c r="A86" s="41" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C86" s="39" t="n"/>
@@ -6647,1329 +6654,1339 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="18" t="inlineStr">
-        <is>
-          <t>자금운용수익</t>
-        </is>
-      </c>
-      <c r="C91" s="20" t="n">
-        <v>29694</v>
-      </c>
-      <c r="D91" s="20" t="n">
-        <v>31865</v>
-      </c>
-      <c r="E91" s="20" t="n">
-        <v>33094</v>
-      </c>
-      <c r="F91" s="20" t="n">
-        <v>37822</v>
-      </c>
-      <c r="G91" s="20" t="n">
-        <v>34916</v>
-      </c>
-      <c r="H91" s="20" t="n">
-        <v>40607</v>
-      </c>
-      <c r="I91" s="20" t="n">
-        <v>36700</v>
-      </c>
-      <c r="J91" s="20" t="n">
-        <v>40428</v>
-      </c>
-      <c r="K91" s="20" t="n">
-        <v>40234</v>
-      </c>
-      <c r="L91" s="20" t="n">
-        <v>45749</v>
-      </c>
-      <c r="M91" s="20" t="n">
-        <v>43552</v>
-      </c>
-      <c r="N91" s="20" t="n">
-        <v>50265</v>
-      </c>
-      <c r="U91" s="20" t="n">
-        <v>24907</v>
-      </c>
-      <c r="V91" s="20" t="n">
-        <v>33094</v>
-      </c>
-      <c r="W91" s="20" t="n">
-        <v>36700</v>
-      </c>
-      <c r="X91" s="20" t="n">
-        <v>43552</v>
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G91" s="15">
+        <f>IF(OR(G90="",C90=""),"",IF(C90&lt;=0,"",IFERROR(G90/C90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H91" s="15">
+        <f>IF(OR(H90="",D90=""),"",IF(D90&lt;=0,"",IFERROR(H90/D90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I91" s="15">
+        <f>IF(OR(I90="",E90=""),"",IF(E90&lt;=0,"",IFERROR(I90/E90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J91" s="15">
+        <f>IF(OR(J90="",F90=""),"",IF(F90&lt;=0,"",IFERROR(J90/F90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K91" s="15">
+        <f>IF(OR(K90="",G90=""),"",IF(G90&lt;=0,"",IFERROR(K90/G90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L91" s="15">
+        <f>IF(OR(L90="",H90=""),"",IF(H90&lt;=0,"",IFERROR(L90/H90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M91" s="15">
+        <f>IF(OR(M90="",I90=""),"",IF(I90&lt;=0,"",IFERROR(M90/I90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N91" s="15">
+        <f>IF(OR(N90="",J90=""),"",IF(J90&lt;=0,"",IFERROR(N90/J90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U91" s="15">
+        <f>IF(OR(U90="",T90=""),"",IF(T90&lt;=0,"",IFERROR(U90/T90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V91" s="15">
+        <f>IF(OR(V90="",U90=""),"",IF(U90&lt;=0,"",IFERROR(V90/U90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W91" s="15">
+        <f>IF(OR(W90="",V90=""),"",IF(V90&lt;=0,"",IFERROR(W90/V90-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X91" s="15">
+        <f>IF(OR(X90="",W90=""),"",IF(W90&lt;=0,"",IFERROR(X90/W90-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="inlineStr">
         <is>
-          <t>(이 중 대출금 이자)</t>
+          <t>자금운용수익</t>
         </is>
       </c>
       <c r="C92" s="20" t="n">
-        <v>20839</v>
+        <v>29694</v>
       </c>
       <c r="D92" s="20" t="n">
-        <v>21695</v>
+        <v>31865</v>
       </c>
       <c r="E92" s="20" t="n">
-        <v>22533</v>
+        <v>33094</v>
       </c>
       <c r="F92" s="20" t="n">
-        <v>24609</v>
+        <v>37822</v>
       </c>
       <c r="G92" s="20" t="n">
-        <v>23635</v>
+        <v>34916</v>
       </c>
       <c r="H92" s="20" t="n">
-        <v>26081</v>
+        <v>40607</v>
       </c>
       <c r="I92" s="20" t="n">
-        <v>24521</v>
+        <v>36700</v>
       </c>
       <c r="J92" s="20" t="n">
-        <v>25743</v>
+        <v>40428</v>
       </c>
       <c r="K92" s="20" t="n">
-        <v>26575</v>
+        <v>40234</v>
       </c>
       <c r="L92" s="20" t="n">
-        <v>27431</v>
+        <v>45749</v>
       </c>
       <c r="M92" s="20" t="n">
-        <v>27587</v>
+        <v>43552</v>
       </c>
       <c r="N92" s="20" t="n">
-        <v>29596</v>
+        <v>50265</v>
       </c>
       <c r="U92" s="20" t="n">
-        <v>17277</v>
+        <v>24907</v>
       </c>
       <c r="V92" s="20" t="n">
-        <v>22533</v>
+        <v>33094</v>
       </c>
       <c r="W92" s="20" t="n">
-        <v>24521</v>
+        <v>36700</v>
       </c>
       <c r="X92" s="20" t="n">
-        <v>27587</v>
+        <v>43552</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="inlineStr">
         <is>
-          <t>(이 중 유가증권 이자·배당금)</t>
+          <t>(이 중 대출금 이자)</t>
         </is>
       </c>
       <c r="C93" s="20" t="n">
-        <v>7872</v>
+        <v>20839</v>
       </c>
       <c r="D93" s="20" t="n">
-        <v>8933</v>
+        <v>21695</v>
       </c>
       <c r="E93" s="20" t="n">
-        <v>9258</v>
+        <v>22533</v>
       </c>
       <c r="F93" s="20" t="n">
-        <v>11423</v>
+        <v>24609</v>
       </c>
       <c r="G93" s="20" t="n">
-        <v>9311</v>
+        <v>23635</v>
       </c>
       <c r="H93" s="20" t="n">
-        <v>12577</v>
+        <v>26081</v>
       </c>
       <c r="I93" s="20" t="n">
-        <v>10047</v>
+        <v>24521</v>
       </c>
       <c r="J93" s="20" t="n">
-        <v>12785</v>
+        <v>25743</v>
       </c>
       <c r="K93" s="20" t="n">
-        <v>11803</v>
+        <v>26575</v>
       </c>
       <c r="L93" s="20" t="n">
-        <v>16393</v>
+        <v>27431</v>
       </c>
       <c r="M93" s="20" t="n">
-        <v>13711</v>
+        <v>27587</v>
       </c>
       <c r="N93" s="20" t="n">
-        <v>18479</v>
+        <v>29596</v>
       </c>
       <c r="U93" s="20" t="n">
-        <v>6863</v>
+        <v>17277</v>
       </c>
       <c r="V93" s="20" t="n">
-        <v>9258</v>
+        <v>22533</v>
       </c>
       <c r="W93" s="20" t="n">
-        <v>10047</v>
+        <v>24521</v>
       </c>
       <c r="X93" s="20" t="n">
-        <v>13711</v>
+        <v>27587</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="inlineStr">
         <is>
-          <t>신탁보수</t>
+          <t>(이 중 유가증권 이자·배당금)</t>
         </is>
       </c>
       <c r="C94" s="20" t="n">
-        <v>0</v>
+        <v>7872</v>
       </c>
       <c r="D94" s="20" t="n">
-        <v>0</v>
+        <v>8933</v>
       </c>
       <c r="E94" s="20" t="n">
-        <v>0</v>
+        <v>9258</v>
       </c>
       <c r="F94" s="20" t="n">
-        <v>0</v>
+        <v>11423</v>
       </c>
       <c r="G94" s="20" t="n">
-        <v>1</v>
+        <v>9311</v>
       </c>
       <c r="H94" s="20" t="n">
-        <v>0</v>
+        <v>12577</v>
       </c>
       <c r="I94" s="20" t="n">
-        <v>8</v>
+        <v>10047</v>
       </c>
       <c r="J94" s="20" t="n">
-        <v>0</v>
+        <v>12785</v>
       </c>
       <c r="K94" s="20" t="n">
-        <v>14</v>
+        <v>11803</v>
       </c>
       <c r="L94" s="20" t="n">
-        <v>1</v>
+        <v>16393</v>
       </c>
       <c r="M94" s="20" t="n">
-        <v>19</v>
+        <v>13711</v>
       </c>
       <c r="N94" s="20" t="n">
-        <v>0</v>
+        <v>18479</v>
       </c>
       <c r="U94" s="20" t="n">
-        <v>0</v>
+        <v>6863</v>
       </c>
       <c r="V94" s="20" t="n">
-        <v>0</v>
+        <v>9258</v>
       </c>
       <c r="W94" s="20" t="n">
-        <v>8</v>
+        <v>10047</v>
       </c>
       <c r="X94" s="20" t="n">
-        <v>19</v>
+        <v>13711</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="inlineStr">
         <is>
-          <t>용역거래 수익</t>
+          <t>신탁보수</t>
         </is>
       </c>
       <c r="C95" s="20" t="n">
-        <v>5475</v>
+        <v>0</v>
       </c>
       <c r="D95" s="20" t="n">
-        <v>5222</v>
+        <v>0</v>
       </c>
       <c r="E95" s="20" t="n">
-        <v>6432</v>
+        <v>0</v>
       </c>
       <c r="F95" s="20" t="n">
-        <v>5698</v>
+        <v>0</v>
       </c>
       <c r="G95" s="20" t="n">
-        <v>6592</v>
+        <v>1</v>
       </c>
       <c r="H95" s="20" t="n">
-        <v>5748</v>
+        <v>0</v>
       </c>
       <c r="I95" s="20" t="n">
-        <v>6125</v>
+        <v>8</v>
       </c>
       <c r="J95" s="20" t="n">
-        <v>6171</v>
+        <v>0</v>
       </c>
       <c r="K95" s="20" t="n">
-        <v>6442</v>
+        <v>14</v>
       </c>
       <c r="L95" s="20" t="n">
-        <v>6292</v>
+        <v>1</v>
       </c>
       <c r="M95" s="20" t="n">
-        <v>7159</v>
+        <v>19</v>
       </c>
       <c r="N95" s="20" t="n">
-        <v>6344</v>
+        <v>0</v>
       </c>
       <c r="U95" s="20" t="n">
-        <v>5362</v>
+        <v>0</v>
       </c>
       <c r="V95" s="20" t="n">
-        <v>6432</v>
+        <v>0</v>
       </c>
       <c r="W95" s="20" t="n">
-        <v>6125</v>
+        <v>8</v>
       </c>
       <c r="X95" s="20" t="n">
-        <v>7159</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="inlineStr">
         <is>
-          <t>기타 업무수익</t>
+          <t>용역거래 수익</t>
         </is>
       </c>
       <c r="C96" s="20" t="n">
-        <v>7163</v>
+        <v>5475</v>
       </c>
       <c r="D96" s="20" t="n">
-        <v>7971</v>
+        <v>5222</v>
       </c>
       <c r="E96" s="20" t="n">
-        <v>5664</v>
+        <v>6432</v>
       </c>
       <c r="F96" s="20" t="n">
-        <v>7446</v>
+        <v>5698</v>
       </c>
       <c r="G96" s="20" t="n">
-        <v>7571</v>
+        <v>6592</v>
       </c>
       <c r="H96" s="20" t="n">
-        <v>7036</v>
+        <v>5748</v>
       </c>
       <c r="I96" s="20" t="n">
-        <v>6779</v>
+        <v>6125</v>
       </c>
       <c r="J96" s="20" t="n">
-        <v>6602</v>
+        <v>6171</v>
       </c>
       <c r="K96" s="20" t="n">
-        <v>7216</v>
+        <v>6442</v>
       </c>
       <c r="L96" s="20" t="n">
-        <v>8003</v>
+        <v>6292</v>
       </c>
       <c r="M96" s="20" t="n">
-        <v>8733</v>
+        <v>7159</v>
       </c>
       <c r="N96" s="20" t="n">
-        <v>33329</v>
+        <v>6344</v>
       </c>
       <c r="U96" s="20" t="n">
-        <v>12197</v>
+        <v>5362</v>
       </c>
       <c r="V96" s="20" t="n">
-        <v>5664</v>
+        <v>6432</v>
       </c>
       <c r="W96" s="20" t="n">
-        <v>6779</v>
+        <v>6125</v>
       </c>
       <c r="X96" s="20" t="n">
-        <v>8733</v>
+        <v>7159</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="inlineStr">
         <is>
-          <t>기타 경상수익</t>
+          <t>기타 업무수익</t>
         </is>
       </c>
       <c r="C97" s="20" t="n">
-        <v>2170</v>
+        <v>7163</v>
       </c>
       <c r="D97" s="20" t="n">
-        <v>2692</v>
+        <v>7971</v>
       </c>
       <c r="E97" s="20" t="n">
-        <v>3366</v>
+        <v>5664</v>
       </c>
       <c r="F97" s="20" t="n">
-        <v>1467</v>
+        <v>7446</v>
       </c>
       <c r="G97" s="20" t="n">
-        <v>1404</v>
+        <v>7571</v>
       </c>
       <c r="H97" s="20" t="n">
-        <v>3771</v>
+        <v>7036</v>
       </c>
       <c r="I97" s="20" t="n">
-        <v>2040</v>
+        <v>6779</v>
       </c>
       <c r="J97" s="20" t="n">
-        <v>3403</v>
+        <v>6602</v>
       </c>
       <c r="K97" s="20" t="n">
-        <v>4004</v>
+        <v>7216</v>
       </c>
       <c r="L97" s="20" t="n">
-        <v>7826</v>
+        <v>8003</v>
       </c>
       <c r="M97" s="20" t="n">
-        <v>7224</v>
+        <v>8733</v>
       </c>
       <c r="N97" s="20" t="n">
-        <v>19700</v>
+        <v>33329</v>
       </c>
       <c r="U97" s="20" t="n">
-        <v>1249</v>
+        <v>12197</v>
       </c>
       <c r="V97" s="20" t="n">
-        <v>3366</v>
+        <v>5664</v>
       </c>
       <c r="W97" s="20" t="n">
-        <v>2040</v>
+        <v>6779</v>
       </c>
       <c r="X97" s="20" t="n">
-        <v>7224</v>
+        <v>8733</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="inlineStr">
         <is>
-          <t>경상비용</t>
+          <t>기타 경상수익</t>
         </is>
       </c>
       <c r="C98" s="20" t="n">
-        <v>39740</v>
+        <v>2170</v>
       </c>
       <c r="D98" s="20" t="n">
-        <v>36466</v>
+        <v>2692</v>
       </c>
       <c r="E98" s="20" t="n">
-        <v>43685</v>
+        <v>3366</v>
       </c>
       <c r="F98" s="20" t="n">
-        <v>38706</v>
+        <v>1467</v>
       </c>
       <c r="G98" s="20" t="n">
-        <v>43229</v>
+        <v>1404</v>
       </c>
       <c r="H98" s="20" t="n">
-        <v>48935</v>
+        <v>3771</v>
       </c>
       <c r="I98" s="20" t="n">
-        <v>42555</v>
+        <v>2040</v>
       </c>
       <c r="J98" s="20" t="n">
-        <v>41622</v>
+        <v>3403</v>
       </c>
       <c r="K98" s="20" t="n">
-        <v>47692</v>
+        <v>4004</v>
       </c>
       <c r="L98" s="20" t="n">
-        <v>47576</v>
+        <v>7826</v>
       </c>
       <c r="M98" s="20" t="n">
-        <v>56146</v>
+        <v>7224</v>
       </c>
       <c r="N98" s="20" t="n">
-        <v>89370</v>
+        <v>19700</v>
       </c>
       <c r="U98" s="20" t="n">
-        <v>39572</v>
+        <v>1249</v>
       </c>
       <c r="V98" s="20" t="n">
-        <v>43685</v>
+        <v>3366</v>
       </c>
       <c r="W98" s="20" t="n">
-        <v>42555</v>
+        <v>2040</v>
       </c>
       <c r="X98" s="20" t="n">
-        <v>56146</v>
+        <v>7224</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="18" t="inlineStr">
         <is>
-          <t>자금조달비용</t>
+          <t>경상비용</t>
         </is>
       </c>
       <c r="C99" s="20" t="n">
-        <v>15127</v>
+        <v>39740</v>
       </c>
       <c r="D99" s="20" t="n">
-        <v>15851</v>
+        <v>36466</v>
       </c>
       <c r="E99" s="20" t="n">
-        <v>17878</v>
+        <v>43685</v>
       </c>
       <c r="F99" s="20" t="n">
-        <v>19294</v>
+        <v>38706</v>
       </c>
       <c r="G99" s="20" t="n">
-        <v>17431</v>
+        <v>43229</v>
       </c>
       <c r="H99" s="20" t="n">
-        <v>20338</v>
+        <v>48935</v>
       </c>
       <c r="I99" s="20" t="n">
-        <v>17617</v>
+        <v>42555</v>
       </c>
       <c r="J99" s="20" t="n">
-        <v>18308</v>
+        <v>41622</v>
       </c>
       <c r="K99" s="20" t="n">
-        <v>19041</v>
+        <v>47692</v>
       </c>
       <c r="L99" s="20" t="n">
-        <v>19466</v>
+        <v>47576</v>
       </c>
       <c r="M99" s="20" t="n">
-        <v>19580</v>
+        <v>56146</v>
       </c>
       <c r="N99" s="20" t="n">
-        <v>19922</v>
+        <v>89370</v>
       </c>
       <c r="U99" s="20" t="n">
-        <v>10769</v>
+        <v>39572</v>
       </c>
       <c r="V99" s="20" t="n">
-        <v>17878</v>
+        <v>43685</v>
       </c>
       <c r="W99" s="20" t="n">
-        <v>17617</v>
+        <v>42555</v>
       </c>
       <c r="X99" s="20" t="n">
-        <v>19580</v>
+        <v>56146</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="18" t="inlineStr">
         <is>
-          <t>(이 중 예금 이자)</t>
+          <t>자금조달비용</t>
         </is>
       </c>
       <c r="C100" s="20" t="n">
-        <v>2749</v>
+        <v>15127</v>
       </c>
       <c r="D100" s="20" t="n">
-        <v>3136</v>
+        <v>15851</v>
       </c>
       <c r="E100" s="20" t="n">
-        <v>3648</v>
+        <v>17878</v>
       </c>
       <c r="F100" s="20" t="n">
-        <v>3676</v>
+        <v>19294</v>
       </c>
       <c r="G100" s="20" t="n">
-        <v>3593</v>
+        <v>17431</v>
       </c>
       <c r="H100" s="20" t="n">
-        <v>5297</v>
+        <v>20338</v>
       </c>
       <c r="I100" s="20" t="n">
-        <v>5564</v>
+        <v>17617</v>
       </c>
       <c r="J100" s="20" t="n">
-        <v>7223</v>
+        <v>18308</v>
       </c>
       <c r="K100" s="20" t="n">
-        <v>8327</v>
+        <v>19041</v>
       </c>
       <c r="L100" s="20" t="n">
-        <v>9148</v>
+        <v>19466</v>
       </c>
       <c r="M100" s="20" t="n">
-        <v>9545</v>
+        <v>19580</v>
       </c>
       <c r="N100" s="20" t="n">
-        <v>9551</v>
+        <v>19922</v>
       </c>
       <c r="U100" s="20" t="n">
-        <v>1706</v>
+        <v>10769</v>
       </c>
       <c r="V100" s="20" t="n">
-        <v>3648</v>
+        <v>17878</v>
       </c>
       <c r="W100" s="20" t="n">
-        <v>5564</v>
+        <v>17617</v>
       </c>
       <c r="X100" s="20" t="n">
-        <v>9545</v>
+        <v>19580</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="18" t="inlineStr">
         <is>
-          <t>용역거래 비용</t>
+          <t>(이 중 예금 이자)</t>
         </is>
       </c>
       <c r="C101" s="20" t="n">
-        <v>1090</v>
+        <v>2749</v>
       </c>
       <c r="D101" s="20" t="n">
-        <v>1102</v>
+        <v>3136</v>
       </c>
       <c r="E101" s="20" t="n">
-        <v>1109</v>
+        <v>3648</v>
       </c>
       <c r="F101" s="20" t="n">
-        <v>367</v>
+        <v>3676</v>
       </c>
       <c r="G101" s="20" t="n">
-        <v>1150</v>
+        <v>3593</v>
       </c>
       <c r="H101" s="20" t="n">
-        <v>1213</v>
+        <v>5297</v>
       </c>
       <c r="I101" s="20" t="n">
-        <v>1190</v>
+        <v>5564</v>
       </c>
       <c r="J101" s="20" t="n">
-        <v>350</v>
+        <v>7223</v>
       </c>
       <c r="K101" s="20" t="n">
-        <v>1273</v>
+        <v>8327</v>
       </c>
       <c r="L101" s="20" t="n">
-        <v>1357</v>
+        <v>9148</v>
       </c>
       <c r="M101" s="20" t="n">
-        <v>1337</v>
+        <v>9545</v>
       </c>
       <c r="N101" s="20" t="n">
-        <v>646</v>
+        <v>9551</v>
       </c>
       <c r="U101" s="20" t="n">
-        <v>1043</v>
+        <v>1706</v>
       </c>
       <c r="V101" s="20" t="n">
-        <v>1109</v>
+        <v>3648</v>
       </c>
       <c r="W101" s="20" t="n">
-        <v>1190</v>
+        <v>5564</v>
       </c>
       <c r="X101" s="20" t="n">
-        <v>1337</v>
+        <v>9545</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="18" t="inlineStr">
         <is>
-          <t>기타 업무비용</t>
+          <t>용역거래 비용</t>
         </is>
       </c>
       <c r="C102" s="20" t="n">
-        <v>5274</v>
+        <v>1090</v>
       </c>
       <c r="D102" s="20" t="n">
-        <v>4143</v>
+        <v>1102</v>
       </c>
       <c r="E102" s="20" t="n">
-        <v>3293</v>
+        <v>1109</v>
       </c>
       <c r="F102" s="20" t="n">
-        <v>3806</v>
+        <v>367</v>
       </c>
       <c r="G102" s="20" t="n">
-        <v>6282</v>
+        <v>1150</v>
       </c>
       <c r="H102" s="20" t="n">
-        <v>4260</v>
+        <v>1213</v>
       </c>
       <c r="I102" s="20" t="n">
-        <v>4897</v>
+        <v>1190</v>
       </c>
       <c r="J102" s="20" t="n">
-        <v>6278</v>
+        <v>350</v>
       </c>
       <c r="K102" s="20" t="n">
-        <v>5952</v>
+        <v>1273</v>
       </c>
       <c r="L102" s="20" t="n">
-        <v>8988</v>
+        <v>1357</v>
       </c>
       <c r="M102" s="20" t="n">
-        <v>13385</v>
+        <v>1337</v>
       </c>
       <c r="N102" s="20" t="n">
-        <v>49191</v>
+        <v>646</v>
       </c>
       <c r="U102" s="20" t="n">
-        <v>8895</v>
+        <v>1043</v>
       </c>
       <c r="V102" s="20" t="n">
-        <v>3293</v>
+        <v>1109</v>
       </c>
       <c r="W102" s="20" t="n">
-        <v>4897</v>
+        <v>1190</v>
       </c>
       <c r="X102" s="20" t="n">
-        <v>13385</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="18" t="inlineStr">
         <is>
-          <t>General And Administrative Expenses OEBNK</t>
+          <t>기타 업무비용</t>
         </is>
       </c>
       <c r="C103" s="20" t="n">
-        <v>14204</v>
+        <v>5274</v>
       </c>
       <c r="D103" s="20" t="n">
-        <v>14173</v>
+        <v>4143</v>
       </c>
       <c r="E103" s="20" t="n">
-        <v>15235</v>
+        <v>3293</v>
       </c>
       <c r="F103" s="20" t="n">
-        <v>14324</v>
+        <v>3806</v>
       </c>
       <c r="G103" s="20" t="n">
-        <v>14553</v>
+        <v>6282</v>
       </c>
       <c r="H103" s="20" t="n">
-        <v>15119</v>
+        <v>4260</v>
       </c>
       <c r="I103" s="20" t="n">
-        <v>15530</v>
+        <v>4897</v>
       </c>
       <c r="J103" s="20" t="n">
-        <v>16365</v>
+        <v>6278</v>
       </c>
       <c r="K103" s="20" t="n">
-        <v>15955</v>
+        <v>5952</v>
       </c>
       <c r="L103" s="20" t="n">
-        <v>16829</v>
+        <v>8988</v>
       </c>
       <c r="M103" s="20" t="n">
-        <v>17416</v>
+        <v>13385</v>
       </c>
       <c r="N103" s="20" t="n">
-        <v>17653</v>
+        <v>49191</v>
       </c>
       <c r="U103" s="20" t="n">
-        <v>14144</v>
+        <v>8895</v>
       </c>
       <c r="V103" s="20" t="n">
-        <v>15235</v>
+        <v>3293</v>
       </c>
       <c r="W103" s="20" t="n">
-        <v>15530</v>
+        <v>4897</v>
       </c>
       <c r="X103" s="20" t="n">
-        <v>17416</v>
+        <v>13385</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="18" t="inlineStr">
         <is>
+          <t>General And Administrative Expenses OEBNK</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="n">
+        <v>14204</v>
+      </c>
+      <c r="D104" s="20" t="n">
+        <v>14173</v>
+      </c>
+      <c r="E104" s="20" t="n">
+        <v>15235</v>
+      </c>
+      <c r="F104" s="20" t="n">
+        <v>14324</v>
+      </c>
+      <c r="G104" s="20" t="n">
+        <v>14553</v>
+      </c>
+      <c r="H104" s="20" t="n">
+        <v>15119</v>
+      </c>
+      <c r="I104" s="20" t="n">
+        <v>15530</v>
+      </c>
+      <c r="J104" s="20" t="n">
+        <v>16365</v>
+      </c>
+      <c r="K104" s="20" t="n">
+        <v>15955</v>
+      </c>
+      <c r="L104" s="20" t="n">
+        <v>16829</v>
+      </c>
+      <c r="M104" s="20" t="n">
+        <v>17416</v>
+      </c>
+      <c r="N104" s="20" t="n">
+        <v>17653</v>
+      </c>
+      <c r="U104" s="20" t="n">
+        <v>14144</v>
+      </c>
+      <c r="V104" s="20" t="n">
+        <v>15235</v>
+      </c>
+      <c r="W104" s="20" t="n">
+        <v>15530</v>
+      </c>
+      <c r="X104" s="20" t="n">
+        <v>17416</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="18" t="inlineStr">
+        <is>
           <t>기타 경상비용</t>
         </is>
       </c>
-      <c r="C104" s="20" t="n">
+      <c r="C105" s="20" t="n">
         <v>4045</v>
       </c>
-      <c r="D104" s="20" t="n">
+      <c r="D105" s="20" t="n">
         <v>1198</v>
       </c>
-      <c r="E104" s="20" t="n">
+      <c r="E105" s="20" t="n">
         <v>6169</v>
       </c>
-      <c r="F104" s="20" t="n">
+      <c r="F105" s="20" t="n">
         <v>913</v>
       </c>
-      <c r="G104" s="20" t="n">
+      <c r="G105" s="20" t="n">
         <v>3814</v>
       </c>
-      <c r="H104" s="20" t="n">
+      <c r="H105" s="20" t="n">
         <v>8004</v>
       </c>
-      <c r="I104" s="20" t="n">
+      <c r="I105" s="20" t="n">
         <v>3320</v>
       </c>
-      <c r="J104" s="20" t="n">
+      <c r="J105" s="20" t="n">
         <v>318</v>
       </c>
-      <c r="K104" s="20" t="n">
+      <c r="K105" s="20" t="n">
         <v>5471</v>
       </c>
-      <c r="L104" s="20" t="n">
+      <c r="L105" s="20" t="n">
         <v>938</v>
       </c>
-      <c r="M104" s="20" t="n">
+      <c r="M105" s="20" t="n">
         <v>4426</v>
       </c>
-      <c r="N104" s="20" t="n">
+      <c r="N105" s="20" t="n">
         <v>1957</v>
       </c>
-      <c r="U104" s="20" t="n">
+      <c r="U105" s="20" t="n">
         <v>4723</v>
       </c>
-      <c r="V104" s="20" t="n">
+      <c r="V105" s="20" t="n">
         <v>6169</v>
       </c>
-      <c r="W104" s="20" t="n">
+      <c r="W105" s="20" t="n">
         <v>3320</v>
       </c>
-      <c r="X104" s="20" t="n">
+      <c r="X105" s="20" t="n">
         <v>4426</v>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="9" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="9" t="inlineStr">
         <is>
           <t>경상이익</t>
         </is>
       </c>
-      <c r="C105" s="12" t="n">
+      <c r="C106" s="12" t="n">
         <v>4761</v>
       </c>
-      <c r="D105" s="12" t="n">
+      <c r="D106" s="12" t="n">
         <v>11283</v>
       </c>
-      <c r="E105" s="12" t="n">
+      <c r="E106" s="12" t="n">
         <v>4872</v>
       </c>
-      <c r="F105" s="12" t="n">
+      <c r="F106" s="12" t="n">
         <v>13728</v>
       </c>
-      <c r="G105" s="12" t="n">
+      <c r="G106" s="12" t="n">
         <v>7256</v>
       </c>
-      <c r="H105" s="12" t="n">
+      <c r="H106" s="12" t="n">
         <v>8226</v>
       </c>
-      <c r="I105" s="12" t="n">
+      <c r="I106" s="12" t="n">
         <v>9098</v>
       </c>
-      <c r="J105" s="12" t="n">
+      <c r="J106" s="12" t="n">
         <v>14984</v>
       </c>
-      <c r="K105" s="12" t="n">
+      <c r="K106" s="12" t="n">
         <v>10217</v>
       </c>
-      <c r="L105" s="12" t="n">
+      <c r="L106" s="12" t="n">
         <v>20295</v>
       </c>
-      <c r="M105" s="12" t="n">
+      <c r="M106" s="12" t="n">
         <v>10542</v>
       </c>
-      <c r="N105" s="12" t="n">
+      <c r="N106" s="12" t="n">
         <v>20269</v>
       </c>
-      <c r="U105" s="12" t="n">
+      <c r="U106" s="12" t="n">
         <v>4142</v>
       </c>
-      <c r="V105" s="12" t="n">
+      <c r="V106" s="12" t="n">
         <v>4872</v>
       </c>
-      <c r="W105" s="12" t="n">
+      <c r="W106" s="12" t="n">
         <v>9098</v>
       </c>
-      <c r="X105" s="12" t="n">
+      <c r="X106" s="12" t="n">
         <v>10542</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="18" t="inlineStr">
-        <is>
-          <t>특별이익</t>
-        </is>
-      </c>
-      <c r="C106" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="D106" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F106" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G106" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H106" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I106" s="20" t="n">
-        <v>111</v>
-      </c>
-      <c r="J106" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="N106" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="U106" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V106" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="W106" s="20" t="n">
-        <v>111</v>
-      </c>
-      <c r="X106" s="20" t="n">
-        <v>13</v>
-      </c>
-    </row>
     <row r="107">
-      <c r="A107" s="18" t="inlineStr">
-        <is>
-          <t>고정자산 처분이익</t>
-        </is>
-      </c>
-      <c r="C107" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="D107" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="F107" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="G107" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H107" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I107" s="20" t="n">
-        <v>111</v>
-      </c>
-      <c r="J107" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="N107" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="U107" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V107" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="W107" s="20" t="n">
-        <v>111</v>
-      </c>
-      <c r="X107" s="20" t="n">
-        <v>13</v>
+      <c r="A107" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G107" s="15">
+        <f>IF(OR(G106="",C106=""),"",IF(C106&lt;=0,"",IFERROR(G106/C106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H107" s="15">
+        <f>IF(OR(H106="",D106=""),"",IF(D106&lt;=0,"",IFERROR(H106/D106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I107" s="15">
+        <f>IF(OR(I106="",E106=""),"",IF(E106&lt;=0,"",IFERROR(I106/E106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J107" s="15">
+        <f>IF(OR(J106="",F106=""),"",IF(F106&lt;=0,"",IFERROR(J106/F106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K107" s="15">
+        <f>IF(OR(K106="",G106=""),"",IF(G106&lt;=0,"",IFERROR(K106/G106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L107" s="15">
+        <f>IF(OR(L106="",H106=""),"",IF(H106&lt;=0,"",IFERROR(L106/H106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M107" s="15">
+        <f>IF(OR(M106="",I106=""),"",IF(I106&lt;=0,"",IFERROR(M106/I106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N107" s="15">
+        <f>IF(OR(N106="",J106=""),"",IF(J106&lt;=0,"",IFERROR(N106/J106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U107" s="15">
+        <f>IF(OR(U106="",T106=""),"",IF(T106&lt;=0,"",IFERROR(U106/T106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V107" s="15">
+        <f>IF(OR(V106="",U106=""),"",IF(U106&lt;=0,"",IFERROR(V106/U106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W107" s="15">
+        <f>IF(OR(W106="",V106=""),"",IF(V106&lt;=0,"",IFERROR(W106/V106-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X107" s="15">
+        <f>IF(OR(X106="",W106=""),"",IF(W106&lt;=0,"",IFERROR(X106/W106-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="18" t="inlineStr">
         <is>
-          <t>특별손실</t>
+          <t>특별이익</t>
         </is>
       </c>
       <c r="C108" s="20" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="D108" s="20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="E108" s="20" t="n">
-        <v>182</v>
+        <v>15</v>
       </c>
       <c r="F108" s="20" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="G108" s="20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H108" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I108" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="J108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="N108" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="I108" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="J108" s="20" t="n">
-        <v>254</v>
-      </c>
-      <c r="K108" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L108" s="20" t="n">
+      <c r="U108" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="V108" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="M108" s="20" t="n">
-        <v>110</v>
-      </c>
-      <c r="N108" s="20" t="n">
-        <v>67</v>
-      </c>
-      <c r="U108" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="V108" s="20" t="n">
-        <v>182</v>
-      </c>
       <c r="W108" s="20" t="n">
-        <v>58</v>
+        <v>111</v>
       </c>
       <c r="X108" s="20" t="n">
-        <v>110</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="18" t="inlineStr">
         <is>
-          <t>고정자산 처분손실</t>
+          <t>고정자산 처분이익</t>
         </is>
       </c>
       <c r="C109" s="20" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D109" s="20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E109" s="20" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="F109" s="20" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G109" s="20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H109" s="20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I109" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="J109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="J109" s="20" t="n">
-        <v>229</v>
-      </c>
-      <c r="K109" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L109" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="M109" s="20" t="n">
-        <v>102</v>
-      </c>
       <c r="N109" s="20" t="n">
-        <v>67</v>
+        <v>21</v>
       </c>
       <c r="U109" s="20" t="n">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="V109" s="20" t="n">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="W109" s="20" t="n">
+        <v>111</v>
+      </c>
+      <c r="X109" s="20" t="n">
         <v>13</v>
-      </c>
-      <c r="X109" s="20" t="n">
-        <v>102</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>손상차손</t>
+          <t>특별손실</t>
         </is>
       </c>
       <c r="C110" s="20" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D110" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="E110" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="F110" s="20" t="n">
+        <v>56</v>
+      </c>
+      <c r="G110" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H110" s="20" t="n">
+        <v>21</v>
+      </c>
+      <c r="I110" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="J110" s="20" t="n">
+        <v>254</v>
+      </c>
+      <c r="K110" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L110" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="M110" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="N110" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="U110" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="V110" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="W110" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="X110" s="20" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="18" t="inlineStr">
+        <is>
+          <t>고정자산 처분손실</t>
+        </is>
+      </c>
+      <c r="C111" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="D111" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E111" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="F111" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="G111" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="H111" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="I111" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="J111" s="20" t="n">
+        <v>229</v>
+      </c>
+      <c r="K111" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="L111" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="E110" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="F110" s="20" t="n">
-        <v>43</v>
-      </c>
-      <c r="G110" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="I110" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="J110" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="K110" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="N110" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V110" s="20" t="n">
-        <v>47</v>
-      </c>
-      <c r="W110" s="20" t="n">
-        <v>46</v>
-      </c>
-      <c r="X110" s="20" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C111" s="12" t="n">
-        <v>4724</v>
-      </c>
-      <c r="D111" s="12" t="n">
-        <v>11254</v>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v>4704</v>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>13674</v>
-      </c>
-      <c r="G111" s="12" t="n">
-        <v>7246</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>8211</v>
-      </c>
-      <c r="I111" s="12" t="n">
-        <v>9151</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>14729</v>
-      </c>
-      <c r="K111" s="12" t="n">
-        <v>10212</v>
-      </c>
-      <c r="L111" s="12" t="n">
-        <v>20279</v>
-      </c>
-      <c r="M111" s="12" t="n">
-        <v>10446</v>
-      </c>
-      <c r="N111" s="12" t="n">
-        <v>20222</v>
-      </c>
-      <c r="U111" s="12" t="n">
-        <v>4091</v>
-      </c>
-      <c r="V111" s="12" t="n">
-        <v>4704</v>
-      </c>
-      <c r="W111" s="12" t="n">
-        <v>9151</v>
-      </c>
-      <c r="X111" s="12" t="n">
-        <v>10446</v>
+      <c r="M111" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="N111" s="20" t="n">
+        <v>67</v>
+      </c>
+      <c r="U111" s="20" t="n">
+        <v>51</v>
+      </c>
+      <c r="V111" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="W111" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="X111" s="20" t="n">
+        <v>102</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="18" t="inlineStr">
         <is>
-          <t>법인세 등</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="C112" s="20" t="n">
-        <v>1486</v>
+        <v>28</v>
       </c>
       <c r="D112" s="20" t="n">
-        <v>3317</v>
+        <v>16</v>
       </c>
       <c r="E112" s="20" t="n">
-        <v>1688</v>
+        <v>47</v>
       </c>
       <c r="F112" s="20" t="n">
-        <v>4276</v>
+        <v>43</v>
       </c>
       <c r="G112" s="20" t="n">
-        <v>2024</v>
+        <v>0</v>
       </c>
       <c r="H112" s="20" t="n">
-        <v>2448</v>
+        <v>11</v>
       </c>
       <c r="I112" s="20" t="n">
-        <v>2100</v>
+        <v>46</v>
       </c>
       <c r="J112" s="20" t="n">
-        <v>4841</v>
+        <v>24</v>
       </c>
       <c r="K112" s="20" t="n">
-        <v>2731</v>
+        <v>0</v>
       </c>
       <c r="L112" s="20" t="n">
-        <v>6071</v>
+        <v>0</v>
       </c>
       <c r="M112" s="20" t="n">
-        <v>2317</v>
+        <v>6</v>
       </c>
       <c r="N112" s="20" t="n">
-        <v>6342</v>
+        <v>0</v>
       </c>
       <c r="U112" s="20" t="n">
-        <v>1473</v>
+        <v>1</v>
       </c>
       <c r="V112" s="20" t="n">
-        <v>1688</v>
+        <v>47</v>
       </c>
       <c r="W112" s="20" t="n">
-        <v>2100</v>
+        <v>46</v>
       </c>
       <c r="X112" s="20" t="n">
-        <v>2317</v>
+        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>순이익</t>
+          <t>법인세차감전 순이익</t>
         </is>
       </c>
       <c r="C113" s="12" t="n">
-        <v>3239</v>
+        <v>4724</v>
       </c>
       <c r="D113" s="12" t="n">
-        <v>7937</v>
+        <v>11254</v>
       </c>
       <c r="E113" s="12" t="n">
-        <v>3016</v>
+        <v>4704</v>
       </c>
       <c r="F113" s="12" t="n">
-        <v>9398</v>
+        <v>13674</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>5221</v>
+        <v>7246</v>
       </c>
       <c r="H113" s="12" t="n">
-        <v>5764</v>
+        <v>8211</v>
       </c>
       <c r="I113" s="12" t="n">
-        <v>7051</v>
+        <v>9151</v>
       </c>
       <c r="J113" s="12" t="n">
-        <v>9887</v>
+        <v>14729</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>7481</v>
+        <v>10212</v>
       </c>
       <c r="L113" s="12" t="n">
-        <v>14209</v>
+        <v>20279</v>
       </c>
       <c r="M113" s="12" t="n">
-        <v>8128</v>
+        <v>10446</v>
       </c>
       <c r="N113" s="12" t="n">
-        <v>13880</v>
+        <v>20222</v>
       </c>
       <c r="U113" s="12" t="n">
-        <v>2618</v>
+        <v>4091</v>
       </c>
       <c r="V113" s="12" t="n">
-        <v>3016</v>
+        <v>4704</v>
       </c>
       <c r="W113" s="12" t="n">
-        <v>7051</v>
+        <v>9151</v>
       </c>
       <c r="X113" s="12" t="n">
-        <v>8128</v>
+        <v>10446</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>비지배주주 순이익</t>
-        </is>
-      </c>
-      <c r="C114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W114" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X114" s="12" t="n">
-        <v>0</v>
+      <c r="A114" s="18" t="inlineStr">
+        <is>
+          <t>법인세 등</t>
+        </is>
+      </c>
+      <c r="C114" s="20" t="n">
+        <v>1486</v>
+      </c>
+      <c r="D114" s="20" t="n">
+        <v>3317</v>
+      </c>
+      <c r="E114" s="20" t="n">
+        <v>1688</v>
+      </c>
+      <c r="F114" s="20" t="n">
+        <v>4276</v>
+      </c>
+      <c r="G114" s="20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H114" s="20" t="n">
+        <v>2448</v>
+      </c>
+      <c r="I114" s="20" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J114" s="20" t="n">
+        <v>4841</v>
+      </c>
+      <c r="K114" s="20" t="n">
+        <v>2731</v>
+      </c>
+      <c r="L114" s="20" t="n">
+        <v>6071</v>
+      </c>
+      <c r="M114" s="20" t="n">
+        <v>2317</v>
+      </c>
+      <c r="N114" s="20" t="n">
+        <v>6342</v>
+      </c>
+      <c r="U114" s="20" t="n">
+        <v>1473</v>
+      </c>
+      <c r="V114" s="20" t="n">
+        <v>1688</v>
+      </c>
+      <c r="W114" s="20" t="n">
+        <v>2100</v>
+      </c>
+      <c r="X114" s="20" t="n">
+        <v>2317</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>지배주주 순이익</t>
+          <t>순이익</t>
         </is>
       </c>
       <c r="C115" s="12" t="n">
@@ -8021,1604 +8038,1704 @@
         <v>8128</v>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G116" s="15">
+        <f>IF(OR(G115="",C115=""),"",IF(C115&lt;=0,"",IFERROR(G115/C115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H116" s="15">
+        <f>IF(OR(H115="",D115=""),"",IF(D115&lt;=0,"",IFERROR(H115/D115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I116" s="15">
+        <f>IF(OR(I115="",E115=""),"",IF(E115&lt;=0,"",IFERROR(I115/E115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J116" s="15">
+        <f>IF(OR(J115="",F115=""),"",IF(F115&lt;=0,"",IFERROR(J115/F115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K116" s="15">
+        <f>IF(OR(K115="",G115=""),"",IF(G115&lt;=0,"",IFERROR(K115/G115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L116" s="15">
+        <f>IF(OR(L115="",H115=""),"",IF(H115&lt;=0,"",IFERROR(L115/H115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M116" s="15">
+        <f>IF(OR(M115="",I115=""),"",IF(I115&lt;=0,"",IFERROR(M115/I115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N116" s="15">
+        <f>IF(OR(N115="",J115=""),"",IF(J115&lt;=0,"",IFERROR(N115/J115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U116" s="15">
+        <f>IF(OR(U115="",T115=""),"",IF(T115&lt;=0,"",IFERROR(U115/T115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V116" s="15">
+        <f>IF(OR(V115="",U115=""),"",IF(U115&lt;=0,"",IFERROR(V115/U115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W116" s="15">
+        <f>IF(OR(W115="",V115=""),"",IF(V115&lt;=0,"",IFERROR(W115/V115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X116" s="15">
+        <f>IF(OR(X115="",W115=""),"",IF(W115&lt;=0,"",IFERROR(X115/W115-1,"")))</f>
+        <v/>
+      </c>
+    </row>
     <row r="117">
-      <c r="A117" s="16" t="inlineStr">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>비지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X117" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>지배주주 순이익</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="n">
+        <v>3239</v>
+      </c>
+      <c r="D118" s="12" t="n">
+        <v>7937</v>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>3016</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>9398</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>5221</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>5764</v>
+      </c>
+      <c r="I118" s="12" t="n">
+        <v>7051</v>
+      </c>
+      <c r="J118" s="12" t="n">
+        <v>9887</v>
+      </c>
+      <c r="K118" s="12" t="n">
+        <v>7481</v>
+      </c>
+      <c r="L118" s="12" t="n">
+        <v>14209</v>
+      </c>
+      <c r="M118" s="12" t="n">
+        <v>8128</v>
+      </c>
+      <c r="N118" s="12" t="n">
+        <v>13880</v>
+      </c>
+      <c r="U118" s="12" t="n">
+        <v>2618</v>
+      </c>
+      <c r="V118" s="12" t="n">
+        <v>3016</v>
+      </c>
+      <c r="W118" s="12" t="n">
+        <v>7051</v>
+      </c>
+      <c r="X118" s="12" t="n">
+        <v>8128</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G119" s="15">
+        <f>IF(OR(G118="",C118=""),"",IF(C118&lt;=0,"",IFERROR(G118/C118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H119" s="15">
+        <f>IF(OR(H118="",D118=""),"",IF(D118&lt;=0,"",IFERROR(H118/D118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I119" s="15">
+        <f>IF(OR(I118="",E118=""),"",IF(E118&lt;=0,"",IFERROR(I118/E118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J119" s="15">
+        <f>IF(OR(J118="",F118=""),"",IF(F118&lt;=0,"",IFERROR(J118/F118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K119" s="15">
+        <f>IF(OR(K118="",G118=""),"",IF(G118&lt;=0,"",IFERROR(K118/G118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L119" s="15">
+        <f>IF(OR(L118="",H118=""),"",IF(H118&lt;=0,"",IFERROR(L118/H118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M119" s="15">
+        <f>IF(OR(M118="",I118=""),"",IF(I118&lt;=0,"",IFERROR(M118/I118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N119" s="15">
+        <f>IF(OR(N118="",J118=""),"",IF(J118&lt;=0,"",IFERROR(N118/J118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U119" s="15">
+        <f>IF(OR(U118="",T118=""),"",IF(T118&lt;=0,"",IFERROR(U118/T118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V119" s="15">
+        <f>IF(OR(V118="",U118=""),"",IF(U118&lt;=0,"",IFERROR(V118/U118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W119" s="15">
+        <f>IF(OR(W118="",V118=""),"",IF(V118&lt;=0,"",IFERROR(W118/V118-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X119" s="15">
+        <f>IF(OR(X118="",W118=""),"",IF(W118&lt;=0,"",IFERROR(X118/W118-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="16" t="inlineStr">
         <is>
           <t>포괄손익 · 전 항목</t>
         </is>
       </c>
-      <c r="B117" s="42" t="inlineStr">
+      <c r="B121" s="42" t="inlineStr">
         <is>
           <t>분기 = 3개월 단독</t>
         </is>
       </c>
-      <c r="C117" s="16" t="n"/>
-      <c r="D117" s="16" t="n"/>
-      <c r="E117" s="16" t="n"/>
-      <c r="F117" s="16" t="n"/>
-      <c r="G117" s="16" t="n"/>
-      <c r="H117" s="16" t="n"/>
-      <c r="I117" s="16" t="n"/>
-      <c r="J117" s="16" t="n"/>
-      <c r="K117" s="16" t="n"/>
-      <c r="L117" s="16" t="n"/>
-      <c r="M117" s="16" t="n"/>
-      <c r="N117" s="16" t="n"/>
-      <c r="O117" s="16" t="n"/>
-      <c r="P117" s="16" t="n"/>
-      <c r="Q117" s="16" t="n"/>
-      <c r="R117" s="16" t="n"/>
-      <c r="S117" s="16" t="n"/>
-      <c r="T117" s="16" t="n"/>
-      <c r="U117" s="16" t="n"/>
-      <c r="V117" s="16" t="n"/>
-      <c r="W117" s="16" t="n"/>
-      <c r="X117" s="16" t="n"/>
-      <c r="Y117" s="16" t="n"/>
-      <c r="Z117" s="16" t="n"/>
-      <c r="AA117" s="16" t="n"/>
-      <c r="AB117" s="16" t="n"/>
-      <c r="AC117" s="16" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="C121" s="16" t="n"/>
+      <c r="D121" s="16" t="n"/>
+      <c r="E121" s="16" t="n"/>
+      <c r="F121" s="16" t="n"/>
+      <c r="G121" s="16" t="n"/>
+      <c r="H121" s="16" t="n"/>
+      <c r="I121" s="16" t="n"/>
+      <c r="J121" s="16" t="n"/>
+      <c r="K121" s="16" t="n"/>
+      <c r="L121" s="16" t="n"/>
+      <c r="M121" s="16" t="n"/>
+      <c r="N121" s="16" t="n"/>
+      <c r="O121" s="16" t="n"/>
+      <c r="P121" s="16" t="n"/>
+      <c r="Q121" s="16" t="n"/>
+      <c r="R121" s="16" t="n"/>
+      <c r="S121" s="16" t="n"/>
+      <c r="T121" s="16" t="n"/>
+      <c r="U121" s="16" t="n"/>
+      <c r="V121" s="16" t="n"/>
+      <c r="W121" s="16" t="n"/>
+      <c r="X121" s="16" t="n"/>
+      <c r="Y121" s="16" t="n"/>
+      <c r="Z121" s="16" t="n"/>
+      <c r="AA121" s="16" t="n"/>
+      <c r="AB121" s="16" t="n"/>
+      <c r="AC121" s="16" t="n"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B122" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C122" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D122" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E122" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F122" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G122" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="H122" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I122" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J122" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr">
+      <c r="K122" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L118" s="5" t="inlineStr">
+      <c r="L122" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M118" s="5" t="inlineStr">
+      <c r="M122" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N118" s="5" t="inlineStr">
+      <c r="N122" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O118" s="5" t="inlineStr">
+      <c r="O122" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P118" s="5" t="inlineStr">
+      <c r="P122" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q118" s="5" t="inlineStr">
+      <c r="Q122" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R118" s="5" t="inlineStr">
+      <c r="R122" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S118" s="5" t="inlineStr">
+      <c r="S122" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T118" s="5" t="inlineStr">
+      <c r="T122" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U118" s="5" t="inlineStr">
+      <c r="U122" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V118" s="5" t="inlineStr">
+      <c r="V122" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W118" s="5" t="inlineStr">
+      <c r="W122" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X118" s="5" t="inlineStr">
+      <c r="X122" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y118" s="5" t="inlineStr">
+      <c r="Y122" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z118" s="5" t="inlineStr">
+      <c r="Z122" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA118" s="5" t="inlineStr">
+      <c r="AA122" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB118" s="5" t="inlineStr">
+      <c r="AB122" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC118" s="5" t="inlineStr">
+      <c r="AC122" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C119" s="12" t="n">
+      <c r="C123" s="12" t="n">
         <v>3239</v>
       </c>
-      <c r="D119" s="12" t="n">
+      <c r="D123" s="12" t="n">
         <v>7937</v>
       </c>
-      <c r="E119" s="12" t="n">
+      <c r="E123" s="12" t="n">
         <v>3016</v>
       </c>
-      <c r="F119" s="12" t="n">
+      <c r="F123" s="12" t="n">
         <v>9398</v>
       </c>
-      <c r="G119" s="12" t="n">
+      <c r="G123" s="12" t="n">
         <v>5221</v>
       </c>
-      <c r="H119" s="12" t="n">
+      <c r="H123" s="12" t="n">
         <v>5764</v>
       </c>
-      <c r="I119" s="12" t="n">
+      <c r="I123" s="12" t="n">
         <v>7051</v>
       </c>
-      <c r="J119" s="12" t="n">
+      <c r="J123" s="12" t="n">
         <v>9887</v>
       </c>
-      <c r="K119" s="12" t="n">
+      <c r="K123" s="12" t="n">
         <v>7481</v>
       </c>
-      <c r="L119" s="12" t="n">
+      <c r="L123" s="12" t="n">
         <v>14209</v>
       </c>
-      <c r="M119" s="12" t="n">
+      <c r="M123" s="12" t="n">
         <v>8128</v>
       </c>
-      <c r="N119" s="12" t="n">
+      <c r="N123" s="12" t="n">
         <v>13880</v>
       </c>
-      <c r="U119" s="12" t="n">
+      <c r="U123" s="12" t="n">
         <v>2618</v>
       </c>
-      <c r="V119" s="12" t="n">
+      <c r="V123" s="12" t="n">
         <v>3016</v>
       </c>
-      <c r="W119" s="12" t="n">
+      <c r="W123" s="12" t="n">
         <v>7051</v>
       </c>
-      <c r="X119" s="12" t="n">
+      <c r="X123" s="12" t="n">
         <v>8128</v>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="18" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="18" t="inlineStr">
         <is>
           <t>기타포괄손익</t>
         </is>
       </c>
-      <c r="C120" s="20" t="n">
+      <c r="C124" s="20" t="n">
         <v>-10012</v>
       </c>
-      <c r="D120" s="20" t="n">
+      <c r="D124" s="20" t="n">
         <v>10965</v>
       </c>
-      <c r="E120" s="20" t="n">
+      <c r="E124" s="20" t="n">
         <v>24456</v>
       </c>
-      <c r="F120" s="20" t="n">
+      <c r="F124" s="20" t="n">
         <v>-12860</v>
       </c>
-      <c r="G120" s="20" t="n">
+      <c r="G124" s="20" t="n">
         <v>-1421</v>
       </c>
-      <c r="H120" s="20" t="n">
+      <c r="H124" s="20" t="n">
         <v>-7977</v>
       </c>
-      <c r="I120" s="20" t="n">
+      <c r="I124" s="20" t="n">
         <v>-28477</v>
       </c>
-      <c r="J120" s="20" t="n">
+      <c r="J124" s="20" t="n">
         <v>20740</v>
       </c>
-      <c r="K120" s="20" t="n">
+      <c r="K124" s="20" t="n">
         <v>22140</v>
       </c>
-      <c r="L120" s="20" t="n">
+      <c r="L124" s="20" t="n">
         <v>9010</v>
       </c>
-      <c r="M120" s="20" t="n">
+      <c r="M124" s="20" t="n">
         <v>1936</v>
       </c>
-      <c r="N120" s="20" t="n">
+      <c r="N124" s="20" t="n">
         <v>48278</v>
       </c>
-      <c r="U120" s="20" t="n">
+      <c r="U124" s="20" t="n">
         <v>12006</v>
       </c>
-      <c r="V120" s="20" t="n">
+      <c r="V124" s="20" t="n">
         <v>24456</v>
       </c>
-      <c r="W120" s="20" t="n">
+      <c r="W124" s="20" t="n">
         <v>-28477</v>
       </c>
-      <c r="X120" s="20" t="n">
+      <c r="X124" s="20" t="n">
         <v>1936</v>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="18" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="18" t="inlineStr">
         <is>
           <t>기타유가증권 평가차액</t>
         </is>
       </c>
-      <c r="C121" s="20" t="n">
+      <c r="C125" s="20" t="n">
         <v>-26947</v>
       </c>
-      <c r="D121" s="20" t="n">
+      <c r="D125" s="20" t="n">
         <v>22147</v>
       </c>
-      <c r="E121" s="20" t="n">
+      <c r="E125" s="20" t="n">
         <v>14747</v>
       </c>
-      <c r="F121" s="20" t="n">
+      <c r="F125" s="20" t="n">
         <v>-22890</v>
       </c>
-      <c r="G121" s="20" t="n">
+      <c r="G125" s="20" t="n">
         <v>14927</v>
       </c>
-      <c r="H121" s="20" t="n">
+      <c r="H125" s="20" t="n">
         <v>-24974</v>
       </c>
-      <c r="I121" s="20" t="n">
+      <c r="I125" s="20" t="n">
         <v>-31353</v>
       </c>
-      <c r="J121" s="20" t="n">
+      <c r="J125" s="20" t="n">
         <v>19140</v>
       </c>
-      <c r="K121" s="20" t="n">
+      <c r="K125" s="20" t="n">
         <v>11620</v>
       </c>
-      <c r="L121" s="20" t="n">
+      <c r="L125" s="20" t="n">
         <v>-8801</v>
       </c>
-      <c r="M121" s="20" t="n">
+      <c r="M125" s="20" t="n">
         <v>-15397</v>
       </c>
-      <c r="N121" s="20" t="n">
+      <c r="N125" s="20" t="n">
         <v>46301</v>
       </c>
-      <c r="U121" s="20" t="n">
+      <c r="U125" s="20" t="n">
         <v>25440</v>
       </c>
-      <c r="V121" s="20" t="n">
+      <c r="V125" s="20" t="n">
         <v>14747</v>
       </c>
-      <c r="W121" s="20" t="n">
+      <c r="W125" s="20" t="n">
         <v>-31353</v>
       </c>
-      <c r="X121" s="20" t="n">
+      <c r="X125" s="20" t="n">
         <v>-15397</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="18" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="18" t="inlineStr">
         <is>
           <t>이연헤지손익</t>
         </is>
       </c>
-      <c r="C122" s="20" t="n">
+      <c r="C126" s="20" t="n">
         <v>16674</v>
       </c>
-      <c r="D122" s="20" t="n">
+      <c r="D126" s="20" t="n">
         <v>-11445</v>
       </c>
-      <c r="E122" s="20" t="n">
+      <c r="E126" s="20" t="n">
         <v>1922</v>
       </c>
-      <c r="F122" s="20" t="n">
+      <c r="F126" s="20" t="n">
         <v>9941</v>
       </c>
-      <c r="G122" s="20" t="n">
+      <c r="G126" s="20" t="n">
         <v>-16436</v>
       </c>
-      <c r="H122" s="20" t="n">
+      <c r="H126" s="20" t="n">
         <v>16908</v>
       </c>
-      <c r="I122" s="20" t="n">
+      <c r="I126" s="20" t="n">
         <v>4415</v>
       </c>
-      <c r="J122" s="20" t="n">
+      <c r="J126" s="20" t="n">
         <v>1439</v>
       </c>
-      <c r="K122" s="20" t="n">
+      <c r="K126" s="20" t="n">
         <v>10213</v>
       </c>
-      <c r="L122" s="20" t="n">
+      <c r="L126" s="20" t="n">
         <v>17673</v>
       </c>
-      <c r="M122" s="20" t="n">
+      <c r="M126" s="20" t="n">
         <v>9526</v>
       </c>
-      <c r="N122" s="20" t="n">
+      <c r="N126" s="20" t="n">
         <v>2218</v>
       </c>
-      <c r="U122" s="20" t="n">
+      <c r="U126" s="20" t="n">
         <v>-11603</v>
       </c>
-      <c r="V122" s="20" t="n">
+      <c r="V126" s="20" t="n">
         <v>1922</v>
       </c>
-      <c r="W122" s="20" t="n">
+      <c r="W126" s="20" t="n">
         <v>4415</v>
       </c>
-      <c r="X122" s="20" t="n">
+      <c r="X126" s="20" t="n">
         <v>9526</v>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="18" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="18" t="inlineStr">
         <is>
           <t>퇴직급여 조정액</t>
         </is>
       </c>
-      <c r="C123" s="20" t="n">
+      <c r="C127" s="20" t="n">
         <v>262</v>
       </c>
-      <c r="D123" s="20" t="n">
+      <c r="D127" s="20" t="n">
         <v>262</v>
       </c>
-      <c r="E123" s="20" t="n">
+      <c r="E127" s="20" t="n">
         <v>7788</v>
       </c>
-      <c r="F123" s="20" t="n">
+      <c r="F127" s="20" t="n">
         <v>88</v>
       </c>
-      <c r="G123" s="20" t="n">
+      <c r="G127" s="20" t="n">
         <v>89</v>
       </c>
-      <c r="H123" s="20" t="n">
+      <c r="H127" s="20" t="n">
         <v>88</v>
       </c>
-      <c r="I123" s="20" t="n">
+      <c r="I127" s="20" t="n">
         <v>-1538</v>
       </c>
-      <c r="J123" s="20" t="n">
+      <c r="J127" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="K123" s="20" t="n">
+      <c r="K127" s="20" t="n">
         <v>308</v>
       </c>
-      <c r="L123" s="20" t="n">
+      <c r="L127" s="20" t="n">
         <v>137</v>
       </c>
-      <c r="M123" s="20" t="n">
+      <c r="M127" s="20" t="n">
         <v>7807</v>
       </c>
-      <c r="N123" s="20" t="n">
+      <c r="N127" s="20" t="n">
         <v>-242</v>
       </c>
-      <c r="U123" s="20" t="n">
+      <c r="U127" s="20" t="n">
         <v>-1829</v>
       </c>
-      <c r="V123" s="20" t="n">
+      <c r="V127" s="20" t="n">
         <v>7788</v>
       </c>
-      <c r="W123" s="20" t="n">
+      <c r="W127" s="20" t="n">
         <v>-1538</v>
       </c>
-      <c r="X123" s="20" t="n">
+      <c r="X127" s="20" t="n">
         <v>7807</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>포괄이익</t>
         </is>
       </c>
-      <c r="C124" s="12" t="n">
+      <c r="C128" s="12" t="n">
         <v>-6774</v>
       </c>
-      <c r="D124" s="12" t="n">
+      <c r="D128" s="12" t="n">
         <v>18902</v>
       </c>
-      <c r="E124" s="12" t="n">
+      <c r="E128" s="12" t="n">
         <v>27473</v>
       </c>
-      <c r="F124" s="12" t="n">
+      <c r="F128" s="12" t="n">
         <v>-3462</v>
       </c>
-      <c r="G124" s="12" t="n">
+      <c r="G128" s="12" t="n">
         <v>3800</v>
       </c>
-      <c r="H124" s="12" t="n">
+      <c r="H128" s="12" t="n">
         <v>-2212</v>
       </c>
-      <c r="I124" s="12" t="n">
+      <c r="I128" s="12" t="n">
         <v>-21427</v>
       </c>
-      <c r="J124" s="12" t="n">
+      <c r="J128" s="12" t="n">
         <v>30627</v>
       </c>
-      <c r="K124" s="12" t="n">
+      <c r="K128" s="12" t="n">
         <v>29621</v>
       </c>
-      <c r="L124" s="12" t="n">
+      <c r="L128" s="12" t="n">
         <v>23219</v>
       </c>
-      <c r="M124" s="12" t="n">
+      <c r="M128" s="12" t="n">
         <v>10065</v>
       </c>
-      <c r="N124" s="12" t="n">
+      <c r="N128" s="12" t="n">
         <v>62159</v>
       </c>
-      <c r="U124" s="12" t="n">
+      <c r="U128" s="12" t="n">
         <v>14624</v>
       </c>
-      <c r="V124" s="12" t="n">
+      <c r="V128" s="12" t="n">
         <v>27473</v>
       </c>
-      <c r="W124" s="12" t="n">
+      <c r="W128" s="12" t="n">
         <v>-21427</v>
       </c>
-      <c r="X124" s="12" t="n">
+      <c r="X128" s="12" t="n">
         <v>10065</v>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="9" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C125" s="12" t="n">
+      <c r="C129" s="12" t="n">
         <v>-6774</v>
       </c>
-      <c r="D125" s="12" t="n">
+      <c r="D129" s="12" t="n">
         <v>18902</v>
       </c>
-      <c r="E125" s="12" t="n">
+      <c r="E129" s="12" t="n">
         <v>27473</v>
       </c>
-      <c r="F125" s="12" t="n">
+      <c r="F129" s="12" t="n">
         <v>-3462</v>
       </c>
-      <c r="G125" s="12" t="n">
+      <c r="G129" s="12" t="n">
         <v>3800</v>
       </c>
-      <c r="H125" s="12" t="n">
+      <c r="H129" s="12" t="n">
         <v>-2212</v>
       </c>
-      <c r="I125" s="12" t="n">
+      <c r="I129" s="12" t="n">
         <v>-21427</v>
       </c>
-      <c r="J125" s="12" t="n">
+      <c r="J129" s="12" t="n">
         <v>30627</v>
       </c>
-      <c r="K125" s="12" t="n">
+      <c r="K129" s="12" t="n">
         <v>29621</v>
       </c>
-      <c r="L125" s="12" t="n">
+      <c r="L129" s="12" t="n">
         <v>23219</v>
       </c>
-      <c r="M125" s="12" t="n">
+      <c r="M129" s="12" t="n">
         <v>10065</v>
       </c>
-      <c r="N125" s="12" t="n">
+      <c r="N129" s="12" t="n">
         <v>62159</v>
       </c>
-      <c r="U125" s="12" t="n">
+      <c r="U129" s="12" t="n">
         <v>14624</v>
       </c>
-      <c r="V125" s="12" t="n">
+      <c r="V129" s="12" t="n">
         <v>27473</v>
       </c>
-      <c r="W125" s="12" t="n">
+      <c r="W129" s="12" t="n">
         <v>-21427</v>
       </c>
-      <c r="X125" s="12" t="n">
+      <c r="X129" s="12" t="n">
         <v>10065</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>비지배주주 포괄이익</t>
         </is>
       </c>
-      <c r="C126" s="12" t="n">
+      <c r="C130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="12" t="n">
+      <c r="D130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E126" s="12" t="n">
+      <c r="E130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="12" t="n">
+      <c r="F130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G126" s="12" t="n">
+      <c r="G130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H126" s="12" t="n">
+      <c r="H130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I126" s="12" t="n">
+      <c r="I130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J126" s="12" t="n">
+      <c r="J130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="K126" s="12" t="n">
+      <c r="K130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="L126" s="12" t="n">
+      <c r="L130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="M126" s="12" t="n">
+      <c r="M130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N126" s="12" t="n">
+      <c r="N130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="U126" s="12" t="n">
+      <c r="U130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="V126" s="12" t="n">
+      <c r="V130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="W126" s="12" t="n">
+      <c r="W130" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="X126" s="12" t="n">
+      <c r="X130" s="12" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="16" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="16" t="inlineStr">
         <is>
           <t>부문 · 전 항목</t>
         </is>
       </c>
-      <c r="B128" s="42" t="inlineStr">
+      <c r="B132" s="42" t="inlineStr">
         <is>
           <t>부문 · 항목</t>
         </is>
       </c>
-      <c r="C128" s="16" t="n"/>
-      <c r="D128" s="16" t="n"/>
-      <c r="E128" s="16" t="n"/>
-      <c r="F128" s="16" t="n"/>
-      <c r="G128" s="16" t="n"/>
-      <c r="H128" s="16" t="n"/>
-      <c r="I128" s="16" t="n"/>
-      <c r="J128" s="16" t="n"/>
-      <c r="K128" s="16" t="n"/>
-      <c r="L128" s="16" t="n"/>
-      <c r="M128" s="16" t="n"/>
-      <c r="N128" s="16" t="n"/>
-      <c r="O128" s="16" t="n"/>
-      <c r="P128" s="16" t="n"/>
-      <c r="Q128" s="16" t="n"/>
-      <c r="R128" s="16" t="n"/>
-      <c r="S128" s="16" t="n"/>
-      <c r="T128" s="16" t="n"/>
-      <c r="U128" s="16" t="n"/>
-      <c r="V128" s="16" t="n"/>
-      <c r="W128" s="16" t="n"/>
-      <c r="X128" s="16" t="n"/>
-      <c r="Y128" s="16" t="n"/>
-      <c r="Z128" s="16" t="n"/>
-      <c r="AA128" s="16" t="n"/>
-      <c r="AB128" s="16" t="n"/>
-      <c r="AC128" s="16" t="n"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="inlineStr">
+      <c r="C132" s="16" t="n"/>
+      <c r="D132" s="16" t="n"/>
+      <c r="E132" s="16" t="n"/>
+      <c r="F132" s="16" t="n"/>
+      <c r="G132" s="16" t="n"/>
+      <c r="H132" s="16" t="n"/>
+      <c r="I132" s="16" t="n"/>
+      <c r="J132" s="16" t="n"/>
+      <c r="K132" s="16" t="n"/>
+      <c r="L132" s="16" t="n"/>
+      <c r="M132" s="16" t="n"/>
+      <c r="N132" s="16" t="n"/>
+      <c r="O132" s="16" t="n"/>
+      <c r="P132" s="16" t="n"/>
+      <c r="Q132" s="16" t="n"/>
+      <c r="R132" s="16" t="n"/>
+      <c r="S132" s="16" t="n"/>
+      <c r="T132" s="16" t="n"/>
+      <c r="U132" s="16" t="n"/>
+      <c r="V132" s="16" t="n"/>
+      <c r="W132" s="16" t="n"/>
+      <c r="X132" s="16" t="n"/>
+      <c r="Y132" s="16" t="n"/>
+      <c r="Z132" s="16" t="n"/>
+      <c r="AA132" s="16" t="n"/>
+      <c r="AB132" s="16" t="n"/>
+      <c r="AC132" s="16" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B133" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C129" s="5" t="inlineStr">
+      <c r="C133" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="D129" s="5" t="inlineStr">
+      <c r="D133" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="E129" s="5" t="inlineStr">
+      <c r="E133" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="F129" s="5" t="inlineStr">
+      <c r="F133" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="G129" s="5" t="inlineStr">
+      <c r="G133" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="H129" s="5" t="inlineStr">
+      <c r="H133" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="I129" s="5" t="inlineStr">
+      <c r="I133" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="J129" s="5" t="inlineStr">
+      <c r="J133" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="K129" s="5" t="inlineStr">
+      <c r="K133" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="L129" s="5" t="inlineStr">
+      <c r="L133" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="M129" s="5" t="inlineStr">
+      <c r="M133" s="5" t="inlineStr">
         <is>
           <t>2026.4Q</t>
         </is>
       </c>
-      <c r="N129" s="5" t="inlineStr">
+      <c r="N133" s="5" t="inlineStr">
         <is>
           <t>2027.1Q</t>
         </is>
       </c>
-      <c r="O129" s="5" t="inlineStr">
+      <c r="O133" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="P129" s="5" t="inlineStr">
+      <c r="P133" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="Q129" s="5" t="inlineStr">
+      <c r="Q133" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="R129" s="5" t="inlineStr">
+      <c r="R133" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="S129" s="5" t="inlineStr">
+      <c r="S133" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="T129" s="5" t="inlineStr">
+      <c r="T133" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="U129" s="5" t="inlineStr">
+      <c r="U133" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="V129" s="5" t="inlineStr">
+      <c r="V133" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="W129" s="5" t="inlineStr">
+      <c r="W133" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="X129" s="5" t="inlineStr">
+      <c r="X133" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="Y129" s="5" t="inlineStr">
+      <c r="Y133" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="Z129" s="5" t="inlineStr">
+      <c r="Z133" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AA129" s="5" t="inlineStr">
+      <c r="AA133" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AB129" s="5" t="inlineStr">
+      <c r="AB133" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
-      <c r="AC129" s="5" t="inlineStr">
+      <c r="AC133" s="5" t="inlineStr">
         <is>
           <t>2031(MW)</t>
         </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="18" t="inlineStr">
-        <is>
-          <t>BankingReportableSegmentMember · Revenues From External Customers</t>
-        </is>
-      </c>
-      <c r="C130" s="20" t="n">
-        <v>40042</v>
-      </c>
-      <c r="D130" s="20" t="n">
-        <v>43145</v>
-      </c>
-      <c r="E130" s="20" t="n">
-        <v>43409</v>
-      </c>
-      <c r="F130" s="20" t="n">
-        <v>47481</v>
-      </c>
-      <c r="G130" s="20" t="n">
-        <v>43916</v>
-      </c>
-      <c r="H130" s="20" t="n">
-        <v>52212</v>
-      </c>
-      <c r="I130" s="20" t="n">
-        <v>46640</v>
-      </c>
-      <c r="J130" s="20" t="n">
-        <v>51645</v>
-      </c>
-      <c r="K130" s="20" t="n">
-        <v>52089</v>
-      </c>
-      <c r="L130" s="20" t="n">
-        <v>61661</v>
-      </c>
-      <c r="M130" s="20" t="n">
-        <v>60676</v>
-      </c>
-      <c r="N130" s="20" t="n">
-        <v>98751</v>
-      </c>
-      <c r="V130" s="20" t="n">
-        <v>43409</v>
-      </c>
-      <c r="W130" s="20" t="n">
-        <v>46640</v>
-      </c>
-      <c r="X130" s="20" t="n">
-        <v>60676</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="18" t="inlineStr">
-        <is>
-          <t>LeasingReportableSegmentMember · Revenues From External Customers</t>
-        </is>
-      </c>
-      <c r="C131" s="20" t="n">
-        <v>2761</v>
-      </c>
-      <c r="D131" s="20" t="n">
-        <v>3084</v>
-      </c>
-      <c r="E131" s="20" t="n">
-        <v>3355</v>
-      </c>
-      <c r="F131" s="20" t="n">
-        <v>3056</v>
-      </c>
-      <c r="G131" s="20" t="n">
-        <v>4981</v>
-      </c>
-      <c r="H131" s="20" t="n">
-        <v>3305</v>
-      </c>
-      <c r="I131" s="20" t="n">
-        <v>3210</v>
-      </c>
-      <c r="J131" s="20" t="n">
-        <v>3457</v>
-      </c>
-      <c r="K131" s="20" t="n">
-        <v>3577</v>
-      </c>
-      <c r="L131" s="20" t="n">
-        <v>3682</v>
-      </c>
-      <c r="M131" s="20" t="n">
-        <v>3699</v>
-      </c>
-      <c r="N131" s="20" t="n">
-        <v>8233</v>
-      </c>
-      <c r="V131" s="20" t="n">
-        <v>3355</v>
-      </c>
-      <c r="W131" s="20" t="n">
-        <v>3210</v>
-      </c>
-      <c r="X131" s="20" t="n">
-        <v>3699</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="18" t="inlineStr">
-        <is>
-          <t>SecuritiesReportableSegmentMember · Revenues From External Customers</t>
-        </is>
-      </c>
-      <c r="C132" s="20" t="n">
-        <v>1045</v>
-      </c>
-      <c r="D132" s="20" t="n">
-        <v>872</v>
-      </c>
-      <c r="E132" s="20" t="n">
-        <v>1039</v>
-      </c>
-      <c r="F132" s="20" t="n">
-        <v>1219</v>
-      </c>
-      <c r="G132" s="20" t="n">
-        <v>932</v>
-      </c>
-      <c r="H132" s="20" t="n">
-        <v>846</v>
-      </c>
-      <c r="I132" s="20" t="n">
-        <v>881</v>
-      </c>
-      <c r="J132" s="20" t="n">
-        <v>841</v>
-      </c>
-      <c r="K132" s="20" t="n">
-        <v>1165</v>
-      </c>
-      <c r="L132" s="20" t="n">
-        <v>1575</v>
-      </c>
-      <c r="M132" s="20" t="n">
-        <v>1369</v>
-      </c>
-      <c r="N132" s="20" t="n">
-        <v>1561</v>
-      </c>
-      <c r="V132" s="20" t="n">
-        <v>1039</v>
-      </c>
-      <c r="W132" s="20" t="n">
-        <v>881</v>
-      </c>
-      <c r="X132" s="20" t="n">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="18" t="inlineStr">
-        <is>
-          <t>보고부문 합계 · Revenues From External Customers</t>
-        </is>
-      </c>
-      <c r="C133" s="20" t="n">
-        <v>43847</v>
-      </c>
-      <c r="D133" s="20" t="n">
-        <v>47102</v>
-      </c>
-      <c r="E133" s="20" t="n">
-        <v>47803</v>
-      </c>
-      <c r="F133" s="20" t="n">
-        <v>51757</v>
-      </c>
-      <c r="G133" s="20" t="n">
-        <v>49830</v>
-      </c>
-      <c r="H133" s="20" t="n">
-        <v>56362</v>
-      </c>
-      <c r="I133" s="20" t="n">
-        <v>50731</v>
-      </c>
-      <c r="J133" s="20" t="n">
-        <v>55943</v>
-      </c>
-      <c r="K133" s="20" t="n">
-        <v>56831</v>
-      </c>
-      <c r="L133" s="20" t="n">
-        <v>66920</v>
-      </c>
-      <c r="M133" s="20" t="n">
-        <v>65743</v>
-      </c>
-      <c r="N133" s="20" t="n">
-        <v>108546</v>
-      </c>
-      <c r="V133" s="20" t="n">
-        <v>47803</v>
-      </c>
-      <c r="W133" s="20" t="n">
-        <v>50731</v>
-      </c>
-      <c r="X133" s="20" t="n">
-        <v>65743</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="18" t="inlineStr">
         <is>
-          <t>기타 · Revenues From External Customers</t>
+          <t>BankingReportableSegmentMember · Revenues From External Customers</t>
         </is>
       </c>
       <c r="C134" s="20" t="n">
-        <v>643</v>
+        <v>40042</v>
       </c>
       <c r="D134" s="20" t="n">
-        <v>647</v>
+        <v>43145</v>
       </c>
       <c r="E134" s="20" t="n">
-        <v>754</v>
+        <v>43409</v>
       </c>
       <c r="F134" s="20" t="n">
-        <v>678</v>
+        <v>47481</v>
       </c>
       <c r="G134" s="20" t="n">
-        <v>735</v>
+        <v>43916</v>
       </c>
       <c r="H134" s="20" t="n">
-        <v>802</v>
+        <v>52212</v>
       </c>
       <c r="I134" s="20" t="n">
-        <v>838</v>
+        <v>46640</v>
       </c>
       <c r="J134" s="20" t="n">
-        <v>765</v>
+        <v>51645</v>
       </c>
       <c r="K134" s="20" t="n">
-        <v>983</v>
+        <v>52089</v>
       </c>
       <c r="L134" s="20" t="n">
-        <v>953</v>
+        <v>61661</v>
       </c>
       <c r="M134" s="20" t="n">
-        <v>935</v>
+        <v>60676</v>
       </c>
       <c r="N134" s="20" t="n">
-        <v>1121</v>
+        <v>98751</v>
       </c>
       <c r="V134" s="20" t="n">
-        <v>754</v>
+        <v>43409</v>
       </c>
       <c r="W134" s="20" t="n">
-        <v>838</v>
+        <v>46640</v>
       </c>
       <c r="X134" s="20" t="n">
-        <v>935</v>
+        <v>60676</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="18" t="inlineStr">
-        <is>
-          <t>합계 · Revenues From External Customers</t>
-        </is>
-      </c>
-      <c r="C135" s="20" t="n">
-        <v>44491</v>
-      </c>
-      <c r="D135" s="20" t="n">
-        <v>47749</v>
-      </c>
-      <c r="E135" s="20" t="n">
-        <v>48557</v>
-      </c>
-      <c r="F135" s="20" t="n">
-        <v>52435</v>
-      </c>
-      <c r="G135" s="20" t="n">
-        <v>50565</v>
-      </c>
-      <c r="H135" s="20" t="n">
-        <v>57165</v>
-      </c>
-      <c r="I135" s="20" t="n">
-        <v>51569</v>
-      </c>
-      <c r="J135" s="20" t="n">
-        <v>56709</v>
-      </c>
-      <c r="K135" s="20" t="n">
-        <v>57814</v>
-      </c>
-      <c r="L135" s="20" t="n">
-        <v>67872</v>
-      </c>
-      <c r="M135" s="20" t="n">
-        <v>66679</v>
-      </c>
-      <c r="N135" s="20" t="n">
-        <v>109667</v>
-      </c>
-      <c r="V135" s="20" t="n">
-        <v>48557</v>
-      </c>
-      <c r="W135" s="20" t="n">
-        <v>51569</v>
-      </c>
-      <c r="X135" s="20" t="n">
-        <v>66679</v>
+      <c r="A135" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G135" s="15">
+        <f>IF(OR(G134="",C134=""),"",IF(C134&lt;=0,"",IFERROR(G134/C134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H135" s="15">
+        <f>IF(OR(H134="",D134=""),"",IF(D134&lt;=0,"",IFERROR(H134/D134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I135" s="15">
+        <f>IF(OR(I134="",E134=""),"",IF(E134&lt;=0,"",IFERROR(I134/E134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J135" s="15">
+        <f>IF(OR(J134="",F134=""),"",IF(F134&lt;=0,"",IFERROR(J134/F134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K135" s="15">
+        <f>IF(OR(K134="",G134=""),"",IF(G134&lt;=0,"",IFERROR(K134/G134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L135" s="15">
+        <f>IF(OR(L134="",H134=""),"",IF(H134&lt;=0,"",IFERROR(L134/H134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M135" s="15">
+        <f>IF(OR(M134="",I134=""),"",IF(I134&lt;=0,"",IFERROR(M134/I134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N135" s="15">
+        <f>IF(OR(N134="",J134=""),"",IF(J134&lt;=0,"",IFERROR(N134/J134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V135" s="15">
+        <f>IF(OR(V134="",U134=""),"",IF(U134&lt;=0,"",IFERROR(V134/U134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W135" s="15">
+        <f>IF(OR(W134="",V134=""),"",IF(V134&lt;=0,"",IFERROR(W134/V134-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X135" s="15">
+        <f>IF(OR(X134="",W134=""),"",IF(W134&lt;=0,"",IFERROR(X134/W134-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="18" t="inlineStr">
         <is>
-          <t>조정액 · Revenues From External Customers</t>
+          <t>LeasingReportableSegmentMember · Revenues From External Customers</t>
         </is>
       </c>
       <c r="C136" s="20" t="n">
-        <v>10</v>
+        <v>2761</v>
       </c>
       <c r="D136" s="20" t="n">
-        <v>0</v>
+        <v>3084</v>
       </c>
       <c r="E136" s="20" t="n">
-        <v>0</v>
+        <v>3355</v>
       </c>
       <c r="F136" s="20" t="n">
-        <v>0</v>
+        <v>3056</v>
       </c>
       <c r="G136" s="20" t="n">
-        <v>-81</v>
+        <v>4981</v>
       </c>
       <c r="H136" s="20" t="n">
-        <v>-3</v>
+        <v>3305</v>
       </c>
       <c r="I136" s="20" t="n">
-        <v>84</v>
+        <v>3210</v>
       </c>
       <c r="J136" s="20" t="n">
-        <v>-103</v>
+        <v>3457</v>
       </c>
       <c r="K136" s="20" t="n">
-        <v>96</v>
+        <v>3577</v>
       </c>
       <c r="L136" s="20" t="n">
-        <v>-1</v>
+        <v>3682</v>
       </c>
       <c r="M136" s="20" t="n">
-        <v>8</v>
+        <v>3699</v>
       </c>
       <c r="N136" s="20" t="n">
-        <v>-27</v>
+        <v>8233</v>
       </c>
       <c r="V136" s="20" t="n">
-        <v>0</v>
+        <v>3355</v>
       </c>
       <c r="W136" s="20" t="n">
-        <v>84</v>
+        <v>3210</v>
       </c>
       <c r="X136" s="20" t="n">
-        <v>8</v>
+        <v>3699</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>Revenues From External Customers</t>
-        </is>
-      </c>
-      <c r="C137" s="12" t="n">
-        <v>44501</v>
-      </c>
-      <c r="D137" s="12" t="n">
-        <v>47749</v>
-      </c>
-      <c r="E137" s="12" t="n">
-        <v>48557</v>
-      </c>
-      <c r="F137" s="12" t="n">
-        <v>52435</v>
-      </c>
-      <c r="G137" s="12" t="n">
-        <v>50484</v>
-      </c>
-      <c r="H137" s="12" t="n">
-        <v>57162</v>
-      </c>
-      <c r="I137" s="12" t="n">
-        <v>51653</v>
-      </c>
-      <c r="V137" s="12" t="n">
-        <v>48557</v>
-      </c>
-      <c r="W137" s="12" t="n">
-        <v>51653</v>
+      <c r="A137" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G137" s="15">
+        <f>IF(OR(G136="",C136=""),"",IF(C136&lt;=0,"",IFERROR(G136/C136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H137" s="15">
+        <f>IF(OR(H136="",D136=""),"",IF(D136&lt;=0,"",IFERROR(H136/D136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I137" s="15">
+        <f>IF(OR(I136="",E136=""),"",IF(E136&lt;=0,"",IFERROR(I136/E136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J137" s="15">
+        <f>IF(OR(J136="",F136=""),"",IF(F136&lt;=0,"",IFERROR(J136/F136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K137" s="15">
+        <f>IF(OR(K136="",G136=""),"",IF(G136&lt;=0,"",IFERROR(K136/G136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L137" s="15">
+        <f>IF(OR(L136="",H136=""),"",IF(H136&lt;=0,"",IFERROR(L136/H136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M137" s="15">
+        <f>IF(OR(M136="",I136=""),"",IF(I136&lt;=0,"",IFERROR(M136/I136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N137" s="15">
+        <f>IF(OR(N136="",J136=""),"",IF(J136&lt;=0,"",IFERROR(N136/J136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V137" s="15">
+        <f>IF(OR(V136="",U136=""),"",IF(U136&lt;=0,"",IFERROR(V136/U136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W137" s="15">
+        <f>IF(OR(W136="",V136=""),"",IF(V136&lt;=0,"",IFERROR(W136/V136-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X137" s="15">
+        <f>IF(OR(X136="",W136=""),"",IF(W136&lt;=0,"",IFERROR(X136/W136-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · Revenues From External Customers</t>
-        </is>
+          <t>SecuritiesReportableSegmentMember · Revenues From External Customers</t>
+        </is>
+      </c>
+      <c r="C138" s="20" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D138" s="20" t="n">
+        <v>872</v>
+      </c>
+      <c r="E138" s="20" t="n">
+        <v>1039</v>
       </c>
       <c r="F138" s="20" t="n">
-        <v>52435</v>
+        <v>1219</v>
+      </c>
+      <c r="G138" s="20" t="n">
+        <v>932</v>
+      </c>
+      <c r="H138" s="20" t="n">
+        <v>846</v>
+      </c>
+      <c r="I138" s="20" t="n">
+        <v>881</v>
       </c>
       <c r="J138" s="20" t="n">
-        <v>56606</v>
+        <v>841</v>
+      </c>
+      <c r="K138" s="20" t="n">
+        <v>1165</v>
+      </c>
+      <c r="L138" s="20" t="n">
+        <v>1575</v>
+      </c>
+      <c r="M138" s="20" t="n">
+        <v>1369</v>
       </c>
       <c r="N138" s="20" t="n">
-        <v>109640</v>
+        <v>1561</v>
+      </c>
+      <c r="V138" s="20" t="n">
+        <v>1039</v>
+      </c>
+      <c r="W138" s="20" t="n">
+        <v>881</v>
+      </c>
+      <c r="X138" s="20" t="n">
+        <v>1369</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="18" t="inlineStr">
-        <is>
-          <t>BankingReportableSegmentMember · Transactions With Other Segments</t>
-        </is>
-      </c>
-      <c r="C139" s="20" t="n">
-        <v>517</v>
-      </c>
-      <c r="D139" s="20" t="n">
-        <v>363</v>
-      </c>
-      <c r="E139" s="20" t="n">
-        <v>538</v>
-      </c>
-      <c r="F139" s="20" t="n">
-        <v>719</v>
-      </c>
-      <c r="G139" s="20" t="n">
-        <v>238</v>
-      </c>
-      <c r="H139" s="20" t="n">
-        <v>435</v>
-      </c>
-      <c r="I139" s="20" t="n">
-        <v>391</v>
-      </c>
-      <c r="J139" s="20" t="n">
-        <v>408</v>
-      </c>
-      <c r="K139" s="20" t="n">
-        <v>512</v>
-      </c>
-      <c r="L139" s="20" t="n">
-        <v>642</v>
-      </c>
-      <c r="M139" s="20" t="n">
-        <v>716</v>
-      </c>
-      <c r="N139" s="20" t="n">
-        <v>660</v>
-      </c>
-      <c r="V139" s="20" t="n">
-        <v>538</v>
-      </c>
-      <c r="W139" s="20" t="n">
-        <v>391</v>
-      </c>
-      <c r="X139" s="20" t="n">
-        <v>716</v>
+      <c r="A139" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G139" s="15">
+        <f>IF(OR(G138="",C138=""),"",IF(C138&lt;=0,"",IFERROR(G138/C138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H139" s="15">
+        <f>IF(OR(H138="",D138=""),"",IF(D138&lt;=0,"",IFERROR(H138/D138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I139" s="15">
+        <f>IF(OR(I138="",E138=""),"",IF(E138&lt;=0,"",IFERROR(I138/E138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J139" s="15">
+        <f>IF(OR(J138="",F138=""),"",IF(F138&lt;=0,"",IFERROR(J138/F138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K139" s="15">
+        <f>IF(OR(K138="",G138=""),"",IF(G138&lt;=0,"",IFERROR(K138/G138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L139" s="15">
+        <f>IF(OR(L138="",H138=""),"",IF(H138&lt;=0,"",IFERROR(L138/H138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M139" s="15">
+        <f>IF(OR(M138="",I138=""),"",IF(I138&lt;=0,"",IFERROR(M138/I138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N139" s="15">
+        <f>IF(OR(N138="",J138=""),"",IF(J138&lt;=0,"",IFERROR(N138/J138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V139" s="15">
+        <f>IF(OR(V138="",U138=""),"",IF(U138&lt;=0,"",IFERROR(V138/U138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W139" s="15">
+        <f>IF(OR(W138="",V138=""),"",IF(V138&lt;=0,"",IFERROR(W138/V138-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X139" s="15">
+        <f>IF(OR(X138="",W138=""),"",IF(W138&lt;=0,"",IFERROR(X138/W138-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="18" t="inlineStr">
         <is>
-          <t>LeasingReportableSegmentMember · Transactions With Other Segments</t>
+          <t>보고부문 합계 · Revenues From External Customers</t>
         </is>
       </c>
       <c r="C140" s="20" t="n">
-        <v>41</v>
+        <v>43847</v>
       </c>
       <c r="D140" s="20" t="n">
-        <v>39</v>
+        <v>47102</v>
       </c>
       <c r="E140" s="20" t="n">
-        <v>44</v>
+        <v>47803</v>
       </c>
       <c r="F140" s="20" t="n">
-        <v>41</v>
+        <v>51757</v>
       </c>
       <c r="G140" s="20" t="n">
-        <v>40</v>
+        <v>49830</v>
       </c>
       <c r="H140" s="20" t="n">
-        <v>40</v>
+        <v>56362</v>
       </c>
       <c r="I140" s="20" t="n">
-        <v>41</v>
+        <v>50731</v>
       </c>
       <c r="J140" s="20" t="n">
-        <v>39</v>
+        <v>55943</v>
       </c>
       <c r="K140" s="20" t="n">
-        <v>41</v>
+        <v>56831</v>
       </c>
       <c r="L140" s="20" t="n">
-        <v>40</v>
+        <v>66920</v>
       </c>
       <c r="M140" s="20" t="n">
-        <v>43</v>
+        <v>65743</v>
       </c>
       <c r="N140" s="20" t="n">
-        <v>43</v>
+        <v>108546</v>
       </c>
       <c r="V140" s="20" t="n">
-        <v>44</v>
+        <v>47803</v>
       </c>
       <c r="W140" s="20" t="n">
-        <v>41</v>
+        <v>50731</v>
       </c>
       <c r="X140" s="20" t="n">
-        <v>43</v>
+        <v>65743</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="18" t="inlineStr">
-        <is>
-          <t>SecuritiesReportableSegmentMember · Transactions With Other Segments</t>
-        </is>
-      </c>
-      <c r="C141" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="D141" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="E141" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="F141" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="G141" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="H141" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="I141" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="J141" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="K141" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="L141" s="20" t="n">
-        <v>27</v>
-      </c>
-      <c r="M141" s="20" t="n">
-        <v>33</v>
-      </c>
-      <c r="N141" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="V141" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="W141" s="20" t="n">
-        <v>26</v>
-      </c>
-      <c r="X141" s="20" t="n">
-        <v>33</v>
+      <c r="A141" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G141" s="15">
+        <f>IF(OR(G140="",C140=""),"",IF(C140&lt;=0,"",IFERROR(G140/C140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H141" s="15">
+        <f>IF(OR(H140="",D140=""),"",IF(D140&lt;=0,"",IFERROR(H140/D140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I141" s="15">
+        <f>IF(OR(I140="",E140=""),"",IF(E140&lt;=0,"",IFERROR(I140/E140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J141" s="15">
+        <f>IF(OR(J140="",F140=""),"",IF(F140&lt;=0,"",IFERROR(J140/F140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K141" s="15">
+        <f>IF(OR(K140="",G140=""),"",IF(G140&lt;=0,"",IFERROR(K140/G140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L141" s="15">
+        <f>IF(OR(L140="",H140=""),"",IF(H140&lt;=0,"",IFERROR(L140/H140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M141" s="15">
+        <f>IF(OR(M140="",I140=""),"",IF(I140&lt;=0,"",IFERROR(M140/I140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N141" s="15">
+        <f>IF(OR(N140="",J140=""),"",IF(J140&lt;=0,"",IFERROR(N140/J140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V141" s="15">
+        <f>IF(OR(V140="",U140=""),"",IF(U140&lt;=0,"",IFERROR(V140/U140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W141" s="15">
+        <f>IF(OR(W140="",V140=""),"",IF(V140&lt;=0,"",IFERROR(W140/V140-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X141" s="15">
+        <f>IF(OR(X140="",W140=""),"",IF(W140&lt;=0,"",IFERROR(X140/W140-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · Transactions With Other Segments</t>
+          <t>기타 · Revenues From External Customers</t>
         </is>
       </c>
       <c r="C142" s="20" t="n">
-        <v>577</v>
+        <v>643</v>
       </c>
       <c r="D142" s="20" t="n">
-        <v>422</v>
+        <v>647</v>
       </c>
       <c r="E142" s="20" t="n">
-        <v>604</v>
+        <v>754</v>
       </c>
       <c r="F142" s="20" t="n">
-        <v>784</v>
+        <v>678</v>
       </c>
       <c r="G142" s="20" t="n">
-        <v>301</v>
+        <v>735</v>
       </c>
       <c r="H142" s="20" t="n">
-        <v>499</v>
+        <v>802</v>
       </c>
       <c r="I142" s="20" t="n">
-        <v>459</v>
+        <v>838</v>
       </c>
       <c r="J142" s="20" t="n">
-        <v>471</v>
+        <v>765</v>
       </c>
       <c r="K142" s="20" t="n">
-        <v>582</v>
+        <v>983</v>
       </c>
       <c r="L142" s="20" t="n">
-        <v>710</v>
+        <v>953</v>
       </c>
       <c r="M142" s="20" t="n">
-        <v>792</v>
+        <v>935</v>
       </c>
       <c r="N142" s="20" t="n">
-        <v>735</v>
+        <v>1121</v>
       </c>
       <c r="V142" s="20" t="n">
-        <v>604</v>
+        <v>754</v>
       </c>
       <c r="W142" s="20" t="n">
-        <v>459</v>
+        <v>838</v>
       </c>
       <c r="X142" s="20" t="n">
-        <v>792</v>
+        <v>935</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="18" t="inlineStr">
-        <is>
-          <t>기타 · Transactions With Other Segments</t>
-        </is>
-      </c>
-      <c r="C143" s="20" t="n">
-        <v>487</v>
-      </c>
-      <c r="D143" s="20" t="n">
-        <v>3986</v>
-      </c>
-      <c r="E143" s="20" t="n">
-        <v>486</v>
-      </c>
-      <c r="F143" s="20" t="n">
-        <v>6640</v>
-      </c>
-      <c r="G143" s="20" t="n">
-        <v>584</v>
-      </c>
-      <c r="H143" s="20" t="n">
-        <v>13092</v>
-      </c>
-      <c r="I143" s="20" t="n">
-        <v>1031</v>
-      </c>
-      <c r="J143" s="20" t="n">
-        <v>11065</v>
-      </c>
-      <c r="K143" s="20" t="n">
-        <v>1075</v>
-      </c>
-      <c r="L143" s="20" t="n">
-        <v>27649</v>
-      </c>
-      <c r="M143" s="20" t="n">
-        <v>1177</v>
-      </c>
-      <c r="N143" s="20" t="n">
-        <v>11926</v>
-      </c>
-      <c r="V143" s="20" t="n">
-        <v>486</v>
-      </c>
-      <c r="W143" s="20" t="n">
-        <v>1031</v>
-      </c>
-      <c r="X143" s="20" t="n">
-        <v>1177</v>
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G143" s="15">
+        <f>IF(OR(G142="",C142=""),"",IF(C142&lt;=0,"",IFERROR(G142/C142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H143" s="15">
+        <f>IF(OR(H142="",D142=""),"",IF(D142&lt;=0,"",IFERROR(H142/D142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I143" s="15">
+        <f>IF(OR(I142="",E142=""),"",IF(E142&lt;=0,"",IFERROR(I142/E142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J143" s="15">
+        <f>IF(OR(J142="",F142=""),"",IF(F142&lt;=0,"",IFERROR(J142/F142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K143" s="15">
+        <f>IF(OR(K142="",G142=""),"",IF(G142&lt;=0,"",IFERROR(K142/G142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L143" s="15">
+        <f>IF(OR(L142="",H142=""),"",IF(H142&lt;=0,"",IFERROR(L142/H142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M143" s="15">
+        <f>IF(OR(M142="",I142=""),"",IF(I142&lt;=0,"",IFERROR(M142/I142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N143" s="15">
+        <f>IF(OR(N142="",J142=""),"",IF(J142&lt;=0,"",IFERROR(N142/J142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V143" s="15">
+        <f>IF(OR(V142="",U142=""),"",IF(U142&lt;=0,"",IFERROR(V142/U142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W143" s="15">
+        <f>IF(OR(W142="",V142=""),"",IF(V142&lt;=0,"",IFERROR(W142/V142-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X143" s="15">
+        <f>IF(OR(X142="",W142=""),"",IF(W142&lt;=0,"",IFERROR(X142/W142-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="18" t="inlineStr">
         <is>
-          <t>합계 · Transactions With Other Segments</t>
+          <t>합계 · Revenues From External Customers</t>
         </is>
       </c>
       <c r="C144" s="20" t="n">
-        <v>1065</v>
+        <v>44491</v>
       </c>
       <c r="D144" s="20" t="n">
-        <v>4408</v>
+        <v>47749</v>
       </c>
       <c r="E144" s="20" t="n">
-        <v>1090</v>
+        <v>48557</v>
       </c>
       <c r="F144" s="20" t="n">
-        <v>7424</v>
+        <v>52435</v>
       </c>
       <c r="G144" s="20" t="n">
-        <v>885</v>
+        <v>50565</v>
       </c>
       <c r="H144" s="20" t="n">
-        <v>13592</v>
+        <v>57165</v>
       </c>
       <c r="I144" s="20" t="n">
-        <v>1490</v>
+        <v>51569</v>
       </c>
       <c r="J144" s="20" t="n">
-        <v>11537</v>
+        <v>56709</v>
       </c>
       <c r="K144" s="20" t="n">
-        <v>1657</v>
+        <v>57814</v>
       </c>
       <c r="L144" s="20" t="n">
-        <v>28359</v>
+        <v>67872</v>
       </c>
       <c r="M144" s="20" t="n">
-        <v>1968</v>
+        <v>66679</v>
       </c>
       <c r="N144" s="20" t="n">
-        <v>12661</v>
+        <v>109667</v>
       </c>
       <c r="V144" s="20" t="n">
-        <v>1090</v>
+        <v>48557</v>
       </c>
       <c r="W144" s="20" t="n">
-        <v>1490</v>
+        <v>51569</v>
       </c>
       <c r="X144" s="20" t="n">
-        <v>1968</v>
+        <v>66679</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="18" t="inlineStr">
-        <is>
-          <t>조정액 · Transactions With Other Segments</t>
-        </is>
-      </c>
-      <c r="C145" s="20" t="n">
-        <v>-1065</v>
-      </c>
-      <c r="D145" s="20" t="n">
-        <v>-4408</v>
-      </c>
-      <c r="E145" s="20" t="n">
-        <v>-1090</v>
-      </c>
-      <c r="F145" s="20" t="n">
-        <v>-7424</v>
-      </c>
-      <c r="G145" s="20" t="n">
-        <v>-885</v>
-      </c>
-      <c r="H145" s="20" t="n">
-        <v>-13592</v>
-      </c>
-      <c r="I145" s="20" t="n">
-        <v>-1490</v>
-      </c>
-      <c r="J145" s="20" t="n">
-        <v>-11537</v>
-      </c>
-      <c r="K145" s="20" t="n">
-        <v>-1657</v>
-      </c>
-      <c r="L145" s="20" t="n">
-        <v>-28359</v>
-      </c>
-      <c r="M145" s="20" t="n">
-        <v>-1968</v>
-      </c>
-      <c r="N145" s="20" t="n">
-        <v>-12661</v>
-      </c>
-      <c r="V145" s="20" t="n">
-        <v>-1090</v>
-      </c>
-      <c r="W145" s="20" t="n">
-        <v>-1490</v>
-      </c>
-      <c r="X145" s="20" t="n">
-        <v>-1968</v>
+      <c r="A145" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G145" s="15">
+        <f>IF(OR(G144="",C144=""),"",IF(C144&lt;=0,"",IFERROR(G144/C144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H145" s="15">
+        <f>IF(OR(H144="",D144=""),"",IF(D144&lt;=0,"",IFERROR(H144/D144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I145" s="15">
+        <f>IF(OR(I144="",E144=""),"",IF(E144&lt;=0,"",IFERROR(I144/E144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J145" s="15">
+        <f>IF(OR(J144="",F144=""),"",IF(F144&lt;=0,"",IFERROR(J144/F144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K145" s="15">
+        <f>IF(OR(K144="",G144=""),"",IF(G144&lt;=0,"",IFERROR(K144/G144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L145" s="15">
+        <f>IF(OR(L144="",H144=""),"",IF(H144&lt;=0,"",IFERROR(L144/H144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M145" s="15">
+        <f>IF(OR(M144="",I144=""),"",IF(I144&lt;=0,"",IFERROR(M144/I144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N145" s="15">
+        <f>IF(OR(N144="",J144=""),"",IF(J144&lt;=0,"",IFERROR(N144/J144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V145" s="15">
+        <f>IF(OR(V144="",U144=""),"",IF(U144&lt;=0,"",IFERROR(V144/U144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W145" s="15">
+        <f>IF(OR(W144="",V144=""),"",IF(V144&lt;=0,"",IFERROR(W144/V144-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X145" s="15">
+        <f>IF(OR(X144="",W144=""),"",IF(W144&lt;=0,"",IFERROR(X144/W144-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="18" t="inlineStr">
         <is>
-          <t>Transactions With Other Segments</t>
+          <t>조정액 · Revenues From External Customers</t>
         </is>
       </c>
       <c r="C146" s="20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D146" s="20" t="n">
         <v>0</v>
@@ -9630,2714 +9747,3276 @@
         <v>0</v>
       </c>
       <c r="G146" s="20" t="n">
-        <v>0</v>
+        <v>-81</v>
       </c>
       <c r="H146" s="20" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I146" s="20" t="n">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="J146" s="20" t="n">
+        <v>-103</v>
+      </c>
+      <c r="K146" s="20" t="n">
+        <v>96</v>
+      </c>
+      <c r="L146" s="20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M146" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N146" s="20" t="n">
+        <v>-27</v>
       </c>
       <c r="V146" s="20" t="n">
         <v>0</v>
       </c>
       <c r="W146" s="20" t="n">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="X146" s="20" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="18" t="inlineStr">
-        <is>
-          <t>EntityTotalMember · Transactions With Other Segments</t>
-        </is>
-      </c>
-      <c r="F147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="N147" s="20" t="n">
-        <v>0</v>
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Revenues From External Customers</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="n">
+        <v>44501</v>
+      </c>
+      <c r="D147" s="12" t="n">
+        <v>47749</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>48557</v>
+      </c>
+      <c r="F147" s="12" t="n">
+        <v>52435</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>50484</v>
+      </c>
+      <c r="H147" s="12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="I147" s="12" t="n">
+        <v>51653</v>
+      </c>
+      <c r="V147" s="12" t="n">
+        <v>48557</v>
+      </c>
+      <c r="W147" s="12" t="n">
+        <v>51653</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="18" t="inlineStr">
-        <is>
-          <t>BankingReportableSegmentMember · 계</t>
-        </is>
-      </c>
-      <c r="C148" s="20" t="n">
-        <v>40558</v>
-      </c>
-      <c r="D148" s="20" t="n">
-        <v>43508</v>
-      </c>
-      <c r="E148" s="20" t="n">
-        <v>43948</v>
-      </c>
-      <c r="F148" s="20" t="n">
-        <v>48201</v>
-      </c>
-      <c r="G148" s="20" t="n">
-        <v>44154</v>
-      </c>
-      <c r="H148" s="20" t="n">
-        <v>52646</v>
-      </c>
-      <c r="I148" s="20" t="n">
-        <v>47032</v>
-      </c>
-      <c r="J148" s="20" t="n">
-        <v>52053</v>
-      </c>
-      <c r="K148" s="20" t="n">
-        <v>52601</v>
-      </c>
-      <c r="L148" s="20" t="n">
-        <v>62304</v>
-      </c>
-      <c r="M148" s="20" t="n">
-        <v>61392</v>
-      </c>
-      <c r="N148" s="20" t="n">
-        <v>99412</v>
-      </c>
-      <c r="V148" s="20" t="n">
-        <v>43948</v>
-      </c>
-      <c r="W148" s="20" t="n">
-        <v>47032</v>
-      </c>
-      <c r="X148" s="20" t="n">
-        <v>61392</v>
+      <c r="A148" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G148" s="15">
+        <f>IF(OR(G147="",C147=""),"",IF(C147&lt;=0,"",IFERROR(G147/C147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H148" s="15">
+        <f>IF(OR(H147="",D147=""),"",IF(D147&lt;=0,"",IFERROR(H147/D147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I148" s="15">
+        <f>IF(OR(I147="",E147=""),"",IF(E147&lt;=0,"",IFERROR(I147/E147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V148" s="15">
+        <f>IF(OR(V147="",U147=""),"",IF(U147&lt;=0,"",IFERROR(V147/U147-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W148" s="15">
+        <f>IF(OR(W147="",V147=""),"",IF(V147&lt;=0,"",IFERROR(W147/V147-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="18" t="inlineStr">
         <is>
-          <t>LeasingReportableSegmentMember · 계</t>
-        </is>
-      </c>
-      <c r="C149" s="20" t="n">
-        <v>2801</v>
-      </c>
-      <c r="D149" s="20" t="n">
-        <v>3124</v>
-      </c>
-      <c r="E149" s="20" t="n">
-        <v>3398</v>
+          <t>EntityTotalMember · Revenues From External Customers</t>
+        </is>
       </c>
       <c r="F149" s="20" t="n">
-        <v>3097</v>
-      </c>
-      <c r="G149" s="20" t="n">
-        <v>5021</v>
-      </c>
-      <c r="H149" s="20" t="n">
-        <v>3346</v>
-      </c>
-      <c r="I149" s="20" t="n">
-        <v>3251</v>
+        <v>52435</v>
       </c>
       <c r="J149" s="20" t="n">
-        <v>3497</v>
-      </c>
-      <c r="K149" s="20" t="n">
-        <v>3617</v>
-      </c>
-      <c r="L149" s="20" t="n">
-        <v>3723</v>
-      </c>
-      <c r="M149" s="20" t="n">
-        <v>3742</v>
+        <v>56606</v>
       </c>
       <c r="N149" s="20" t="n">
-        <v>8276</v>
-      </c>
-      <c r="V149" s="20" t="n">
-        <v>3398</v>
-      </c>
-      <c r="W149" s="20" t="n">
-        <v>3251</v>
-      </c>
-      <c r="X149" s="20" t="n">
-        <v>3742</v>
+        <v>109640</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="18" t="inlineStr">
         <is>
-          <t>SecuritiesReportableSegmentMember · 계</t>
+          <t>BankingReportableSegmentMember · Transactions With Other Segments</t>
         </is>
       </c>
       <c r="C150" s="20" t="n">
-        <v>1065</v>
+        <v>517</v>
       </c>
       <c r="D150" s="20" t="n">
-        <v>892</v>
+        <v>363</v>
       </c>
       <c r="E150" s="20" t="n">
-        <v>1061</v>
+        <v>538</v>
       </c>
       <c r="F150" s="20" t="n">
-        <v>1242</v>
+        <v>719</v>
       </c>
       <c r="G150" s="20" t="n">
-        <v>956</v>
+        <v>238</v>
       </c>
       <c r="H150" s="20" t="n">
-        <v>870</v>
+        <v>435</v>
       </c>
       <c r="I150" s="20" t="n">
-        <v>907</v>
+        <v>391</v>
       </c>
       <c r="J150" s="20" t="n">
-        <v>865</v>
+        <v>408</v>
       </c>
       <c r="K150" s="20" t="n">
-        <v>1194</v>
+        <v>512</v>
       </c>
       <c r="L150" s="20" t="n">
-        <v>1602</v>
+        <v>642</v>
       </c>
       <c r="M150" s="20" t="n">
-        <v>1402</v>
+        <v>716</v>
       </c>
       <c r="N150" s="20" t="n">
-        <v>1592</v>
+        <v>660</v>
       </c>
       <c r="V150" s="20" t="n">
-        <v>1061</v>
+        <v>538</v>
       </c>
       <c r="W150" s="20" t="n">
-        <v>907</v>
+        <v>391</v>
       </c>
       <c r="X150" s="20" t="n">
-        <v>1402</v>
+        <v>716</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 계</t>
+          <t>LeasingReportableSegmentMember · Transactions With Other Segments</t>
         </is>
       </c>
       <c r="C151" s="20" t="n">
-        <v>44424</v>
+        <v>41</v>
       </c>
       <c r="D151" s="20" t="n">
-        <v>47524</v>
+        <v>39</v>
       </c>
       <c r="E151" s="20" t="n">
-        <v>48407</v>
+        <v>44</v>
       </c>
       <c r="F151" s="20" t="n">
-        <v>52541</v>
+        <v>41</v>
       </c>
       <c r="G151" s="20" t="n">
-        <v>50131</v>
+        <v>40</v>
       </c>
       <c r="H151" s="20" t="n">
-        <v>56862</v>
+        <v>40</v>
       </c>
       <c r="I151" s="20" t="n">
-        <v>51190</v>
+        <v>41</v>
       </c>
       <c r="J151" s="20" t="n">
-        <v>56415</v>
+        <v>39</v>
       </c>
       <c r="K151" s="20" t="n">
-        <v>57413</v>
+        <v>41</v>
       </c>
       <c r="L151" s="20" t="n">
-        <v>67629</v>
+        <v>40</v>
       </c>
       <c r="M151" s="20" t="n">
-        <v>66535</v>
+        <v>43</v>
       </c>
       <c r="N151" s="20" t="n">
-        <v>109281</v>
+        <v>43</v>
       </c>
       <c r="V151" s="20" t="n">
-        <v>48407</v>
+        <v>44</v>
       </c>
       <c r="W151" s="20" t="n">
-        <v>51190</v>
+        <v>41</v>
       </c>
       <c r="X151" s="20" t="n">
-        <v>66535</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="18" t="inlineStr">
         <is>
-          <t>기타 · 계</t>
+          <t>SecuritiesReportableSegmentMember · Transactions With Other Segments</t>
         </is>
       </c>
       <c r="C152" s="20" t="n">
-        <v>1131</v>
+        <v>20</v>
       </c>
       <c r="D152" s="20" t="n">
-        <v>4633</v>
+        <v>21</v>
       </c>
       <c r="E152" s="20" t="n">
-        <v>1240</v>
+        <v>22</v>
       </c>
       <c r="F152" s="20" t="n">
-        <v>7318</v>
+        <v>23</v>
       </c>
       <c r="G152" s="20" t="n">
-        <v>1319</v>
+        <v>24</v>
       </c>
       <c r="H152" s="20" t="n">
-        <v>13894</v>
+        <v>23</v>
       </c>
       <c r="I152" s="20" t="n">
-        <v>1870</v>
+        <v>26</v>
       </c>
       <c r="J152" s="20" t="n">
-        <v>11831</v>
+        <v>23</v>
       </c>
       <c r="K152" s="20" t="n">
-        <v>2058</v>
+        <v>29</v>
       </c>
       <c r="L152" s="20" t="n">
-        <v>28602</v>
+        <v>27</v>
       </c>
       <c r="M152" s="20" t="n">
-        <v>2112</v>
+        <v>33</v>
       </c>
       <c r="N152" s="20" t="n">
-        <v>13047</v>
+        <v>30</v>
       </c>
       <c r="V152" s="20" t="n">
-        <v>1240</v>
+        <v>22</v>
       </c>
       <c r="W152" s="20" t="n">
-        <v>1870</v>
+        <v>26</v>
       </c>
       <c r="X152" s="20" t="n">
-        <v>2112</v>
+        <v>33</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="18" t="inlineStr">
         <is>
-          <t>합계 · 계</t>
+          <t>보고부문 합계 · Transactions With Other Segments</t>
         </is>
       </c>
       <c r="C153" s="20" t="n">
-        <v>45555</v>
+        <v>577</v>
       </c>
       <c r="D153" s="20" t="n">
-        <v>52158</v>
+        <v>422</v>
       </c>
       <c r="E153" s="20" t="n">
-        <v>49646</v>
+        <v>604</v>
       </c>
       <c r="F153" s="20" t="n">
-        <v>59859</v>
+        <v>784</v>
       </c>
       <c r="G153" s="20" t="n">
-        <v>51451</v>
+        <v>301</v>
       </c>
       <c r="H153" s="20" t="n">
-        <v>70756</v>
+        <v>499</v>
       </c>
       <c r="I153" s="20" t="n">
-        <v>53059</v>
+        <v>459</v>
       </c>
       <c r="J153" s="20" t="n">
-        <v>68247</v>
+        <v>471</v>
       </c>
       <c r="K153" s="20" t="n">
-        <v>59470</v>
+        <v>582</v>
       </c>
       <c r="L153" s="20" t="n">
-        <v>96232</v>
+        <v>710</v>
       </c>
       <c r="M153" s="20" t="n">
-        <v>68647</v>
+        <v>792</v>
       </c>
       <c r="N153" s="20" t="n">
-        <v>122329</v>
+        <v>735</v>
       </c>
       <c r="V153" s="20" t="n">
-        <v>49646</v>
+        <v>604</v>
       </c>
       <c r="W153" s="20" t="n">
-        <v>53059</v>
+        <v>459</v>
       </c>
       <c r="X153" s="20" t="n">
-        <v>68647</v>
+        <v>792</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="18" t="inlineStr">
         <is>
-          <t>조정액 · 계</t>
+          <t>기타 · Transactions With Other Segments</t>
         </is>
       </c>
       <c r="C154" s="20" t="n">
-        <v>-1054</v>
+        <v>487</v>
       </c>
       <c r="D154" s="20" t="n">
-        <v>-4408</v>
+        <v>3986</v>
       </c>
       <c r="E154" s="20" t="n">
-        <v>-1090</v>
+        <v>486</v>
       </c>
       <c r="F154" s="20" t="n">
-        <v>-7424</v>
+        <v>6640</v>
       </c>
       <c r="G154" s="20" t="n">
-        <v>-966</v>
+        <v>584</v>
       </c>
       <c r="H154" s="20" t="n">
-        <v>-13595</v>
+        <v>13092</v>
       </c>
       <c r="I154" s="20" t="n">
-        <v>-1406</v>
+        <v>1031</v>
       </c>
       <c r="J154" s="20" t="n">
-        <v>-11640</v>
+        <v>11065</v>
       </c>
       <c r="K154" s="20" t="n">
-        <v>-1561</v>
+        <v>1075</v>
       </c>
       <c r="L154" s="20" t="n">
-        <v>-28361</v>
+        <v>27649</v>
       </c>
       <c r="M154" s="20" t="n">
-        <v>-1959</v>
+        <v>1177</v>
       </c>
       <c r="N154" s="20" t="n">
-        <v>-12689</v>
+        <v>11926</v>
       </c>
       <c r="V154" s="20" t="n">
-        <v>-1090</v>
+        <v>486</v>
       </c>
       <c r="W154" s="20" t="n">
-        <v>-1406</v>
+        <v>1031</v>
       </c>
       <c r="X154" s="20" t="n">
-        <v>-1959</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>계</t>
-        </is>
-      </c>
-      <c r="C155" s="12" t="n">
-        <v>44501</v>
-      </c>
-      <c r="D155" s="12" t="n">
-        <v>47749</v>
-      </c>
-      <c r="E155" s="12" t="n">
-        <v>48557</v>
-      </c>
-      <c r="F155" s="12" t="n">
-        <v>52435</v>
-      </c>
-      <c r="G155" s="12" t="n">
-        <v>50484</v>
-      </c>
-      <c r="H155" s="12" t="n">
-        <v>57162</v>
-      </c>
-      <c r="I155" s="12" t="n">
-        <v>51653</v>
-      </c>
-      <c r="V155" s="12" t="n">
-        <v>48557</v>
-      </c>
-      <c r="W155" s="12" t="n">
-        <v>51653</v>
+      <c r="A155" s="18" t="inlineStr">
+        <is>
+          <t>합계 · Transactions With Other Segments</t>
+        </is>
+      </c>
+      <c r="C155" s="20" t="n">
+        <v>1065</v>
+      </c>
+      <c r="D155" s="20" t="n">
+        <v>4408</v>
+      </c>
+      <c r="E155" s="20" t="n">
+        <v>1090</v>
+      </c>
+      <c r="F155" s="20" t="n">
+        <v>7424</v>
+      </c>
+      <c r="G155" s="20" t="n">
+        <v>885</v>
+      </c>
+      <c r="H155" s="20" t="n">
+        <v>13592</v>
+      </c>
+      <c r="I155" s="20" t="n">
+        <v>1490</v>
+      </c>
+      <c r="J155" s="20" t="n">
+        <v>11537</v>
+      </c>
+      <c r="K155" s="20" t="n">
+        <v>1657</v>
+      </c>
+      <c r="L155" s="20" t="n">
+        <v>28359</v>
+      </c>
+      <c r="M155" s="20" t="n">
+        <v>1968</v>
+      </c>
+      <c r="N155" s="20" t="n">
+        <v>12661</v>
+      </c>
+      <c r="V155" s="20" t="n">
+        <v>1090</v>
+      </c>
+      <c r="W155" s="20" t="n">
+        <v>1490</v>
+      </c>
+      <c r="X155" s="20" t="n">
+        <v>1968</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · 계</t>
-        </is>
+          <t>조정액 · Transactions With Other Segments</t>
+        </is>
+      </c>
+      <c r="C156" s="20" t="n">
+        <v>-1065</v>
+      </c>
+      <c r="D156" s="20" t="n">
+        <v>-4408</v>
+      </c>
+      <c r="E156" s="20" t="n">
+        <v>-1090</v>
       </c>
       <c r="F156" s="20" t="n">
-        <v>52435</v>
+        <v>-7424</v>
+      </c>
+      <c r="G156" s="20" t="n">
+        <v>-885</v>
+      </c>
+      <c r="H156" s="20" t="n">
+        <v>-13592</v>
+      </c>
+      <c r="I156" s="20" t="n">
+        <v>-1490</v>
       </c>
       <c r="J156" s="20" t="n">
-        <v>56606</v>
+        <v>-11537</v>
+      </c>
+      <c r="K156" s="20" t="n">
+        <v>-1657</v>
+      </c>
+      <c r="L156" s="20" t="n">
+        <v>-28359</v>
+      </c>
+      <c r="M156" s="20" t="n">
+        <v>-1968</v>
       </c>
       <c r="N156" s="20" t="n">
-        <v>109640</v>
+        <v>-12661</v>
+      </c>
+      <c r="V156" s="20" t="n">
+        <v>-1090</v>
+      </c>
+      <c r="W156" s="20" t="n">
+        <v>-1490</v>
+      </c>
+      <c r="X156" s="20" t="n">
+        <v>-1968</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="18" t="inlineStr">
         <is>
-          <t>BankingReportableSegmentMember · 부문 이익</t>
+          <t>Transactions With Other Segments</t>
         </is>
       </c>
       <c r="C157" s="20" t="n">
-        <v>4371</v>
+        <v>0</v>
       </c>
       <c r="D157" s="20" t="n">
-        <v>10554</v>
+        <v>0</v>
       </c>
       <c r="E157" s="20" t="n">
-        <v>4153</v>
+        <v>0</v>
       </c>
       <c r="F157" s="20" t="n">
-        <v>13033</v>
+        <v>0</v>
       </c>
       <c r="G157" s="20" t="n">
-        <v>6230</v>
+        <v>0</v>
       </c>
       <c r="H157" s="20" t="n">
-        <v>7961</v>
+        <v>0</v>
       </c>
       <c r="I157" s="20" t="n">
-        <v>8572</v>
-      </c>
-      <c r="J157" s="20" t="n">
-        <v>14326</v>
-      </c>
-      <c r="K157" s="20" t="n">
-        <v>9267</v>
-      </c>
-      <c r="L157" s="20" t="n">
-        <v>19024</v>
-      </c>
-      <c r="M157" s="20" t="n">
-        <v>9863</v>
-      </c>
-      <c r="N157" s="20" t="n">
-        <v>18687</v>
+        <v>0</v>
       </c>
       <c r="V157" s="20" t="n">
-        <v>4153</v>
+        <v>0</v>
       </c>
       <c r="W157" s="20" t="n">
-        <v>8572</v>
-      </c>
-      <c r="X157" s="20" t="n">
-        <v>9863</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="18" t="inlineStr">
         <is>
-          <t>LeasingReportableSegmentMember · 부문 이익</t>
-        </is>
-      </c>
-      <c r="C158" s="20" t="n">
-        <v>38</v>
-      </c>
-      <c r="D158" s="20" t="n">
-        <v>384</v>
-      </c>
-      <c r="E158" s="20" t="n">
-        <v>252</v>
+          <t>EntityTotalMember · Transactions With Other Segments</t>
+        </is>
       </c>
       <c r="F158" s="20" t="n">
-        <v>139</v>
-      </c>
-      <c r="G158" s="20" t="n">
-        <v>615</v>
-      </c>
-      <c r="H158" s="20" t="n">
-        <v>129</v>
-      </c>
-      <c r="I158" s="20" t="n">
-        <v>-198</v>
+        <v>0</v>
       </c>
       <c r="J158" s="20" t="n">
-        <v>100</v>
-      </c>
-      <c r="K158" s="20" t="n">
-        <v>183</v>
-      </c>
-      <c r="L158" s="20" t="n">
-        <v>210</v>
-      </c>
-      <c r="M158" s="20" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="N158" s="20" t="n">
-        <v>298</v>
-      </c>
-      <c r="V158" s="20" t="n">
-        <v>252</v>
-      </c>
-      <c r="W158" s="20" t="n">
-        <v>-198</v>
-      </c>
-      <c r="X158" s="20" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="18" t="inlineStr">
         <is>
-          <t>SecuritiesReportableSegmentMember · 부문 이익</t>
+          <t>BankingReportableSegmentMember · 계</t>
         </is>
       </c>
       <c r="C159" s="20" t="n">
-        <v>226</v>
+        <v>40558</v>
       </c>
       <c r="D159" s="20" t="n">
-        <v>162</v>
+        <v>43508</v>
       </c>
       <c r="E159" s="20" t="n">
-        <v>236</v>
+        <v>43948</v>
       </c>
       <c r="F159" s="20" t="n">
-        <v>354</v>
+        <v>48201</v>
       </c>
       <c r="G159" s="20" t="n">
-        <v>215</v>
+        <v>44154</v>
       </c>
       <c r="H159" s="20" t="n">
-        <v>137</v>
+        <v>52646</v>
       </c>
       <c r="I159" s="20" t="n">
-        <v>162</v>
+        <v>47032</v>
       </c>
       <c r="J159" s="20" t="n">
-        <v>110</v>
+        <v>52053</v>
       </c>
       <c r="K159" s="20" t="n">
-        <v>306</v>
+        <v>52601</v>
       </c>
       <c r="L159" s="20" t="n">
-        <v>567</v>
+        <v>62304</v>
       </c>
       <c r="M159" s="20" t="n">
-        <v>377</v>
+        <v>61392</v>
       </c>
       <c r="N159" s="20" t="n">
-        <v>524</v>
+        <v>99412</v>
       </c>
       <c r="V159" s="20" t="n">
-        <v>236</v>
+        <v>43948</v>
       </c>
       <c r="W159" s="20" t="n">
-        <v>162</v>
+        <v>47032</v>
       </c>
       <c r="X159" s="20" t="n">
-        <v>377</v>
+        <v>61392</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="18" t="inlineStr">
         <is>
-          <t>보고부문 합계 · 부문 이익</t>
+          <t>LeasingReportableSegmentMember · 계</t>
         </is>
       </c>
       <c r="C160" s="20" t="n">
-        <v>4636</v>
+        <v>2801</v>
       </c>
       <c r="D160" s="20" t="n">
-        <v>11099</v>
+        <v>3124</v>
       </c>
       <c r="E160" s="20" t="n">
-        <v>4641</v>
+        <v>3398</v>
       </c>
       <c r="F160" s="20" t="n">
-        <v>13526</v>
+        <v>3097</v>
       </c>
       <c r="G160" s="20" t="n">
-        <v>7061</v>
+        <v>5021</v>
       </c>
       <c r="H160" s="20" t="n">
-        <v>8227</v>
+        <v>3346</v>
       </c>
       <c r="I160" s="20" t="n">
-        <v>8537</v>
+        <v>3251</v>
       </c>
       <c r="J160" s="20" t="n">
-        <v>14537</v>
+        <v>3497</v>
       </c>
       <c r="K160" s="20" t="n">
-        <v>9756</v>
+        <v>3617</v>
       </c>
       <c r="L160" s="20" t="n">
-        <v>19801</v>
+        <v>3723</v>
       </c>
       <c r="M160" s="20" t="n">
-        <v>10298</v>
+        <v>3742</v>
       </c>
       <c r="N160" s="20" t="n">
-        <v>19509</v>
+        <v>8276</v>
       </c>
       <c r="V160" s="20" t="n">
-        <v>4641</v>
+        <v>3398</v>
       </c>
       <c r="W160" s="20" t="n">
-        <v>8537</v>
+        <v>3251</v>
       </c>
       <c r="X160" s="20" t="n">
-        <v>10298</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="18" t="inlineStr">
         <is>
-          <t>기타 · 부문 이익</t>
+          <t>SecuritiesReportableSegmentMember · 계</t>
         </is>
       </c>
       <c r="C161" s="20" t="n">
-        <v>124</v>
+        <v>1065</v>
       </c>
       <c r="D161" s="20" t="n">
-        <v>3681</v>
+        <v>892</v>
       </c>
       <c r="E161" s="20" t="n">
-        <v>194</v>
+        <v>1061</v>
       </c>
       <c r="F161" s="20" t="n">
-        <v>6267</v>
+        <v>1242</v>
       </c>
       <c r="G161" s="20" t="n">
-        <v>168</v>
+        <v>956</v>
       </c>
       <c r="H161" s="20" t="n">
-        <v>12492</v>
+        <v>870</v>
       </c>
       <c r="I161" s="20" t="n">
-        <v>555</v>
+        <v>907</v>
       </c>
       <c r="J161" s="20" t="n">
-        <v>10459</v>
+        <v>865</v>
       </c>
       <c r="K161" s="20" t="n">
-        <v>468</v>
+        <v>1194</v>
       </c>
       <c r="L161" s="20" t="n">
-        <v>26967</v>
+        <v>1602</v>
       </c>
       <c r="M161" s="20" t="n">
-        <v>391</v>
+        <v>1402</v>
       </c>
       <c r="N161" s="20" t="n">
-        <v>11422</v>
+        <v>1592</v>
       </c>
       <c r="V161" s="20" t="n">
-        <v>194</v>
+        <v>1061</v>
       </c>
       <c r="W161" s="20" t="n">
-        <v>555</v>
+        <v>907</v>
       </c>
       <c r="X161" s="20" t="n">
-        <v>391</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="18" t="inlineStr">
         <is>
-          <t>합계 · 부문 이익</t>
+          <t>보고부문 합계 · 계</t>
         </is>
       </c>
       <c r="C162" s="20" t="n">
-        <v>4760</v>
+        <v>44424</v>
       </c>
       <c r="D162" s="20" t="n">
-        <v>14780</v>
+        <v>47524</v>
       </c>
       <c r="E162" s="20" t="n">
-        <v>4835</v>
+        <v>48407</v>
       </c>
       <c r="F162" s="20" t="n">
-        <v>19794</v>
+        <v>52541</v>
       </c>
       <c r="G162" s="20" t="n">
-        <v>7228</v>
+        <v>50131</v>
       </c>
       <c r="H162" s="20" t="n">
-        <v>20719</v>
+        <v>56862</v>
       </c>
       <c r="I162" s="20" t="n">
-        <v>9092</v>
+        <v>51190</v>
       </c>
       <c r="J162" s="20" t="n">
-        <v>24996</v>
+        <v>56415</v>
       </c>
       <c r="K162" s="20" t="n">
-        <v>10224</v>
+        <v>57413</v>
       </c>
       <c r="L162" s="20" t="n">
-        <v>46769</v>
+        <v>67629</v>
       </c>
       <c r="M162" s="20" t="n">
-        <v>10689</v>
+        <v>66535</v>
       </c>
       <c r="N162" s="20" t="n">
-        <v>30932</v>
+        <v>109281</v>
       </c>
       <c r="V162" s="20" t="n">
-        <v>4835</v>
+        <v>48407</v>
       </c>
       <c r="W162" s="20" t="n">
-        <v>9092</v>
+        <v>51190</v>
       </c>
       <c r="X162" s="20" t="n">
-        <v>10689</v>
+        <v>66535</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="18" t="inlineStr">
         <is>
-          <t>조정액 · 부문 이익</t>
+          <t>기타 · 계</t>
         </is>
       </c>
       <c r="C163" s="20" t="n">
-        <v>1</v>
+        <v>1131</v>
       </c>
       <c r="D163" s="20" t="n">
-        <v>-3496</v>
+        <v>4633</v>
       </c>
       <c r="E163" s="20" t="n">
-        <v>37</v>
+        <v>1240</v>
       </c>
       <c r="F163" s="20" t="n">
-        <v>-6065</v>
+        <v>7318</v>
       </c>
       <c r="G163" s="20" t="n">
-        <v>27</v>
+        <v>1319</v>
       </c>
       <c r="H163" s="20" t="n">
-        <v>-12492</v>
+        <v>13894</v>
       </c>
       <c r="I163" s="20" t="n">
-        <v>5</v>
+        <v>1870</v>
       </c>
       <c r="J163" s="20" t="n">
-        <v>-10012</v>
+        <v>11831</v>
       </c>
       <c r="K163" s="20" t="n">
-        <v>-7</v>
+        <v>2058</v>
       </c>
       <c r="L163" s="20" t="n">
-        <v>-26474</v>
+        <v>28602</v>
       </c>
       <c r="M163" s="20" t="n">
-        <v>-146</v>
+        <v>2112</v>
       </c>
       <c r="N163" s="20" t="n">
-        <v>-10663</v>
+        <v>13047</v>
       </c>
       <c r="V163" s="20" t="n">
-        <v>37</v>
+        <v>1240</v>
       </c>
       <c r="W163" s="20" t="n">
-        <v>5</v>
+        <v>1870</v>
       </c>
       <c r="X163" s="20" t="n">
-        <v>-146</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="9" t="inlineStr">
-        <is>
-          <t>부문 이익</t>
-        </is>
-      </c>
-      <c r="C164" s="12" t="n">
-        <v>4761</v>
-      </c>
-      <c r="D164" s="12" t="n">
-        <v>11283</v>
-      </c>
-      <c r="E164" s="12" t="n">
-        <v>4872</v>
-      </c>
-      <c r="F164" s="12" t="n">
-        <v>13728</v>
-      </c>
-      <c r="G164" s="12" t="n">
-        <v>7256</v>
-      </c>
-      <c r="H164" s="12" t="n">
-        <v>8226</v>
-      </c>
-      <c r="I164" s="12" t="n">
-        <v>9098</v>
-      </c>
-      <c r="V164" s="12" t="n">
-        <v>4872</v>
-      </c>
-      <c r="W164" s="12" t="n">
-        <v>9098</v>
+      <c r="A164" s="18" t="inlineStr">
+        <is>
+          <t>합계 · 계</t>
+        </is>
+      </c>
+      <c r="C164" s="20" t="n">
+        <v>45555</v>
+      </c>
+      <c r="D164" s="20" t="n">
+        <v>52158</v>
+      </c>
+      <c r="E164" s="20" t="n">
+        <v>49646</v>
+      </c>
+      <c r="F164" s="20" t="n">
+        <v>59859</v>
+      </c>
+      <c r="G164" s="20" t="n">
+        <v>51451</v>
+      </c>
+      <c r="H164" s="20" t="n">
+        <v>70756</v>
+      </c>
+      <c r="I164" s="20" t="n">
+        <v>53059</v>
+      </c>
+      <c r="J164" s="20" t="n">
+        <v>68247</v>
+      </c>
+      <c r="K164" s="20" t="n">
+        <v>59470</v>
+      </c>
+      <c r="L164" s="20" t="n">
+        <v>96232</v>
+      </c>
+      <c r="M164" s="20" t="n">
+        <v>68647</v>
+      </c>
+      <c r="N164" s="20" t="n">
+        <v>122329</v>
+      </c>
+      <c r="V164" s="20" t="n">
+        <v>49646</v>
+      </c>
+      <c r="W164" s="20" t="n">
+        <v>53059</v>
+      </c>
+      <c r="X164" s="20" t="n">
+        <v>68647</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="18" t="inlineStr">
         <is>
-          <t>EntityTotalMember · 부문 이익</t>
-        </is>
+          <t>조정액 · 계</t>
+        </is>
+      </c>
+      <c r="C165" s="20" t="n">
+        <v>-1054</v>
+      </c>
+      <c r="D165" s="20" t="n">
+        <v>-4408</v>
+      </c>
+      <c r="E165" s="20" t="n">
+        <v>-1090</v>
       </c>
       <c r="F165" s="20" t="n">
-        <v>13728</v>
+        <v>-7424</v>
+      </c>
+      <c r="G165" s="20" t="n">
+        <v>-966</v>
+      </c>
+      <c r="H165" s="20" t="n">
+        <v>-13595</v>
+      </c>
+      <c r="I165" s="20" t="n">
+        <v>-1406</v>
       </c>
       <c r="J165" s="20" t="n">
-        <v>14984</v>
+        <v>-11640</v>
+      </c>
+      <c r="K165" s="20" t="n">
+        <v>-1561</v>
+      </c>
+      <c r="L165" s="20" t="n">
+        <v>-28361</v>
+      </c>
+      <c r="M165" s="20" t="n">
+        <v>-1959</v>
       </c>
       <c r="N165" s="20" t="n">
-        <v>20269</v>
+        <v>-12689</v>
+      </c>
+      <c r="V165" s="20" t="n">
+        <v>-1090</v>
+      </c>
+      <c r="W165" s="20" t="n">
+        <v>-1406</v>
+      </c>
+      <c r="X165" s="20" t="n">
+        <v>-1959</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="9" t="inlineStr">
+        <is>
+          <t>계</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="n">
+        <v>44501</v>
+      </c>
+      <c r="D166" s="12" t="n">
+        <v>47749</v>
+      </c>
+      <c r="E166" s="12" t="n">
+        <v>48557</v>
+      </c>
+      <c r="F166" s="12" t="n">
+        <v>52435</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>50484</v>
+      </c>
+      <c r="H166" s="12" t="n">
+        <v>57162</v>
+      </c>
+      <c r="I166" s="12" t="n">
+        <v>51653</v>
+      </c>
+      <c r="V166" s="12" t="n">
+        <v>48557</v>
+      </c>
+      <c r="W166" s="12" t="n">
+        <v>51653</v>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="16" t="inlineStr">
-        <is>
-          <t>현금흐름표 · 전 항목</t>
-        </is>
-      </c>
-      <c r="B167" s="42" t="inlineStr">
-        <is>
-          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
-        </is>
-      </c>
-      <c r="C167" s="16" t="n"/>
-      <c r="D167" s="16" t="n"/>
-      <c r="E167" s="16" t="n"/>
-      <c r="F167" s="16" t="n"/>
-      <c r="G167" s="16" t="n"/>
-      <c r="H167" s="16" t="n"/>
-      <c r="I167" s="16" t="n"/>
-      <c r="J167" s="16" t="n"/>
-      <c r="K167" s="16" t="n"/>
-      <c r="L167" s="16" t="n"/>
-      <c r="M167" s="16" t="n"/>
-      <c r="N167" s="16" t="n"/>
-      <c r="O167" s="16" t="n"/>
-      <c r="P167" s="16" t="n"/>
-      <c r="Q167" s="16" t="n"/>
-      <c r="R167" s="16" t="n"/>
-      <c r="S167" s="16" t="n"/>
-      <c r="T167" s="16" t="n"/>
-      <c r="U167" s="16" t="n"/>
-      <c r="V167" s="16" t="n"/>
-      <c r="W167" s="16" t="n"/>
-      <c r="X167" s="16" t="n"/>
-      <c r="Y167" s="16" t="n"/>
-      <c r="Z167" s="16" t="n"/>
-      <c r="AA167" s="16" t="n"/>
-      <c r="AB167" s="16" t="n"/>
-      <c r="AC167" s="16" t="n"/>
+      <c r="A167" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G167" s="15">
+        <f>IF(OR(G166="",C166=""),"",IF(C166&lt;=0,"",IFERROR(G166/C166-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H167" s="15">
+        <f>IF(OR(H166="",D166=""),"",IF(D166&lt;=0,"",IFERROR(H166/D166-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I167" s="15">
+        <f>IF(OR(I166="",E166=""),"",IF(E166&lt;=0,"",IFERROR(I166/E166-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V167" s="15">
+        <f>IF(OR(V166="",U166=""),"",IF(U166&lt;=0,"",IFERROR(V166/U166-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W167" s="15">
+        <f>IF(OR(W166="",V166=""),"",IF(V166&lt;=0,"",IFERROR(W166/V166-1,"")))</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="inlineStr">
-        <is>
-          <t>항목</t>
-        </is>
-      </c>
-      <c r="B168" s="5" t="inlineStr">
-        <is>
-          <t>참고</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>2024.2Q</t>
-        </is>
-      </c>
-      <c r="D168" s="5" t="inlineStr">
-        <is>
-          <t>2024.3Q</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>2024.4Q</t>
-        </is>
-      </c>
-      <c r="F168" s="5" t="inlineStr">
-        <is>
-          <t>2025.1Q</t>
-        </is>
-      </c>
-      <c r="G168" s="5" t="inlineStr">
-        <is>
-          <t>2025.2Q</t>
-        </is>
-      </c>
-      <c r="H168" s="5" t="inlineStr">
-        <is>
-          <t>2025.3Q</t>
-        </is>
-      </c>
-      <c r="I168" s="5" t="inlineStr">
-        <is>
-          <t>2025.4Q</t>
-        </is>
-      </c>
-      <c r="J168" s="5" t="inlineStr">
-        <is>
-          <t>2026.1Q</t>
-        </is>
-      </c>
-      <c r="K168" s="5" t="inlineStr">
-        <is>
-          <t>2026.2Q</t>
-        </is>
-      </c>
-      <c r="L168" s="5" t="inlineStr">
-        <is>
-          <t>2026.3Q</t>
-        </is>
-      </c>
-      <c r="M168" s="5" t="inlineStr">
-        <is>
-          <t>2026.4Q</t>
-        </is>
-      </c>
-      <c r="N168" s="5" t="inlineStr">
-        <is>
-          <t>2027.1Q</t>
-        </is>
-      </c>
-      <c r="O168" s="5" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="P168" s="5" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="Q168" s="5" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="R168" s="5" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="S168" s="5" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="T168" s="5" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="U168" s="5" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="V168" s="5" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="W168" s="5" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="X168" s="5" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Y168" s="5" t="inlineStr">
-        <is>
-          <t>2027(MW)</t>
-        </is>
-      </c>
-      <c r="Z168" s="5" t="inlineStr">
-        <is>
-          <t>2028(MW)</t>
-        </is>
-      </c>
-      <c r="AA168" s="5" t="inlineStr">
-        <is>
-          <t>2029(MW)</t>
-        </is>
-      </c>
-      <c r="AB168" s="5" t="inlineStr">
-        <is>
-          <t>2030(MW)</t>
-        </is>
-      </c>
-      <c r="AC168" s="5" t="inlineStr">
-        <is>
-          <t>2031(MW)</t>
-        </is>
+      <c r="A168" s="18" t="inlineStr">
+        <is>
+          <t>EntityTotalMember · 계</t>
+        </is>
+      </c>
+      <c r="F168" s="20" t="n">
+        <v>52435</v>
+      </c>
+      <c r="J168" s="20" t="n">
+        <v>56606</v>
+      </c>
+      <c r="N168" s="20" t="n">
+        <v>109640</v>
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="E169" s="12" t="n">
-        <v>30899</v>
-      </c>
-      <c r="I169" s="12" t="n">
-        <v>38282</v>
-      </c>
-      <c r="M169" s="12" t="n">
-        <v>55666</v>
-      </c>
-      <c r="U169" s="12" t="n">
-        <v>29518</v>
-      </c>
-      <c r="V169" s="12" t="n">
-        <v>30899</v>
-      </c>
-      <c r="W169" s="12" t="n">
-        <v>38282</v>
-      </c>
-      <c r="X169" s="12" t="n">
-        <v>55666</v>
+      <c r="A169" s="18" t="inlineStr">
+        <is>
+          <t>BankingReportableSegmentMember · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C169" s="20" t="n">
+        <v>4371</v>
+      </c>
+      <c r="D169" s="20" t="n">
+        <v>10554</v>
+      </c>
+      <c r="E169" s="20" t="n">
+        <v>4153</v>
+      </c>
+      <c r="F169" s="20" t="n">
+        <v>13033</v>
+      </c>
+      <c r="G169" s="20" t="n">
+        <v>6230</v>
+      </c>
+      <c r="H169" s="20" t="n">
+        <v>7961</v>
+      </c>
+      <c r="I169" s="20" t="n">
+        <v>8572</v>
+      </c>
+      <c r="J169" s="20" t="n">
+        <v>14326</v>
+      </c>
+      <c r="K169" s="20" t="n">
+        <v>9267</v>
+      </c>
+      <c r="L169" s="20" t="n">
+        <v>19024</v>
+      </c>
+      <c r="M169" s="20" t="n">
+        <v>9863</v>
+      </c>
+      <c r="N169" s="20" t="n">
+        <v>18687</v>
+      </c>
+      <c r="V169" s="20" t="n">
+        <v>4153</v>
+      </c>
+      <c r="W169" s="20" t="n">
+        <v>8572</v>
+      </c>
+      <c r="X169" s="20" t="n">
+        <v>9863</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="18" t="inlineStr">
         <is>
-          <t>감가상각비</t>
-        </is>
+          <t>LeasingReportableSegmentMember · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C170" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="D170" s="20" t="n">
+        <v>384</v>
       </c>
       <c r="E170" s="20" t="n">
-        <v>3312</v>
+        <v>252</v>
+      </c>
+      <c r="F170" s="20" t="n">
+        <v>139</v>
+      </c>
+      <c r="G170" s="20" t="n">
+        <v>615</v>
+      </c>
+      <c r="H170" s="20" t="n">
+        <v>129</v>
       </c>
       <c r="I170" s="20" t="n">
-        <v>4249</v>
+        <v>-198</v>
+      </c>
+      <c r="J170" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K170" s="20" t="n">
+        <v>183</v>
+      </c>
+      <c r="L170" s="20" t="n">
+        <v>210</v>
       </c>
       <c r="M170" s="20" t="n">
-        <v>5268</v>
-      </c>
-      <c r="U170" s="20" t="n">
-        <v>3177</v>
+        <v>57</v>
+      </c>
+      <c r="N170" s="20" t="n">
+        <v>298</v>
       </c>
       <c r="V170" s="20" t="n">
-        <v>3312</v>
+        <v>252</v>
       </c>
       <c r="W170" s="20" t="n">
-        <v>4249</v>
+        <v>-198</v>
       </c>
       <c r="X170" s="20" t="n">
-        <v>5268</v>
+        <v>57</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="18" t="inlineStr">
         <is>
-          <t>손상차손</t>
-        </is>
+          <t>SecuritiesReportableSegmentMember · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C171" s="20" t="n">
+        <v>226</v>
+      </c>
+      <c r="D171" s="20" t="n">
+        <v>162</v>
       </c>
       <c r="E171" s="20" t="n">
-        <v>122</v>
+        <v>236</v>
+      </c>
+      <c r="F171" s="20" t="n">
+        <v>354</v>
+      </c>
+      <c r="G171" s="20" t="n">
+        <v>215</v>
+      </c>
+      <c r="H171" s="20" t="n">
+        <v>137</v>
       </c>
       <c r="I171" s="20" t="n">
-        <v>100</v>
+        <v>162</v>
+      </c>
+      <c r="J171" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="K171" s="20" t="n">
+        <v>306</v>
+      </c>
+      <c r="L171" s="20" t="n">
+        <v>567</v>
       </c>
       <c r="M171" s="20" t="n">
-        <v>30</v>
-      </c>
-      <c r="U171" s="20" t="n">
-        <v>55</v>
+        <v>377</v>
+      </c>
+      <c r="N171" s="20" t="n">
+        <v>524</v>
       </c>
       <c r="V171" s="20" t="n">
-        <v>122</v>
+        <v>236</v>
       </c>
       <c r="W171" s="20" t="n">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="X171" s="20" t="n">
-        <v>30</v>
+        <v>377</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="18" t="inlineStr">
         <is>
-          <t>영업권 상각</t>
-        </is>
+          <t>보고부문 합계 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C172" s="20" t="n">
+        <v>4636</v>
+      </c>
+      <c r="D172" s="20" t="n">
+        <v>11099</v>
+      </c>
+      <c r="E172" s="20" t="n">
+        <v>4641</v>
+      </c>
+      <c r="F172" s="20" t="n">
+        <v>13526</v>
+      </c>
+      <c r="G172" s="20" t="n">
+        <v>7061</v>
+      </c>
+      <c r="H172" s="20" t="n">
+        <v>8227</v>
       </c>
       <c r="I172" s="20" t="n">
-        <v>0</v>
+        <v>8537</v>
+      </c>
+      <c r="J172" s="20" t="n">
+        <v>14537</v>
+      </c>
+      <c r="K172" s="20" t="n">
+        <v>9756</v>
+      </c>
+      <c r="L172" s="20" t="n">
+        <v>19801</v>
       </c>
       <c r="M172" s="20" t="n">
-        <v>61</v>
+        <v>10298</v>
+      </c>
+      <c r="N172" s="20" t="n">
+        <v>19509</v>
+      </c>
+      <c r="V172" s="20" t="n">
+        <v>4641</v>
       </c>
       <c r="W172" s="20" t="n">
-        <v>0</v>
+        <v>8537</v>
       </c>
       <c r="X172" s="20" t="n">
-        <v>61</v>
+        <v>10298</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="18" t="inlineStr">
         <is>
-          <t>주식보상비용</t>
-        </is>
+          <t>기타 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C173" s="20" t="n">
+        <v>124</v>
+      </c>
+      <c r="D173" s="20" t="n">
+        <v>3681</v>
       </c>
       <c r="E173" s="20" t="n">
-        <v>97</v>
+        <v>194</v>
+      </c>
+      <c r="F173" s="20" t="n">
+        <v>6267</v>
+      </c>
+      <c r="G173" s="20" t="n">
+        <v>168</v>
+      </c>
+      <c r="H173" s="20" t="n">
+        <v>12492</v>
       </c>
       <c r="I173" s="20" t="n">
-        <v>89</v>
+        <v>555</v>
+      </c>
+      <c r="J173" s="20" t="n">
+        <v>10459</v>
+      </c>
+      <c r="K173" s="20" t="n">
+        <v>468</v>
+      </c>
+      <c r="L173" s="20" t="n">
+        <v>26967</v>
       </c>
       <c r="M173" s="20" t="n">
-        <v>345</v>
-      </c>
-      <c r="U173" s="20" t="n">
-        <v>39</v>
+        <v>391</v>
+      </c>
+      <c r="N173" s="20" t="n">
+        <v>11422</v>
       </c>
       <c r="V173" s="20" t="n">
-        <v>97</v>
+        <v>194</v>
       </c>
       <c r="W173" s="20" t="n">
-        <v>89</v>
+        <v>555</v>
       </c>
       <c r="X173" s="20" t="n">
-        <v>345</v>
+        <v>391</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="18" t="inlineStr">
         <is>
-          <t>대손충당금 전입</t>
-        </is>
+          <t>합계 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C174" s="20" t="n">
+        <v>4760</v>
+      </c>
+      <c r="D174" s="20" t="n">
+        <v>14780</v>
       </c>
       <c r="E174" s="20" t="n">
-        <v>8942</v>
+        <v>4835</v>
+      </c>
+      <c r="F174" s="20" t="n">
+        <v>19794</v>
+      </c>
+      <c r="G174" s="20" t="n">
+        <v>7228</v>
+      </c>
+      <c r="H174" s="20" t="n">
+        <v>20719</v>
       </c>
       <c r="I174" s="20" t="n">
-        <v>14034</v>
+        <v>9092</v>
+      </c>
+      <c r="J174" s="20" t="n">
+        <v>24996</v>
+      </c>
+      <c r="K174" s="20" t="n">
+        <v>10224</v>
+      </c>
+      <c r="L174" s="20" t="n">
+        <v>46769</v>
       </c>
       <c r="M174" s="20" t="n">
-        <v>6737</v>
-      </c>
-      <c r="U174" s="20" t="n">
-        <v>5717</v>
+        <v>10689</v>
+      </c>
+      <c r="N174" s="20" t="n">
+        <v>30932</v>
       </c>
       <c r="V174" s="20" t="n">
-        <v>8942</v>
+        <v>4835</v>
       </c>
       <c r="W174" s="20" t="n">
-        <v>14034</v>
+        <v>9092</v>
       </c>
       <c r="X174" s="20" t="n">
-        <v>6737</v>
+        <v>10689</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="18" t="inlineStr">
         <is>
-          <t>상여충당금 증감</t>
-        </is>
+          <t>조정액 · 부문 이익</t>
+        </is>
+      </c>
+      <c r="C175" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" s="20" t="n">
+        <v>-3496</v>
       </c>
       <c r="E175" s="20" t="n">
-        <v>26</v>
+        <v>37</v>
+      </c>
+      <c r="F175" s="20" t="n">
+        <v>-6065</v>
+      </c>
+      <c r="G175" s="20" t="n">
+        <v>27</v>
+      </c>
+      <c r="H175" s="20" t="n">
+        <v>-12492</v>
       </c>
       <c r="I175" s="20" t="n">
-        <v>205</v>
+        <v>5</v>
+      </c>
+      <c r="J175" s="20" t="n">
+        <v>-10012</v>
+      </c>
+      <c r="K175" s="20" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L175" s="20" t="n">
+        <v>-26474</v>
       </c>
       <c r="M175" s="20" t="n">
-        <v>267</v>
-      </c>
-      <c r="U175" s="20" t="n">
-        <v>67</v>
+        <v>-146</v>
+      </c>
+      <c r="N175" s="20" t="n">
+        <v>-10663</v>
       </c>
       <c r="V175" s="20" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="W175" s="20" t="n">
-        <v>205</v>
+        <v>5</v>
       </c>
       <c r="X175" s="20" t="n">
-        <v>267</v>
+        <v>-146</v>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="18" t="inlineStr">
-        <is>
-          <t>임원 상여충당금 증감</t>
-        </is>
-      </c>
-      <c r="E176" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="I176" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M176" s="20" t="n">
-        <v>-12</v>
-      </c>
-      <c r="U176" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V176" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="W176" s="20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X176" s="20" t="n">
-        <v>-12</v>
+      <c r="A176" s="9" t="inlineStr">
+        <is>
+          <t>부문 이익</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="n">
+        <v>4761</v>
+      </c>
+      <c r="D176" s="12" t="n">
+        <v>11283</v>
+      </c>
+      <c r="E176" s="12" t="n">
+        <v>4872</v>
+      </c>
+      <c r="F176" s="12" t="n">
+        <v>13728</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>7256</v>
+      </c>
+      <c r="H176" s="12" t="n">
+        <v>8226</v>
+      </c>
+      <c r="I176" s="12" t="n">
+        <v>9098</v>
+      </c>
+      <c r="V176" s="12" t="n">
+        <v>4872</v>
+      </c>
+      <c r="W176" s="12" t="n">
+        <v>9098</v>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="18" t="inlineStr">
-        <is>
-          <t>퇴직급여부채 증감</t>
-        </is>
-      </c>
-      <c r="E177" s="20" t="n">
-        <v>288</v>
-      </c>
-      <c r="I177" s="20" t="n">
-        <v>-763</v>
-      </c>
-      <c r="M177" s="20" t="n">
-        <v>-462</v>
-      </c>
-      <c r="U177" s="20" t="n">
-        <v>-290</v>
-      </c>
-      <c r="V177" s="20" t="n">
-        <v>288</v>
-      </c>
-      <c r="W177" s="20" t="n">
-        <v>-763</v>
-      </c>
-      <c r="X177" s="20" t="n">
-        <v>-462</v>
+      <c r="A177" s="43" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G177" s="15">
+        <f>IF(OR(G176="",C176=""),"",IF(C176&lt;=0,"",IFERROR(G176/C176-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H177" s="15">
+        <f>IF(OR(H176="",D176=""),"",IF(D176&lt;=0,"",IFERROR(H176/D176-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I177" s="15">
+        <f>IF(OR(I176="",E176=""),"",IF(E176&lt;=0,"",IFERROR(I176/E176-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V177" s="15">
+        <f>IF(OR(V176="",U176=""),"",IF(U176&lt;=0,"",IFERROR(V176/U176-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W177" s="15">
+        <f>IF(OR(W176="",V176=""),"",IF(V176&lt;=0,"",IFERROR(W176/V176-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="18" t="inlineStr">
         <is>
-          <t>임원 퇴직위로 충당금 증감</t>
-        </is>
-      </c>
-      <c r="E178" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="I178" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="M178" s="20" t="n">
-        <v>-24</v>
-      </c>
-      <c r="U178" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V178" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="W178" s="20" t="n">
-        <v>-0</v>
-      </c>
-      <c r="X178" s="20" t="n">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="18" t="inlineStr">
-        <is>
-          <t>Increase Decrease In Provision For Reimbursement Of Deposits Ope CFBNK</t>
-        </is>
-      </c>
-      <c r="E179" s="20" t="n">
-        <v>550</v>
-      </c>
-      <c r="I179" s="20" t="n">
-        <v>-150</v>
-      </c>
-      <c r="M179" s="20" t="n">
-        <v>-100</v>
-      </c>
-      <c r="U179" s="20" t="n">
-        <v>190</v>
-      </c>
-      <c r="V179" s="20" t="n">
-        <v>550</v>
-      </c>
-      <c r="W179" s="20" t="n">
-        <v>-150</v>
-      </c>
-      <c r="X179" s="20" t="n">
-        <v>-100</v>
+          <t>EntityTotalMember · 부문 이익</t>
+        </is>
+      </c>
+      <c r="F178" s="20" t="n">
+        <v>13728</v>
+      </c>
+      <c r="J178" s="20" t="n">
+        <v>14984</v>
+      </c>
+      <c r="N178" s="20" t="n">
+        <v>20269</v>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="18" t="inlineStr">
-        <is>
-          <t>포인트 충당금 증감</t>
-        </is>
-      </c>
-      <c r="E180" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="I180" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="M180" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="U180" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="V180" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="W180" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="X180" s="20" t="n">
-        <v>1</v>
-      </c>
+      <c r="A180" s="16" t="inlineStr">
+        <is>
+          <t>현금흐름표 · 전 항목</t>
+        </is>
+      </c>
+      <c r="B180" s="42" t="inlineStr">
+        <is>
+          <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
+        </is>
+      </c>
+      <c r="C180" s="16" t="n"/>
+      <c r="D180" s="16" t="n"/>
+      <c r="E180" s="16" t="n"/>
+      <c r="F180" s="16" t="n"/>
+      <c r="G180" s="16" t="n"/>
+      <c r="H180" s="16" t="n"/>
+      <c r="I180" s="16" t="n"/>
+      <c r="J180" s="16" t="n"/>
+      <c r="K180" s="16" t="n"/>
+      <c r="L180" s="16" t="n"/>
+      <c r="M180" s="16" t="n"/>
+      <c r="N180" s="16" t="n"/>
+      <c r="O180" s="16" t="n"/>
+      <c r="P180" s="16" t="n"/>
+      <c r="Q180" s="16" t="n"/>
+      <c r="R180" s="16" t="n"/>
+      <c r="S180" s="16" t="n"/>
+      <c r="T180" s="16" t="n"/>
+      <c r="U180" s="16" t="n"/>
+      <c r="V180" s="16" t="n"/>
+      <c r="W180" s="16" t="n"/>
+      <c r="X180" s="16" t="n"/>
+      <c r="Y180" s="16" t="n"/>
+      <c r="Z180" s="16" t="n"/>
+      <c r="AA180" s="16" t="n"/>
+      <c r="AB180" s="16" t="n"/>
+      <c r="AC180" s="16" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="18" t="inlineStr">
-        <is>
-          <t>자금운용수익</t>
-        </is>
-      </c>
-      <c r="E181" s="20" t="n">
-        <v>-124120</v>
-      </c>
-      <c r="I181" s="20" t="n">
-        <v>-150045</v>
-      </c>
-      <c r="M181" s="20" t="n">
-        <v>-169963</v>
-      </c>
-      <c r="U181" s="20" t="n">
-        <v>-93157</v>
-      </c>
-      <c r="V181" s="20" t="n">
-        <v>-124120</v>
-      </c>
-      <c r="W181" s="20" t="n">
-        <v>-150045</v>
-      </c>
-      <c r="X181" s="20" t="n">
-        <v>-169963</v>
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>항목</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>참고</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>2024.2Q</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>2024.3Q</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="inlineStr">
+        <is>
+          <t>2024.4Q</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>2025.1Q</t>
+        </is>
+      </c>
+      <c r="G181" s="5" t="inlineStr">
+        <is>
+          <t>2025.2Q</t>
+        </is>
+      </c>
+      <c r="H181" s="5" t="inlineStr">
+        <is>
+          <t>2025.3Q</t>
+        </is>
+      </c>
+      <c r="I181" s="5" t="inlineStr">
+        <is>
+          <t>2025.4Q</t>
+        </is>
+      </c>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t>2026.1Q</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="inlineStr">
+        <is>
+          <t>2026.2Q</t>
+        </is>
+      </c>
+      <c r="L181" s="5" t="inlineStr">
+        <is>
+          <t>2026.3Q</t>
+        </is>
+      </c>
+      <c r="M181" s="5" t="inlineStr">
+        <is>
+          <t>2026.4Q</t>
+        </is>
+      </c>
+      <c r="N181" s="5" t="inlineStr">
+        <is>
+          <t>2027.1Q</t>
+        </is>
+      </c>
+      <c r="O181" s="5" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="P181" s="5" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q181" s="5" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="R181" s="5" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="S181" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="T181" s="5" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="U181" s="5" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="V181" s="5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="W181" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="X181" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Y181" s="5" t="inlineStr">
+        <is>
+          <t>2027(MW)</t>
+        </is>
+      </c>
+      <c r="Z181" s="5" t="inlineStr">
+        <is>
+          <t>2028(MW)</t>
+        </is>
+      </c>
+      <c r="AA181" s="5" t="inlineStr">
+        <is>
+          <t>2029(MW)</t>
+        </is>
+      </c>
+      <c r="AB181" s="5" t="inlineStr">
+        <is>
+          <t>2030(MW)</t>
+        </is>
+      </c>
+      <c r="AC181" s="5" t="inlineStr">
+        <is>
+          <t>2031(MW)</t>
+        </is>
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="18" t="inlineStr">
-        <is>
-          <t>자금조달비용</t>
-        </is>
-      </c>
-      <c r="E182" s="20" t="n">
-        <v>61843</v>
-      </c>
-      <c r="I182" s="20" t="n">
-        <v>74680</v>
-      </c>
-      <c r="M182" s="20" t="n">
-        <v>76395</v>
-      </c>
-      <c r="U182" s="20" t="n">
-        <v>28134</v>
-      </c>
-      <c r="V182" s="20" t="n">
-        <v>61843</v>
-      </c>
-      <c r="W182" s="20" t="n">
-        <v>74680</v>
-      </c>
-      <c r="X182" s="20" t="n">
-        <v>76395</v>
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="E182" s="12" t="n">
+        <v>30899</v>
+      </c>
+      <c r="I182" s="12" t="n">
+        <v>38282</v>
+      </c>
+      <c r="M182" s="12" t="n">
+        <v>55666</v>
+      </c>
+      <c r="U182" s="12" t="n">
+        <v>29518</v>
+      </c>
+      <c r="V182" s="12" t="n">
+        <v>30899</v>
+      </c>
+      <c r="W182" s="12" t="n">
+        <v>38282</v>
+      </c>
+      <c r="X182" s="12" t="n">
+        <v>55666</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="18" t="inlineStr">
         <is>
-          <t>유가증권 관련 손익</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="E183" s="20" t="n">
-        <v>-5713</v>
+        <v>3312</v>
       </c>
       <c r="I183" s="20" t="n">
-        <v>-3534</v>
+        <v>4249</v>
       </c>
       <c r="M183" s="20" t="n">
-        <v>736</v>
+        <v>5268</v>
       </c>
       <c r="U183" s="20" t="n">
-        <v>1745</v>
+        <v>3177</v>
       </c>
       <c r="V183" s="20" t="n">
-        <v>-5713</v>
+        <v>3312</v>
       </c>
       <c r="W183" s="20" t="n">
-        <v>-3534</v>
+        <v>4249</v>
       </c>
       <c r="X183" s="20" t="n">
-        <v>736</v>
+        <v>5268</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="18" t="inlineStr">
         <is>
-          <t>금전신탁 운용손익</t>
+          <t>손상차손</t>
         </is>
       </c>
       <c r="E184" s="20" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="I184" s="20" t="n">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="M184" s="20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="U184" s="20" t="n">
-        <v>297</v>
+        <v>55</v>
       </c>
       <c r="V184" s="20" t="n">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="W184" s="20" t="n">
-        <v>266</v>
+        <v>100</v>
       </c>
       <c r="X184" s="20" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="18" t="inlineStr">
         <is>
-          <t>외환차손익</t>
-        </is>
-      </c>
-      <c r="E185" s="20" t="n">
-        <v>-49425</v>
+          <t>영업권 상각</t>
+        </is>
       </c>
       <c r="I185" s="20" t="n">
-        <v>5980</v>
+        <v>0</v>
       </c>
       <c r="M185" s="20" t="n">
-        <v>-35524</v>
-      </c>
-      <c r="U185" s="20" t="n">
-        <v>-36402</v>
-      </c>
-      <c r="V185" s="20" t="n">
-        <v>-49425</v>
+        <v>61</v>
       </c>
       <c r="W185" s="20" t="n">
-        <v>5980</v>
+        <v>0</v>
       </c>
       <c r="X185" s="20" t="n">
-        <v>-35524</v>
+        <v>61</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="18" t="inlineStr">
         <is>
-          <t>고정자산 처분손익</t>
+          <t>주식보상비용</t>
         </is>
       </c>
       <c r="E186" s="20" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="I186" s="20" t="n">
-        <v>-104</v>
+        <v>89</v>
       </c>
       <c r="M186" s="20" t="n">
-        <v>49</v>
+        <v>345</v>
       </c>
       <c r="U186" s="20" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="V186" s="20" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="W186" s="20" t="n">
-        <v>-104</v>
+        <v>89</v>
       </c>
       <c r="X186" s="20" t="n">
-        <v>49</v>
+        <v>345</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Trading Account Securities Ope CFBNK</t>
+          <t>대손충당금 전입</t>
         </is>
       </c>
       <c r="E187" s="20" t="n">
-        <v>1005</v>
+        <v>8942</v>
       </c>
       <c r="I187" s="20" t="n">
-        <v>506</v>
+        <v>14034</v>
       </c>
       <c r="M187" s="20" t="n">
-        <v>-13</v>
+        <v>6737</v>
       </c>
       <c r="U187" s="20" t="n">
-        <v>811</v>
+        <v>5717</v>
       </c>
       <c r="V187" s="20" t="n">
-        <v>1005</v>
+        <v>8942</v>
       </c>
       <c r="W187" s="20" t="n">
-        <v>506</v>
+        <v>14034</v>
       </c>
       <c r="X187" s="20" t="n">
-        <v>-13</v>
+        <v>6737</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="18" t="inlineStr">
         <is>
-          <t>기타 자산 증감</t>
+          <t>상여충당금 증감</t>
         </is>
       </c>
       <c r="E188" s="20" t="n">
-        <v>-34707</v>
+        <v>26</v>
       </c>
       <c r="I188" s="20" t="n">
-        <v>54963</v>
+        <v>205</v>
       </c>
       <c r="M188" s="20" t="n">
-        <v>-71041</v>
+        <v>267</v>
       </c>
       <c r="U188" s="20" t="n">
-        <v>-14089</v>
+        <v>67</v>
       </c>
       <c r="V188" s="20" t="n">
-        <v>-34707</v>
+        <v>26</v>
       </c>
       <c r="W188" s="20" t="n">
-        <v>54963</v>
+        <v>205</v>
       </c>
       <c r="X188" s="20" t="n">
-        <v>-71041</v>
+        <v>267</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Lease Receivables And Investment Assets Ope CF</t>
+          <t>임원 상여충당금 증감</t>
         </is>
       </c>
       <c r="E189" s="20" t="n">
-        <v>-3446</v>
+        <v>18</v>
       </c>
       <c r="I189" s="20" t="n">
-        <v>-2908</v>
+        <v>-1</v>
       </c>
       <c r="M189" s="20" t="n">
-        <v>-3461</v>
+        <v>-12</v>
       </c>
       <c r="U189" s="20" t="n">
-        <v>-1606</v>
+        <v>0</v>
       </c>
       <c r="V189" s="20" t="n">
-        <v>-3446</v>
+        <v>18</v>
       </c>
       <c r="W189" s="20" t="n">
-        <v>-2908</v>
+        <v>-1</v>
       </c>
       <c r="X189" s="20" t="n">
-        <v>-3461</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="18" t="inlineStr">
         <is>
-          <t>기타 부채 증감</t>
+          <t>퇴직급여부채 증감</t>
         </is>
       </c>
       <c r="E190" s="20" t="n">
-        <v>14421</v>
+        <v>288</v>
       </c>
       <c r="I190" s="20" t="n">
-        <v>52540</v>
+        <v>-763</v>
       </c>
       <c r="M190" s="20" t="n">
-        <v>143271</v>
+        <v>-462</v>
       </c>
       <c r="U190" s="20" t="n">
-        <v>21106</v>
+        <v>-290</v>
       </c>
       <c r="V190" s="20" t="n">
-        <v>14421</v>
+        <v>288</v>
       </c>
       <c r="W190" s="20" t="n">
-        <v>52540</v>
+        <v>-763</v>
       </c>
       <c r="X190" s="20" t="n">
-        <v>143271</v>
+        <v>-462</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="18" t="inlineStr">
         <is>
-          <t>대출금 순증감</t>
+          <t>임원 퇴직위로 충당금 증감</t>
         </is>
       </c>
       <c r="E191" s="20" t="n">
-        <v>-678242</v>
+        <v>5</v>
       </c>
       <c r="I191" s="20" t="n">
-        <v>-342025</v>
+        <v>-0</v>
       </c>
       <c r="M191" s="20" t="n">
-        <v>-229903</v>
+        <v>-24</v>
       </c>
       <c r="U191" s="20" t="n">
-        <v>-300191</v>
+        <v>2</v>
       </c>
       <c r="V191" s="20" t="n">
-        <v>-678242</v>
+        <v>5</v>
       </c>
       <c r="W191" s="20" t="n">
-        <v>-342025</v>
+        <v>-0</v>
       </c>
       <c r="X191" s="20" t="n">
-        <v>-229903</v>
+        <v>-24</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="18" t="inlineStr">
         <is>
-          <t>예금 순증감</t>
+          <t>Increase Decrease In Provision For Reimbursement Of Deposits Ope CFBNK</t>
         </is>
       </c>
       <c r="E192" s="20" t="n">
-        <v>313518</v>
+        <v>550</v>
       </c>
       <c r="I192" s="20" t="n">
-        <v>45163</v>
+        <v>-150</v>
       </c>
       <c r="M192" s="20" t="n">
-        <v>188317</v>
+        <v>-100</v>
       </c>
       <c r="U192" s="20" t="n">
-        <v>247526</v>
+        <v>190</v>
       </c>
       <c r="V192" s="20" t="n">
-        <v>313518</v>
+        <v>550</v>
       </c>
       <c r="W192" s="20" t="n">
-        <v>45163</v>
+        <v>-150</v>
       </c>
       <c r="X192" s="20" t="n">
-        <v>188317</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="18" t="inlineStr">
         <is>
-          <t>양도성예금 순증감</t>
+          <t>포인트 충당금 증감</t>
         </is>
       </c>
       <c r="E193" s="20" t="n">
-        <v>-57468</v>
+        <v>18</v>
       </c>
       <c r="I193" s="20" t="n">
-        <v>9054</v>
+        <v>9</v>
       </c>
       <c r="M193" s="20" t="n">
-        <v>-48206</v>
+        <v>1</v>
       </c>
       <c r="U193" s="20" t="n">
-        <v>-55678</v>
+        <v>6</v>
       </c>
       <c r="V193" s="20" t="n">
-        <v>-57468</v>
+        <v>18</v>
       </c>
       <c r="W193" s="20" t="n">
-        <v>9054</v>
+        <v>9</v>
       </c>
       <c r="X193" s="20" t="n">
-        <v>-48206</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="18" t="inlineStr">
         <is>
-          <t>차용금(후순위차입금 제외) 순증감</t>
+          <t>자금운용수익</t>
         </is>
       </c>
       <c r="E194" s="20" t="n">
-        <v>423263</v>
+        <v>-124120</v>
       </c>
       <c r="I194" s="20" t="n">
-        <v>19591</v>
+        <v>-150045</v>
       </c>
       <c r="M194" s="20" t="n">
-        <v>86879</v>
+        <v>-169963</v>
       </c>
       <c r="U194" s="20" t="n">
-        <v>-353291</v>
+        <v>-93157</v>
       </c>
       <c r="V194" s="20" t="n">
-        <v>423263</v>
+        <v>-124120</v>
       </c>
       <c r="W194" s="20" t="n">
-        <v>19591</v>
+        <v>-150045</v>
       </c>
       <c r="X194" s="20" t="n">
-        <v>86879</v>
+        <v>-169963</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="18" t="inlineStr">
         <is>
-          <t>콜론 등 순증감</t>
+          <t>자금조달비용</t>
         </is>
       </c>
       <c r="E195" s="20" t="n">
-        <v>-14677</v>
+        <v>61843</v>
       </c>
       <c r="I195" s="20" t="n">
-        <v>2039</v>
+        <v>74680</v>
       </c>
       <c r="M195" s="20" t="n">
-        <v>65294</v>
+        <v>76395</v>
       </c>
       <c r="U195" s="20" t="n">
-        <v>265676</v>
+        <v>28134</v>
       </c>
       <c r="V195" s="20" t="n">
-        <v>-14677</v>
+        <v>61843</v>
       </c>
       <c r="W195" s="20" t="n">
-        <v>2039</v>
+        <v>74680</v>
       </c>
       <c r="X195" s="20" t="n">
-        <v>65294</v>
+        <v>76395</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Payables Under Repurchase Agreements Ope CF</t>
+          <t>유가증권 관련 손익</t>
         </is>
       </c>
       <c r="E196" s="20" t="n">
-        <v>64108</v>
+        <v>-5713</v>
       </c>
       <c r="I196" s="20" t="n">
-        <v>-8254</v>
+        <v>-3534</v>
       </c>
       <c r="M196" s="20" t="n">
-        <v>-71224</v>
+        <v>736</v>
       </c>
       <c r="U196" s="20" t="n">
-        <v>-97093</v>
+        <v>1745</v>
       </c>
       <c r="V196" s="20" t="n">
-        <v>64108</v>
+        <v>-5713</v>
       </c>
       <c r="W196" s="20" t="n">
-        <v>-8254</v>
+        <v>-3534</v>
       </c>
       <c r="X196" s="20" t="n">
-        <v>-71224</v>
+        <v>736</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="18" t="inlineStr">
         <is>
-          <t>콜머니 등 순증감</t>
+          <t>금전신탁 운용손익</t>
         </is>
       </c>
       <c r="E197" s="20" t="n">
-        <v>-34964</v>
+        <v>134</v>
       </c>
       <c r="I197" s="20" t="n">
-        <v>20402</v>
+        <v>266</v>
       </c>
       <c r="M197" s="20" t="n">
-        <v>-14193</v>
+        <v>18</v>
       </c>
       <c r="U197" s="20" t="n">
-        <v>69278</v>
+        <v>297</v>
       </c>
       <c r="V197" s="20" t="n">
-        <v>-34964</v>
+        <v>134</v>
       </c>
       <c r="W197" s="20" t="n">
-        <v>20402</v>
+        <v>266</v>
       </c>
       <c r="X197" s="20" t="n">
-        <v>-14193</v>
+        <v>18</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="18" t="inlineStr">
         <is>
-          <t>채권대차거래 수입담보금 순증감</t>
+          <t>외환차손익</t>
         </is>
       </c>
       <c r="E198" s="20" t="n">
-        <v>180619</v>
+        <v>-49425</v>
       </c>
       <c r="I198" s="20" t="n">
-        <v>161628</v>
+        <v>5980</v>
       </c>
       <c r="M198" s="20" t="n">
-        <v>-2660</v>
+        <v>-35524</v>
       </c>
       <c r="U198" s="20" t="n">
-        <v>-164925</v>
+        <v>-36402</v>
       </c>
       <c r="V198" s="20" t="n">
-        <v>180619</v>
+        <v>-49425</v>
       </c>
       <c r="W198" s="20" t="n">
-        <v>161628</v>
+        <v>5980</v>
       </c>
       <c r="X198" s="20" t="n">
-        <v>-2660</v>
+        <v>-35524</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Deposit Excluding Deposit Paid To Bank Of Japan Ope CFBNK</t>
+          <t>고정자산 처분손익</t>
         </is>
       </c>
       <c r="E199" s="20" t="n">
-        <v>1440</v>
+        <v>7</v>
       </c>
       <c r="I199" s="20" t="n">
-        <v>1016</v>
+        <v>-104</v>
       </c>
       <c r="M199" s="20" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="U199" s="20" t="n">
-        <v>-256</v>
+        <v>1</v>
       </c>
       <c r="V199" s="20" t="n">
-        <v>1440</v>
+        <v>7</v>
       </c>
       <c r="W199" s="20" t="n">
-        <v>1016</v>
+        <v>-104</v>
       </c>
       <c r="X199" s="20" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="18" t="inlineStr">
         <is>
-          <t>Net Increase Decrease In Commercial Papers Ope CFBNK</t>
+          <t>Net Decrease Increase In Trading Account Securities Ope CFBNK</t>
         </is>
       </c>
       <c r="E200" s="20" t="n">
-        <v>-46530</v>
+        <v>1005</v>
       </c>
       <c r="I200" s="20" t="n">
-        <v>0</v>
+        <v>506</v>
+      </c>
+      <c r="M200" s="20" t="n">
+        <v>-13</v>
       </c>
       <c r="U200" s="20" t="n">
-        <v>-8486</v>
+        <v>811</v>
       </c>
       <c r="V200" s="20" t="n">
-        <v>-46530</v>
+        <v>1005</v>
       </c>
       <c r="W200" s="20" t="n">
-        <v>0</v>
+        <v>506</v>
+      </c>
+      <c r="X200" s="20" t="n">
+        <v>-13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="18" t="inlineStr">
         <is>
-          <t>외국환(자산) 순증감</t>
+          <t>기타 자산 증감</t>
         </is>
       </c>
       <c r="E201" s="20" t="n">
-        <v>664</v>
+        <v>-34707</v>
       </c>
       <c r="I201" s="20" t="n">
-        <v>-11406</v>
+        <v>54963</v>
       </c>
       <c r="M201" s="20" t="n">
-        <v>10307</v>
+        <v>-71041</v>
       </c>
       <c r="U201" s="20" t="n">
-        <v>-8459</v>
+        <v>-14089</v>
       </c>
       <c r="V201" s="20" t="n">
-        <v>664</v>
+        <v>-34707</v>
       </c>
       <c r="W201" s="20" t="n">
-        <v>-11406</v>
+        <v>54963</v>
       </c>
       <c r="X201" s="20" t="n">
-        <v>10307</v>
+        <v>-71041</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>외국환(부채) 순증감</t>
+          <t>Net Decrease Increase In Lease Receivables And Investment Assets Ope CF</t>
         </is>
       </c>
       <c r="E202" s="20" t="n">
-        <v>-51</v>
+        <v>-3446</v>
       </c>
       <c r="I202" s="20" t="n">
-        <v>-31</v>
+        <v>-2908</v>
       </c>
       <c r="M202" s="20" t="n">
-        <v>283</v>
+        <v>-3461</v>
       </c>
       <c r="U202" s="20" t="n">
-        <v>-133</v>
+        <v>-1606</v>
       </c>
       <c r="V202" s="20" t="n">
-        <v>-51</v>
+        <v>-3446</v>
       </c>
       <c r="W202" s="20" t="n">
-        <v>-31</v>
+        <v>-2908</v>
       </c>
       <c r="X202" s="20" t="n">
-        <v>283</v>
+        <v>-3461</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="18" t="inlineStr">
         <is>
-          <t>신탁계정 차변 순증감</t>
+          <t>기타 부채 증감</t>
         </is>
       </c>
       <c r="E203" s="20" t="n">
-        <v>1492</v>
+        <v>14421</v>
       </c>
       <c r="I203" s="20" t="n">
-        <v>1945</v>
+        <v>52540</v>
       </c>
       <c r="M203" s="20" t="n">
-        <v>2251</v>
+        <v>143271</v>
       </c>
       <c r="U203" s="20" t="n">
-        <v>1560</v>
+        <v>21106</v>
       </c>
       <c r="V203" s="20" t="n">
-        <v>1492</v>
+        <v>14421</v>
       </c>
       <c r="W203" s="20" t="n">
-        <v>1945</v>
+        <v>52540</v>
       </c>
       <c r="X203" s="20" t="n">
-        <v>2251</v>
+        <v>143271</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="18" t="inlineStr">
         <is>
-          <t>자금운용 수입</t>
+          <t>대출금 순증감</t>
         </is>
       </c>
       <c r="E204" s="20" t="n">
-        <v>120079</v>
+        <v>-678242</v>
       </c>
       <c r="I204" s="20" t="n">
-        <v>148850</v>
+        <v>-342025</v>
       </c>
       <c r="M204" s="20" t="n">
-        <v>167378</v>
+        <v>-229903</v>
       </c>
       <c r="U204" s="20" t="n">
-        <v>91567</v>
+        <v>-300191</v>
       </c>
       <c r="V204" s="20" t="n">
-        <v>120079</v>
+        <v>-678242</v>
       </c>
       <c r="W204" s="20" t="n">
-        <v>148850</v>
+        <v>-342025</v>
       </c>
       <c r="X204" s="20" t="n">
-        <v>167378</v>
+        <v>-229903</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="18" t="inlineStr">
         <is>
-          <t>자금조달 지출</t>
+          <t>예금 순증감</t>
         </is>
       </c>
       <c r="E205" s="20" t="n">
-        <v>-52933</v>
+        <v>313518</v>
       </c>
       <c r="I205" s="20" t="n">
-        <v>-73896</v>
+        <v>45163</v>
       </c>
       <c r="M205" s="20" t="n">
-        <v>-77052</v>
+        <v>188317</v>
       </c>
       <c r="U205" s="20" t="n">
-        <v>-28113</v>
+        <v>247526</v>
       </c>
       <c r="V205" s="20" t="n">
-        <v>-52933</v>
+        <v>313518</v>
       </c>
       <c r="W205" s="20" t="n">
-        <v>-73896</v>
+        <v>45163</v>
       </c>
       <c r="X205" s="20" t="n">
-        <v>-77052</v>
+        <v>188317</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="18" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>양도성예금 순증감</t>
         </is>
       </c>
       <c r="E206" s="20" t="n">
-        <v>124599</v>
+        <v>-57468</v>
       </c>
       <c r="I206" s="20" t="n">
-        <v>62481</v>
+        <v>9054</v>
       </c>
       <c r="M206" s="20" t="n">
-        <v>85755</v>
+        <v>-48206</v>
       </c>
       <c r="U206" s="20" t="n">
-        <v>-395694</v>
+        <v>-55678</v>
       </c>
       <c r="V206" s="20" t="n">
-        <v>124599</v>
+        <v>-57468</v>
       </c>
       <c r="W206" s="20" t="n">
-        <v>62481</v>
+        <v>9054</v>
       </c>
       <c r="X206" s="20" t="n">
-        <v>85755</v>
+        <v>-48206</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="18" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
+          <t>차용금(후순위차입금 제외) 순증감</t>
         </is>
       </c>
       <c r="E207" s="20" t="n">
-        <v>-9008</v>
+        <v>423263</v>
       </c>
       <c r="I207" s="20" t="n">
-        <v>-15536</v>
+        <v>19591</v>
       </c>
       <c r="M207" s="20" t="n">
-        <v>-14851</v>
+        <v>86879</v>
       </c>
       <c r="U207" s="20" t="n">
-        <v>-7787</v>
+        <v>-353291</v>
       </c>
       <c r="V207" s="20" t="n">
-        <v>-9008</v>
+        <v>423263</v>
       </c>
       <c r="W207" s="20" t="n">
-        <v>-15536</v>
+        <v>19591</v>
       </c>
       <c r="X207" s="20" t="n">
-        <v>-14851</v>
+        <v>86879</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="18" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>콜론 등 순증감</t>
         </is>
       </c>
       <c r="E208" s="20" t="n">
-        <v>4</v>
+        <v>-14677</v>
       </c>
       <c r="I208" s="20" t="n">
-        <v>0</v>
+        <v>2039</v>
+      </c>
+      <c r="M208" s="20" t="n">
+        <v>65294</v>
       </c>
       <c r="U208" s="20" t="n">
-        <v>0</v>
+        <v>265676</v>
       </c>
       <c r="V208" s="20" t="n">
-        <v>4</v>
+        <v>-14677</v>
       </c>
       <c r="W208" s="20" t="n">
-        <v>0</v>
+        <v>2039</v>
+      </c>
+      <c r="X208" s="20" t="n">
+        <v>65294</v>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E209" s="12" t="n">
-        <v>115595</v>
-      </c>
-      <c r="I209" s="12" t="n">
-        <v>46944</v>
-      </c>
-      <c r="M209" s="12" t="n">
-        <v>70904</v>
-      </c>
-      <c r="U209" s="12" t="n">
-        <v>-403482</v>
-      </c>
-      <c r="V209" s="12" t="n">
-        <v>115595</v>
-      </c>
-      <c r="W209" s="12" t="n">
-        <v>46944</v>
-      </c>
-      <c r="X209" s="12" t="n">
-        <v>70904</v>
+      <c r="A209" s="18" t="inlineStr">
+        <is>
+          <t>Net Increase Decrease In Payables Under Repurchase Agreements Ope CF</t>
+        </is>
+      </c>
+      <c r="E209" s="20" t="n">
+        <v>64108</v>
+      </c>
+      <c r="I209" s="20" t="n">
+        <v>-8254</v>
+      </c>
+      <c r="M209" s="20" t="n">
+        <v>-71224</v>
+      </c>
+      <c r="U209" s="20" t="n">
+        <v>-97093</v>
+      </c>
+      <c r="V209" s="20" t="n">
+        <v>64108</v>
+      </c>
+      <c r="W209" s="20" t="n">
+        <v>-8254</v>
+      </c>
+      <c r="X209" s="20" t="n">
+        <v>-71224</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="18" t="inlineStr">
         <is>
-          <t>유가증권 취득</t>
+          <t>콜머니 등 순증감</t>
         </is>
       </c>
       <c r="E210" s="20" t="n">
-        <v>-806215</v>
+        <v>-34964</v>
       </c>
       <c r="I210" s="20" t="n">
-        <v>-837497</v>
+        <v>20402</v>
       </c>
       <c r="M210" s="20" t="n">
-        <v>-1183899</v>
+        <v>-14193</v>
       </c>
       <c r="U210" s="20" t="n">
-        <v>-1390078</v>
+        <v>69278</v>
       </c>
       <c r="V210" s="20" t="n">
-        <v>-806215</v>
+        <v>-34964</v>
       </c>
       <c r="W210" s="20" t="n">
-        <v>-837497</v>
+        <v>20402</v>
       </c>
       <c r="X210" s="20" t="n">
-        <v>-1183899</v>
+        <v>-14193</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="18" t="inlineStr">
         <is>
-          <t>유가증권 매각</t>
+          <t>채권대차거래 수입담보금 순증감</t>
         </is>
       </c>
       <c r="E211" s="20" t="n">
-        <v>413801</v>
+        <v>180619</v>
       </c>
       <c r="I211" s="20" t="n">
-        <v>359821</v>
+        <v>161628</v>
       </c>
       <c r="M211" s="20" t="n">
-        <v>665913</v>
+        <v>-2660</v>
       </c>
       <c r="U211" s="20" t="n">
-        <v>1273089</v>
+        <v>-164925</v>
       </c>
       <c r="V211" s="20" t="n">
-        <v>413801</v>
+        <v>180619</v>
       </c>
       <c r="W211" s="20" t="n">
-        <v>359821</v>
+        <v>161628</v>
       </c>
       <c r="X211" s="20" t="n">
-        <v>665913</v>
+        <v>-2660</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>유가증권 상환 수입</t>
+          <t>Net Decrease Increase In Deposit Excluding Deposit Paid To Bank Of Japan Ope CFBNK</t>
         </is>
       </c>
       <c r="E212" s="20" t="n">
-        <v>205573</v>
+        <v>1440</v>
       </c>
       <c r="I212" s="20" t="n">
-        <v>203445</v>
+        <v>1016</v>
       </c>
       <c r="M212" s="20" t="n">
-        <v>241133</v>
+        <v>37</v>
       </c>
       <c r="U212" s="20" t="n">
-        <v>280810</v>
+        <v>-256</v>
       </c>
       <c r="V212" s="20" t="n">
-        <v>205573</v>
+        <v>1440</v>
       </c>
       <c r="W212" s="20" t="n">
-        <v>203445</v>
+        <v>1016</v>
       </c>
       <c r="X212" s="20" t="n">
-        <v>241133</v>
+        <v>37</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="18" t="inlineStr">
         <is>
-          <t>금전신탁 증가 지출</t>
+          <t>Net Increase Decrease In Commercial Papers Ope CFBNK</t>
         </is>
       </c>
       <c r="E213" s="20" t="n">
-        <v>-7562</v>
+        <v>-46530</v>
       </c>
       <c r="I213" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="M213" s="20" t="n">
-        <v>-6347</v>
-      </c>
       <c r="U213" s="20" t="n">
-        <v>-7323</v>
+        <v>-8486</v>
       </c>
       <c r="V213" s="20" t="n">
-        <v>-7562</v>
+        <v>-46530</v>
       </c>
       <c r="W213" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="X213" s="20" t="n">
-        <v>-6347</v>
-      </c>
     </row>
     <row r="214">
       <c r="A214" s="18" t="inlineStr">
         <is>
-          <t>금전신탁 감소 수입</t>
+          <t>외국환(자산) 순증감</t>
         </is>
       </c>
       <c r="E214" s="20" t="n">
-        <v>28</v>
+        <v>664</v>
       </c>
       <c r="I214" s="20" t="n">
-        <v>20300</v>
+        <v>-11406</v>
       </c>
       <c r="M214" s="20" t="n">
-        <v>29</v>
+        <v>10307</v>
       </c>
       <c r="U214" s="20" t="n">
-        <v>10025</v>
+        <v>-8459</v>
       </c>
       <c r="V214" s="20" t="n">
-        <v>28</v>
+        <v>664</v>
       </c>
       <c r="W214" s="20" t="n">
-        <v>20300</v>
+        <v>-11406</v>
       </c>
       <c r="X214" s="20" t="n">
-        <v>29</v>
+        <v>10307</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>외국환(부채) 순증감</t>
         </is>
       </c>
       <c r="E215" s="20" t="n">
-        <v>-3500</v>
+        <v>-51</v>
       </c>
       <c r="I215" s="20" t="n">
-        <v>-11006</v>
+        <v>-31</v>
       </c>
       <c r="M215" s="20" t="n">
-        <v>-6645</v>
+        <v>283</v>
       </c>
       <c r="U215" s="20" t="n">
-        <v>-2143</v>
+        <v>-133</v>
       </c>
       <c r="V215" s="20" t="n">
-        <v>-3500</v>
+        <v>-51</v>
       </c>
       <c r="W215" s="20" t="n">
-        <v>-11006</v>
+        <v>-31</v>
       </c>
       <c r="X215" s="20" t="n">
-        <v>-6645</v>
+        <v>283</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="18" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
+          <t>신탁계정 차변 순증감</t>
         </is>
       </c>
       <c r="E216" s="20" t="n">
-        <v>524</v>
+        <v>1492</v>
       </c>
       <c r="I216" s="20" t="n">
-        <v>762</v>
+        <v>1945</v>
       </c>
       <c r="M216" s="20" t="n">
-        <v>425</v>
+        <v>2251</v>
       </c>
       <c r="U216" s="20" t="n">
-        <v>562</v>
+        <v>1560</v>
       </c>
       <c r="V216" s="20" t="n">
-        <v>524</v>
+        <v>1492</v>
       </c>
       <c r="W216" s="20" t="n">
-        <v>762</v>
+        <v>1945</v>
       </c>
       <c r="X216" s="20" t="n">
-        <v>425</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="18" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>자금운용 수입</t>
         </is>
       </c>
       <c r="E217" s="20" t="n">
-        <v>-1044</v>
+        <v>120079</v>
       </c>
       <c r="I217" s="20" t="n">
-        <v>-899</v>
+        <v>148850</v>
       </c>
       <c r="M217" s="20" t="n">
-        <v>-2266</v>
+        <v>167378</v>
       </c>
       <c r="U217" s="20" t="n">
-        <v>-642</v>
+        <v>91567</v>
       </c>
       <c r="V217" s="20" t="n">
-        <v>-1044</v>
+        <v>120079</v>
       </c>
       <c r="W217" s="20" t="n">
-        <v>-899</v>
+        <v>148850</v>
       </c>
       <c r="X217" s="20" t="n">
-        <v>-2266</v>
+        <v>167378</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="18" t="inlineStr">
         <is>
-          <t>연결범위 변경 자회사 주식 취득</t>
-        </is>
+          <t>자금조달 지출</t>
+        </is>
+      </c>
+      <c r="E218" s="20" t="n">
+        <v>-52933</v>
       </c>
       <c r="I218" s="20" t="n">
-        <v>0</v>
+        <v>-73896</v>
       </c>
       <c r="M218" s="20" t="n">
-        <v>-1519</v>
+        <v>-77052</v>
+      </c>
+      <c r="U218" s="20" t="n">
+        <v>-28113</v>
+      </c>
+      <c r="V218" s="20" t="n">
+        <v>-52933</v>
       </c>
       <c r="W218" s="20" t="n">
-        <v>0</v>
+        <v>-73896</v>
       </c>
       <c r="X218" s="20" t="n">
-        <v>-1519</v>
+        <v>-77052</v>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E219" s="12" t="n">
-        <v>-198394</v>
-      </c>
-      <c r="I219" s="12" t="n">
-        <v>-265073</v>
-      </c>
-      <c r="M219" s="12" t="n">
-        <v>-293176</v>
-      </c>
-      <c r="U219" s="12" t="n">
-        <v>164298</v>
-      </c>
-      <c r="V219" s="12" t="n">
-        <v>-198394</v>
-      </c>
-      <c r="W219" s="12" t="n">
-        <v>-265073</v>
-      </c>
-      <c r="X219" s="12" t="n">
-        <v>-293176</v>
+      <c r="A219" s="18" t="inlineStr">
+        <is>
+          <t>소계</t>
+        </is>
+      </c>
+      <c r="E219" s="20" t="n">
+        <v>124599</v>
+      </c>
+      <c r="I219" s="20" t="n">
+        <v>62481</v>
+      </c>
+      <c r="M219" s="20" t="n">
+        <v>85755</v>
+      </c>
+      <c r="U219" s="20" t="n">
+        <v>-395694</v>
+      </c>
+      <c r="V219" s="20" t="n">
+        <v>124599</v>
+      </c>
+      <c r="W219" s="20" t="n">
+        <v>62481</v>
+      </c>
+      <c r="X219" s="20" t="n">
+        <v>85755</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="18" t="inlineStr">
         <is>
-          <t>Issuance Of Subordinated Bonds Fin CFBNK</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="E220" s="20" t="n">
-        <v>0</v>
+        <v>-9008</v>
       </c>
       <c r="I220" s="20" t="n">
-        <v>20000</v>
+        <v>-15536</v>
       </c>
       <c r="M220" s="20" t="n">
-        <v>20000</v>
+        <v>-14851</v>
+      </c>
+      <c r="U220" s="20" t="n">
+        <v>-7787</v>
       </c>
       <c r="V220" s="20" t="n">
-        <v>0</v>
+        <v>-9008</v>
       </c>
       <c r="W220" s="20" t="n">
-        <v>20000</v>
+        <v>-15536</v>
       </c>
       <c r="X220" s="20" t="n">
-        <v>20000</v>
+        <v>-14851</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="18" t="inlineStr">
         <is>
-          <t>Redemption Of Subordinated Bonds Fin CFBNK</t>
-        </is>
+          <t>법인세 환급</t>
+        </is>
+      </c>
+      <c r="E221" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="I221" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="M221" s="20" t="n">
-        <v>-10000</v>
+      <c r="U221" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V221" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="W221" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="X221" s="20" t="n">
-        <v>-10000</v>
-      </c>
     </row>
     <row r="222">
-      <c r="A222" s="18" t="inlineStr">
-        <is>
-          <t>배당금 지급</t>
-        </is>
-      </c>
-      <c r="E222" s="20" t="n">
-        <v>-5678</v>
-      </c>
-      <c r="I222" s="20" t="n">
-        <v>-10566</v>
-      </c>
-      <c r="M222" s="20" t="n">
-        <v>-12928</v>
-      </c>
-      <c r="U222" s="20" t="n">
-        <v>-5651</v>
-      </c>
-      <c r="V222" s="20" t="n">
-        <v>-5678</v>
-      </c>
-      <c r="W222" s="20" t="n">
-        <v>-10566</v>
-      </c>
-      <c r="X222" s="20" t="n">
-        <v>-12928</v>
+      <c r="A222" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E222" s="12" t="n">
+        <v>115595</v>
+      </c>
+      <c r="I222" s="12" t="n">
+        <v>46944</v>
+      </c>
+      <c r="M222" s="12" t="n">
+        <v>70904</v>
+      </c>
+      <c r="U222" s="12" t="n">
+        <v>-403482</v>
+      </c>
+      <c r="V222" s="12" t="n">
+        <v>115595</v>
+      </c>
+      <c r="W222" s="12" t="n">
+        <v>46944</v>
+      </c>
+      <c r="X222" s="12" t="n">
+        <v>70904</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="18" t="inlineStr">
         <is>
-          <t>리스부채 상환</t>
+          <t>유가증권 취득</t>
         </is>
       </c>
       <c r="E223" s="20" t="n">
-        <v>-251</v>
+        <v>-806215</v>
       </c>
       <c r="I223" s="20" t="n">
-        <v>-218</v>
+        <v>-837497</v>
       </c>
       <c r="M223" s="20" t="n">
-        <v>-185</v>
+        <v>-1183899</v>
       </c>
       <c r="U223" s="20" t="n">
-        <v>-251</v>
+        <v>-1390078</v>
       </c>
       <c r="V223" s="20" t="n">
-        <v>-251</v>
+        <v>-806215</v>
       </c>
       <c r="W223" s="20" t="n">
-        <v>-218</v>
+        <v>-837497</v>
       </c>
       <c r="X223" s="20" t="n">
-        <v>-185</v>
+        <v>-1183899</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="18" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>유가증권 매각</t>
         </is>
       </c>
       <c r="E224" s="20" t="n">
-        <v>-2000</v>
+        <v>413801</v>
       </c>
       <c r="I224" s="20" t="n">
-        <v>-5000</v>
+        <v>359821</v>
       </c>
       <c r="M224" s="20" t="n">
-        <v>-3001</v>
+        <v>665913</v>
       </c>
       <c r="U224" s="20" t="n">
-        <v>-1941</v>
+        <v>1273089</v>
       </c>
       <c r="V224" s="20" t="n">
-        <v>-2000</v>
+        <v>413801</v>
       </c>
       <c r="W224" s="20" t="n">
-        <v>-5000</v>
+        <v>359821</v>
       </c>
       <c r="X224" s="20" t="n">
-        <v>-3001</v>
+        <v>665913</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
         <is>
-          <t>자기주식 매각</t>
+          <t>유가증권 상환 수입</t>
         </is>
       </c>
       <c r="E225" s="20" t="n">
-        <v>0</v>
+        <v>205573</v>
       </c>
       <c r="I225" s="20" t="n">
-        <v>0</v>
+        <v>203445</v>
       </c>
       <c r="M225" s="20" t="n">
-        <v>1</v>
+        <v>241133</v>
       </c>
       <c r="U225" s="20" t="n">
-        <v>0</v>
+        <v>280810</v>
       </c>
       <c r="V225" s="20" t="n">
-        <v>0</v>
+        <v>205573</v>
       </c>
       <c r="W225" s="20" t="n">
-        <v>0</v>
+        <v>203445</v>
       </c>
       <c r="X225" s="20" t="n">
-        <v>1</v>
+        <v>241133</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>스톡옵션 행사 수입</t>
+          <t>금전신탁 증가 지출</t>
         </is>
       </c>
       <c r="E226" s="20" t="n">
-        <v>0</v>
+        <v>-7562</v>
       </c>
       <c r="I226" s="20" t="n">
         <v>0</v>
       </c>
       <c r="M226" s="20" t="n">
-        <v>0</v>
+        <v>-6347</v>
       </c>
       <c r="U226" s="20" t="n">
-        <v>0</v>
+        <v>-7323</v>
       </c>
       <c r="V226" s="20" t="n">
-        <v>0</v>
+        <v>-7562</v>
       </c>
       <c r="W226" s="20" t="n">
         <v>0</v>
       </c>
       <c r="X226" s="20" t="n">
-        <v>0</v>
+        <v>-6347</v>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="9" t="inlineStr">
-        <is>
-          <t>재무활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="E227" s="12" t="n">
-        <v>-7930</v>
-      </c>
-      <c r="I227" s="12" t="n">
-        <v>4214</v>
-      </c>
-      <c r="M227" s="12" t="n">
-        <v>-6114</v>
-      </c>
-      <c r="U227" s="12" t="n">
-        <v>-7844</v>
-      </c>
-      <c r="V227" s="12" t="n">
-        <v>-7930</v>
-      </c>
-      <c r="W227" s="12" t="n">
-        <v>4214</v>
-      </c>
-      <c r="X227" s="12" t="n">
-        <v>-6114</v>
+      <c r="A227" s="18" t="inlineStr">
+        <is>
+          <t>금전신탁 감소 수입</t>
+        </is>
+      </c>
+      <c r="E227" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="I227" s="20" t="n">
+        <v>20300</v>
+      </c>
+      <c r="M227" s="20" t="n">
+        <v>29</v>
+      </c>
+      <c r="U227" s="20" t="n">
+        <v>10025</v>
+      </c>
+      <c r="V227" s="20" t="n">
+        <v>28</v>
+      </c>
+      <c r="W227" s="20" t="n">
+        <v>20300</v>
+      </c>
+      <c r="X227" s="20" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="18" t="inlineStr">
         <is>
-          <t>현금성자산 환산차이</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="E228" s="20" t="n">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="I228" s="20" t="n">
-        <v>0</v>
+        <v>-11006</v>
       </c>
       <c r="M228" s="20" t="n">
-        <v>0</v>
+        <v>-6645</v>
       </c>
       <c r="U228" s="20" t="n">
-        <v>0</v>
+        <v>-2143</v>
       </c>
       <c r="V228" s="20" t="n">
-        <v>0</v>
+        <v>-3500</v>
       </c>
       <c r="W228" s="20" t="n">
-        <v>0</v>
+        <v>-11006</v>
       </c>
       <c r="X228" s="20" t="n">
-        <v>0</v>
+        <v>-6645</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="18" t="inlineStr">
         <is>
+          <t>유형자산 매각</t>
+        </is>
+      </c>
+      <c r="E229" s="20" t="n">
+        <v>524</v>
+      </c>
+      <c r="I229" s="20" t="n">
+        <v>762</v>
+      </c>
+      <c r="M229" s="20" t="n">
+        <v>425</v>
+      </c>
+      <c r="U229" s="20" t="n">
+        <v>562</v>
+      </c>
+      <c r="V229" s="20" t="n">
+        <v>524</v>
+      </c>
+      <c r="W229" s="20" t="n">
+        <v>762</v>
+      </c>
+      <c r="X229" s="20" t="n">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="18" t="inlineStr">
+        <is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="E230" s="20" t="n">
+        <v>-1044</v>
+      </c>
+      <c r="I230" s="20" t="n">
+        <v>-899</v>
+      </c>
+      <c r="M230" s="20" t="n">
+        <v>-2266</v>
+      </c>
+      <c r="U230" s="20" t="n">
+        <v>-642</v>
+      </c>
+      <c r="V230" s="20" t="n">
+        <v>-1044</v>
+      </c>
+      <c r="W230" s="20" t="n">
+        <v>-899</v>
+      </c>
+      <c r="X230" s="20" t="n">
+        <v>-2266</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="18" t="inlineStr">
+        <is>
+          <t>연결범위 변경 자회사 주식 취득</t>
+        </is>
+      </c>
+      <c r="I231" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" s="20" t="n">
+        <v>-1519</v>
+      </c>
+      <c r="W231" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X231" s="20" t="n">
+        <v>-1519</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="9" t="inlineStr">
+        <is>
+          <t>투자활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E232" s="12" t="n">
+        <v>-198394</v>
+      </c>
+      <c r="I232" s="12" t="n">
+        <v>-265073</v>
+      </c>
+      <c r="M232" s="12" t="n">
+        <v>-293176</v>
+      </c>
+      <c r="U232" s="12" t="n">
+        <v>164298</v>
+      </c>
+      <c r="V232" s="12" t="n">
+        <v>-198394</v>
+      </c>
+      <c r="W232" s="12" t="n">
+        <v>-265073</v>
+      </c>
+      <c r="X232" s="12" t="n">
+        <v>-293176</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="18" t="inlineStr">
+        <is>
+          <t>Issuance Of Subordinated Bonds Fin CFBNK</t>
+        </is>
+      </c>
+      <c r="E233" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I233" s="20" t="n">
+        <v>20000</v>
+      </c>
+      <c r="M233" s="20" t="n">
+        <v>20000</v>
+      </c>
+      <c r="V233" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W233" s="20" t="n">
+        <v>20000</v>
+      </c>
+      <c r="X233" s="20" t="n">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="18" t="inlineStr">
+        <is>
+          <t>Redemption Of Subordinated Bonds Fin CFBNK</t>
+        </is>
+      </c>
+      <c r="I234" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" s="20" t="n">
+        <v>-10000</v>
+      </c>
+      <c r="W234" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X234" s="20" t="n">
+        <v>-10000</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="18" t="inlineStr">
+        <is>
+          <t>배당금 지급</t>
+        </is>
+      </c>
+      <c r="E235" s="20" t="n">
+        <v>-5678</v>
+      </c>
+      <c r="I235" s="20" t="n">
+        <v>-10566</v>
+      </c>
+      <c r="M235" s="20" t="n">
+        <v>-12928</v>
+      </c>
+      <c r="U235" s="20" t="n">
+        <v>-5651</v>
+      </c>
+      <c r="V235" s="20" t="n">
+        <v>-5678</v>
+      </c>
+      <c r="W235" s="20" t="n">
+        <v>-10566</v>
+      </c>
+      <c r="X235" s="20" t="n">
+        <v>-12928</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="18" t="inlineStr">
+        <is>
+          <t>리스부채 상환</t>
+        </is>
+      </c>
+      <c r="E236" s="20" t="n">
+        <v>-251</v>
+      </c>
+      <c r="I236" s="20" t="n">
+        <v>-218</v>
+      </c>
+      <c r="M236" s="20" t="n">
+        <v>-185</v>
+      </c>
+      <c r="U236" s="20" t="n">
+        <v>-251</v>
+      </c>
+      <c r="V236" s="20" t="n">
+        <v>-251</v>
+      </c>
+      <c r="W236" s="20" t="n">
+        <v>-218</v>
+      </c>
+      <c r="X236" s="20" t="n">
+        <v>-185</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="18" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="E237" s="20" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="I237" s="20" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="M237" s="20" t="n">
+        <v>-3001</v>
+      </c>
+      <c r="U237" s="20" t="n">
+        <v>-1941</v>
+      </c>
+      <c r="V237" s="20" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="W237" s="20" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="X237" s="20" t="n">
+        <v>-3001</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="18" t="inlineStr">
+        <is>
+          <t>자기주식 매각</t>
+        </is>
+      </c>
+      <c r="E238" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I238" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U238" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V238" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W238" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X238" s="20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="18" t="inlineStr">
+        <is>
+          <t>스톡옵션 행사 수입</t>
+        </is>
+      </c>
+      <c r="E239" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I239" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U239" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V239" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W239" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X239" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="E240" s="12" t="n">
+        <v>-7930</v>
+      </c>
+      <c r="I240" s="12" t="n">
+        <v>4214</v>
+      </c>
+      <c r="M240" s="12" t="n">
+        <v>-6114</v>
+      </c>
+      <c r="U240" s="12" t="n">
+        <v>-7844</v>
+      </c>
+      <c r="V240" s="12" t="n">
+        <v>-7930</v>
+      </c>
+      <c r="W240" s="12" t="n">
+        <v>4214</v>
+      </c>
+      <c r="X240" s="12" t="n">
+        <v>-6114</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="18" t="inlineStr">
+        <is>
+          <t>현금성자산 환산차이</t>
+        </is>
+      </c>
+      <c r="E241" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I241" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W241" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X241" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="18" t="inlineStr">
+        <is>
           <t>현금성자산 증감</t>
         </is>
       </c>
-      <c r="E229" s="20" t="n">
+      <c r="E242" s="20" t="n">
         <v>-90729</v>
       </c>
-      <c r="I229" s="20" t="n">
+      <c r="I242" s="20" t="n">
         <v>-213913</v>
       </c>
-      <c r="M229" s="20" t="n">
+      <c r="M242" s="20" t="n">
         <v>-228386</v>
       </c>
-      <c r="U229" s="20" t="n">
+      <c r="U242" s="20" t="n">
         <v>-247028</v>
       </c>
-      <c r="V229" s="20" t="n">
+      <c r="V242" s="20" t="n">
         <v>-90729</v>
       </c>
-      <c r="W229" s="20" t="n">
+      <c r="W242" s="20" t="n">
         <v>-213913</v>
       </c>
-      <c r="X229" s="20" t="n">
+      <c r="X242" s="20" t="n">
         <v>-228386</v>
       </c>
     </row>
@@ -12377,7 +13056,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="inlineStr">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -13534,7 +14213,7 @@
       <c r="K42" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="44" t="inlineStr">
+      <c r="A43" s="45" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -13582,7 +14261,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="44" t="inlineStr">
+      <c r="A44" s="45" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -13630,7 +14309,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="44" t="inlineStr">
+      <c r="A45" s="45" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -13678,7 +14357,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="44" t="inlineStr">
+      <c r="A46" s="45" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -13726,7 +14405,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="44" t="inlineStr">
+      <c r="A47" s="45" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -13774,7 +14453,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="44" t="inlineStr">
+      <c r="A48" s="45" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -13822,7 +14501,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="44" t="inlineStr">
+      <c r="A49" s="45" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -13832,39 +14511,39 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="45">
+      <c r="C49" s="46">
         <f>IFERROR(IF((IF(COUNT('연간'!G56:J56)&lt;4,"",SUM('연간'!G56:J56)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G56:J56)&lt;4,"",SUM('연간'!G56:J56)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="46">
+      <c r="D49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!H56:K56)&lt;4,"",SUM('연간'!H56:K56)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H56:K56)&lt;4,"",SUM('연간'!H56:K56)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="46">
+      <c r="E49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!I56:L56)&lt;4,"",SUM('연간'!I56:L56)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I56:L56)&lt;4,"",SUM('연간'!I56:L56)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="46">
+      <c r="F49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!J56:M56)&lt;4,"",SUM('연간'!J56:M56)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J56:M56)&lt;4,"",SUM('연간'!J56:M56)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="46">
+      <c r="G49" s="47">
         <f>IFERROR(IF((IF(COUNT('연간'!K56:N56)&lt;4,"",SUM('연간'!K56:N56)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K56:N56)&lt;4,"",SUM('연간'!K56:N56)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="45">
+      <c r="H49" s="46">
         <f>IFERROR(IF(('연간'!U56)&lt;=0,"적자",H28/('연간'!U56)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="46">
+      <c r="I49" s="47">
         <f>IFERROR(IF(('연간'!V56)&lt;=0,"적자",I28/('연간'!V56)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="46">
+      <c r="J49" s="47">
         <f>IFERROR(IF(('연간'!W56)&lt;=0,"적자",J28/('연간'!W56)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="46">
+      <c r="K49" s="47">
         <f>IFERROR(IF(('연간'!X56)&lt;=0,"적자",K28/('연간'!X56)),"")</f>
         <v/>
       </c>
@@ -13887,7 +14566,7 @@
       <c r="K50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="44" t="inlineStr">
+      <c r="A51" s="45" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -13935,7 +14614,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="44" t="inlineStr">
+      <c r="A52" s="45" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -13983,7 +14662,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="44" t="inlineStr">
+      <c r="A53" s="45" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -14031,7 +14710,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="44" t="inlineStr">
+      <c r="A54" s="45" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -14079,7 +14758,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="44" t="inlineStr">
+      <c r="A55" s="45" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -14127,7 +14806,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="44" t="inlineStr">
+      <c r="A56" s="45" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -14192,7 +14871,7 @@
       <c r="K57" s="23" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="44" t="inlineStr">
+      <c r="A58" s="45" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -14240,7 +14919,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="44" t="inlineStr">
+      <c r="A59" s="45" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -14250,45 +14929,45 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="47">
+      <c r="C59" s="48">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="48">
+      <c r="D59" s="49">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="48">
+      <c r="E59" s="49">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="48">
+      <c r="F59" s="49">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="48">
+      <c r="G59" s="49">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="47">
+      <c r="H59" s="48">
         <f>IFERROR(H8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="48">
+      <c r="I59" s="49">
         <f>IFERROR(I8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="48">
+      <c r="J59" s="49">
         <f>IFERROR(J8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="48">
+      <c r="K59" s="49">
         <f>IFERROR(K8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="44" t="inlineStr">
+      <c r="A60" s="45" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -14298,45 +14977,45 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="47">
+      <c r="C60" s="48">
         <f>IFERROR(C9/(IF(COUNT('연간'!G23:J23)&lt;4,"",SUM('연간'!G23:J23)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="48">
+      <c r="D60" s="49">
         <f>IFERROR(D9/(IF(COUNT('연간'!H23:K23)&lt;4,"",SUM('연간'!H23:K23)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="48">
+      <c r="E60" s="49">
         <f>IFERROR(E9/(IF(COUNT('연간'!I23:L23)&lt;4,"",SUM('연간'!I23:L23)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="48">
+      <c r="F60" s="49">
         <f>IFERROR(F9/(IF(COUNT('연간'!J23:M23)&lt;4,"",SUM('연간'!J23:M23)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="48">
+      <c r="G60" s="49">
         <f>IFERROR(G9/(IF(COUNT('연간'!K23:N23)&lt;4,"",SUM('연간'!K23:N23)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="47">
+      <c r="H60" s="48">
         <f>IFERROR(H9/('연간'!U23)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="48">
+      <c r="I60" s="49">
         <f>IFERROR(I9/('연간'!V23)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="48">
+      <c r="J60" s="49">
         <f>IFERROR(J9/('연간'!W23)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="48">
+      <c r="K60" s="49">
         <f>IFERROR(K9/('연간'!X23)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="44" t="inlineStr">
+      <c r="A61" s="45" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -14346,45 +15025,45 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="47">
+      <c r="C61" s="48">
         <f>IFERROR(C19/(IF(COUNT('연간'!G23:J23)&lt;4,"",SUM('연간'!G23:J23)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="48">
+      <c r="D61" s="49">
         <f>IFERROR(D19/(IF(COUNT('연간'!H23:K23)&lt;4,"",SUM('연간'!H23:K23)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="48">
+      <c r="E61" s="49">
         <f>IFERROR(E19/(IF(COUNT('연간'!I23:L23)&lt;4,"",SUM('연간'!I23:L23)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="48">
+      <c r="F61" s="49">
         <f>IFERROR(F19/(IF(COUNT('연간'!J23:M23)&lt;4,"",SUM('연간'!J23:M23)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="48">
+      <c r="G61" s="49">
         <f>IFERROR(G19/(IF(COUNT('연간'!K23:N23)&lt;4,"",SUM('연간'!K23:N23)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="47">
+      <c r="H61" s="48">
         <f>IFERROR(H19/('연간'!U23)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="48">
+      <c r="I61" s="49">
         <f>IFERROR(I19/('연간'!V23)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="48">
+      <c r="J61" s="49">
         <f>IFERROR(J19/('연간'!W23)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="48">
+      <c r="K61" s="49">
         <f>IFERROR(K19/('연간'!X23)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="44" t="inlineStr">
+      <c r="A62" s="45" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -14394,39 +15073,39 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="47">
+      <c r="C62" s="48">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="48">
+      <c r="D62" s="49">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="48">
+      <c r="E62" s="49">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="48">
+      <c r="F62" s="49">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="48">
+      <c r="G62" s="49">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="47">
+      <c r="H62" s="48">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="48">
+      <c r="I62" s="49">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="48">
+      <c r="J62" s="49">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="48">
+      <c r="K62" s="49">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
@@ -14449,7 +15128,7 @@
       <c r="K63" s="23" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="44" t="inlineStr">
+      <c r="A64" s="45" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -14497,7 +15176,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="44" t="inlineStr">
+      <c r="A65" s="45" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -14545,7 +15224,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="44" t="inlineStr">
+      <c r="A66" s="45" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -14593,7 +15272,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="44" t="inlineStr">
+      <c r="A67" s="45" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -16685,24 +17364,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="inlineStr">
+      <c r="A1" s="50" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="51" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="50" t="inlineStr">
+      <c r="B3" s="51" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="51" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
